--- a/Output/reporte_REAL.xlsx
+++ b/Output/reporte_REAL.xlsx
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.08</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-11T10:46:53.058492</t>
+          <t>2026-02-12T09:51:45.540427</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.9125</v>
+        <v>-1.165494736842105</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.86875</v>
+        <v>-1.74899298245614</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9562499999999999</v>
+        <v>0.5585298245614037</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.9562499999999999</v>
+        <v>-0.6666140350877193</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.295</v>
+        <v>-1.394442105263158</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,26 +609,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-10T17:00:00</t>
+          <t>2026-02-12T15:11:01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kristi Noem Firma Contrato Para la Compra de Acero para el Muro entre EUA y México - N+</t>
+          <t>México pide a EU revisar aranceles a acero, aluminio y sector automotriz: Ebrard - Tiempo La Noticia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N+</t>
+          <t>Tiempo La Noticia Digital</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPamxsVURNOGU0aGN5Z1g2QVpTeFZxcFNFY2tJS01MWC05ZWF5bG1tU1hnN0RRSG9Fd2VxM2hqVDBNd1pwdThmeUJkUXVCM19DdEVhSHFiaENnLUdkVXhyYTd6WS1pdy1sM09jUXhoU3BJTVBCUVdTNWIzWTZyb1R1ZWdPLXduNFVmdDhhbURERl9YUkVCR28yamVVZmFrWEpHdGNNeWZYM3RLSmR3SjY5VGJjTWhJWUpVcU4tZW9JS1dkbFMxQkgyMGlCb0F3WUZvdUh6amd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNajFrU3ZnYTV0NE4yd1ZBLWNidEExT2JicmdjVWhWaWJRU1Q5TWUzT3MxVW5rWjE3bFo0YjVUTy1UUDdtN3NtbHdxSng5RHNTMy1uSTZPSklxeHRMNzhxQ2NkUWNQWFpnVWg5OEQ0TktlbDBSNTJpb2JIczEwSjUtRXhBUm1lTkJWVXVtbWNaSDlfQzJkbWlraVFsQ3dUWE5IVk9IU0xfRVhKZjVjalV3dg?oc=5</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -636,37 +636,37 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-08T21:20:47</t>
+          <t>2026-02-12T14:07:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jóvenes escalan chimenea de AHMSA en Monclova y se viralizan en redes - vanguardia.com.mx</t>
+          <t>Ternium toma el control de Usiminas tras comprar la participación de Nippon en Brasil - La Nación</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vanguardia.com.mx</t>
+          <t>La Nación</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeHNyWFhVTVVoNGcySjIzSTZXSGsxM2pfc2VCMC1rbDgweU9odG9IaGp3Y1ROU1lWTGZQbHRyQXVWVWRwX1o1aXduamZ3QzJUOEpGZlVqZEFqU0t3XzBITmU2bmNyX3dMVW5pUWlkaE9hUy05SkU1YS1WX215RWZZMS1BMkt3ZVRQSG5CaUJXckx2QV9lZWJyeXdKbGlxUER6T25zVDBHU3loTEFkdnBKSThpSU5ka2duTllFSXVfSFFYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOd2s0M1NwcVpIQVdGNDhEdXQ2RzR4Wkc0VHFkcTZCZmxoNl84NkVqYWpXdURHOWlObmRuLWxnRWljU3BzdmtXX3dqS283dDJqQ3JMeU1nU2ROOXpERTFoWHgzQ09aM0hyRkV5NjJYU1ZybHNmbkRya1ZoX0V2czk4YXUta3FkSzlURjA1blpvME16N1JVclY4V0d2d3RsMVRVSWcteE5fLVp3OWpsM29Ra2xndnA3emFpeGI5TnoxTDczZ0psYlpBaWxSQUdzVHc5Q1I0YVF2RjRCWDVS?oc=5</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -693,22 +693,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-08T14:00:00</t>
+          <t>2026-02-12T13:56:03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Entre fuego y acero, la herencia artesanal de los cuchilleros de Sayula de México - UDG TV</t>
+          <t>Ternium toma el control de una acerera de Brasil - Ejes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UDG TV</t>
+          <t>Ejes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPQWVLdjlMX1J0MHY5dHNrMjA3WlJTTWJkV1o4N010UGR5d3dtUzVpc3RUenYwR1BoeG9vNllDLXN5dU1sb2hsZjNFSkNtSE14aVJ3S2N0cXRxM1Q5d3M0ZERHay1KZFpVNm5mUDlGOWl2Y3VoNC11anZSRUd5T2p5QW1IZVBJS1RWVFR3dUsyNzRnYXo0dks3bHp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQVUxyZk9HTE4wQXhYeEV6dUpoamlSM3FpWkFMNVB6VHNINW9KbTFiOVNMejZtLUVnX2duek04MllENHpYUmRYWEp3R245Qk5kYjdZTGRYUWNnMWpabmJtR3NBUFJtaWM0MDFBLUxNeW1XcDhwd2hLVzRiT1VMamgyeW1hWk5FVUhyR1RranNadzNGQlpJR3BqWS1WMzM?oc=5</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -735,43 +735,2269 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-05T10:28:49</t>
+          <t>2026-02-12T12:15:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Estados Unidos ultima un acuerdo con México para permitir un cupo de acero sin aranceles del 50% - M</t>
+          <t>China y México mantienen conversaciones en medio de tensiones comerciales por aranceles - El Economi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>El Economista</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOT0lpWWt2MXo2Ym1fbHdrVEF6V2loR25WSkZkLXVuTHNtOUp5dW41bWZ0a2V3dFAyY25ONmhGMHlrT1JMRE1fWmNIS0hRSXAwM1dUa3UwblBNR0dySkktRmpKdF9aTVFoZXpVbFF4MlEtRmwzSTd2Yzc1OWxUNXBYUFJ6empNLTY3NlFKZFVmcXhwX2ptWUdZZmZIOTNPbm02a2RENmpUb0h3LTFIbEtBeERzWGFxZlBPLVdsOUQyaXlIZ1Utekl5UUFsWndXdHJwUGlJ0gHYAUFVX3lxTE1aZVMxYU9VdjdqUzMzUW9aVEdMVWN4elpjX013R1RkQ0VDb2V3WjRyMEx4VFhYRjRDUTlVb29XVFBxNkxtRGZJZ0hpV2V5LXVuOGRadE5NSHRPRGdkRzJaVUN2bjNkUEpnbHdVUnVXN3FfQlhtZGhheDFUTHdNdE81aXdNZEozYTdKampaajJNZWdtc1RnTUx0Tmw5UWY4ME5iRHROLXJhLTZoSVFiUUl1TzdZTDd4T3E2WHZLSjNKWkZkdG5NcGdmWmpGNkxhR2RtQndUck1iVg?oc=5</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-12T11:16:54</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CEO de Thyssenkrupp: Aranceles mejoran panorama del acero y negociaciones con Jindal - Investing.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investing.com México - Finanzas, Bolsa y Forex</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQNXhjRHJNNzRkSHN2eTNWcGdaX1FCYzRLNGtvQkx2Si1fcjB3X2sxS1dYWnhpUWtZdnU4SmlwR01ZVklSUGdQOHg3Y0RzanFSUWgza25VSmNwaERiOWdJbk11c0NjMnJ2X2NiaFJwam9KVEoyTHNTNTl2Y1lvZFhHZkhQMmJiLUdJcWc4RDAxamVmcmJWSHBVN3F1MlBnS0hWYWJ3TlpwTFRTcWRwYXoyZExGVjZITjhsTnVxeEh1YVF3TnlJd0l0WWFsT1ZGZkdQTXhoZzB6MnRobnNO?oc=5</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>positivo</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-9.899999999999999</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-12T11:15:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Director ejecutivo de Thyssenkrupp: Aranceles impulsan la confianza en el acero y negociaciones con </t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investing.com Español</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxONkdtb3FEbmNsUmZWVEdHdFBJazNWQ0R1bTFzek9uOVJBSkR3cVFRTTRJTFA2VERoYV9KYXBuWm9hdWdHc2RpV3E0U0ZfdWswYzMxelBlVjlwUUFZdGszTFNocGY5c1hlcDY4ZnR2Q284cnM1WjBGaG40WldhcmZTYmJ0MjNyVFVzRzhJZzNuaWVDYzkwVHhQeDk2Zk9pbHVaVlNQLW5TcHF0cGxfTGg3WDlaS1dPZ1NUa0lBV0dTV1ZybEhaMUwtcC1rbDM2X0lWOEkwTGxSTXVvbmxtQkktMnZVLWZfa3Z0a1BLUWdaM3l1X25GNU9Ua2hR?oc=5</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>positivo</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.899999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-12T03:55:00</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Arcelormittal fuerza la subida de sus precios objetivo a lomos del escudo arancelario - TradingView</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE96QmZVdjBPNDY1RXBtUUwxVDNKaktlODdpcXhhS043UHJZcFdIZDY4M1JmSHZuczR1ZFBSOUF0Q3R2MGprLVpkU3FJdDVRUGxrRFFFN0FwaDFuUnhpRU5IbnhlR09KWHNI?oc=5</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-12T00:30:00</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hay una grave persecución sindical y laboral en Coahuila: Mejía Berdeja - Sociedad Noticias</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sociedad Noticias</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRllJNURiZ0ZraXU5Ny0xc05WX3NJLUowT1U0NlQ3MERpeF9JU1gxZ21FTktVMEV3MGlKdmdvYndtdG9zZDdKRndJUi1fckFNRUx5aHJPOFQ5R0hFM0lKZ1RtLWJnZE0xc2tVb3FaYkwxaGMyZGZ5WW9VVm9RMjlta3UyLUh4R1RBdl85dlJFb2JyRmVaVDEydHpCZXBtR3JNQlNsYUlvVkhoUDdfamRLUmVn?oc=5</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-12T00:20:12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Exige PT se Liquiden a extrabajadores de Altos Hornos de México Tras la Quiebra de la Empresa - Tecn</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tecnoempresa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUHJkdFFiaDBiLVlPOV9CczZlLWFIWFFVbGJOd2UycWNqeU5wdVNtazNGMTJDbVZPdm1qQmt5VlFUYXV6S2ItZ0tSYnZNNE1pOEhKa2pvWXFKaG5tb2ZWaFBjTWZfUlpVZm9mNFZPZGJ6Y0tFRVY2NklSTlRJWkV6UkF4cVBaR0prRXNIQTNfSzVsUW9RbHRGMjNOYmZudEMxUnVqQ0dDTGtQenpxRWlENHFqcjFidWc1ZEE?oc=5</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-11T23:16:00</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Inversionistas buscan adquirir AHMSA en Monclova: subasta el 27 de febrero - Periódico La Voz</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Periódico La Voz</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNOUxFNHBERUNtdTdISXpQaE1wd1pQT2dpdk50cnBMN25fSnlvSDh6S012SVpNbEhqTzRDR0VOd3FvVG5OWEVONUJUZnUyaFh5aTE2VWU0REV0XzR1VDVIUjBzeW9qN0N2SEItRmEyS3M2LUt0eUtFT2wySGtSRGZrV2FHTlBicDc3Q2YwcE9nZWh3VERZZzNzOU52RmVFb1l4RHhfWlZ30gGrAUFVX3lxTE9YTFZZcGFEUHZsbXIxaHpPci1KTzJDbUU1NUwxc0VMR1p5aV9rdHFFRU5rcXVmU3B5MnhwVkFlbkFuWERTbUVBeUs0azN3Z1l3Qi0xX3RnTnIwWV9TcTJZWVFDWDFzMkJXNWp3VWRwbjdNNThBdmpGSERIUm55c0xlTFd4LXBkZzhGdGFlRklyRnFKOE1lOUhWczJWRjE0azloX2MtakVhNDM0WQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-11T21:04:44</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Después de la polémica con la Casa Rosada, Techint concretó una fuerte inversión en Brasil - El Canc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>El Canciller</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPQjVYZ0ZLZ0JkbWVmXzQ1OF8wREpoZ1loWGhYY0hnejdhZ0tmUVE0RFA3SDBrd0ZzMG5GbTJya2JDcmFTN3BZQlJMQ0k4MnltZkx1dnMwaE9aclBGUkNhYmZOOTRkQlF2QkFqaVB1Zk91Vy1veVhtb2tlNDdzVXB4UHN1UTl6VFNpZXduM0JCMXpJY0JRUXdGa3k0REk1R1ExNURLcUJ3eGlXOHBobk1TS3VjY1Z0UXljQ0k4SHlia091VWxydk5VU0Z6WGVEdkViWTZBLThkSGwyd0JEMzRuVk4wa9IB8gFBVV95cUxPSHJGQ0pYbjdJN01oNThSRTlzT2tTSXZrTl9RSXZlUUFuUmZBdHRsSmRaWE1TZm5hZlBaVWNsVDY2VXBKZ3RkR1J2SDRMaFhuRkM0T0lDaUwtejM4bXkwNXpwZGlyS05pcjZfNmlqTUo3SW9WMXhfTmZPLXRxQ0xFUzBJS2I0SmFoLW1jSzRlMjhSQzZuME5WejJxcXlIRXhWRld6b2VUZ2NkRVZOWkdqMVVBSlZoaVdGY0ZNWVNNcjdJOV9PSjJLdlRMME56TS1TZVcwSXVONU5YTVdfS2Fnbk0tZnhVRC12LU04NHRIUnpvQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-11T20:35:00</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Avanza venta de AHMSA; compiten seis compradores por la siderúrgica - PostaMx</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PostaMx</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWHNSM1dUWHNGbkdVTlcwMHdlRVk1bzZWZGZiaVkyOTdpRDNqWHdmb1ljNk1sNjNWVGp0akJLTVRRY3ptZElHcGl5MktlODNCcG5saXhyd2RfZHZ0RzlzNV9MSlR0VlFzSjlNLVh6QTN5Zk5EdG9lNXEzbG93dG1RN295UVFSQVI5TmZaRVdfbWh3WEhRV0hMSGtzbHpyczBlMWVEUzA1THJycXlfX2RZ0gG0AUFVX3lxTE93eXF1V0ZvbWVhRndVaWtqVmtNVkJJbFZhcmhZZUZ6T3NoaGZ1aWhCSzZHX0NGWUFCLTVrWkFEbC12ZnBGb2s0a0x0SU81d0tsUmVITVd1OWNaT0RYZWpiak1pRkYxWG1UTGJpUHZXZ0ZPVWt5U3E1WnZvRmhNcnJNRXVoOFc5b2E4QTBINGc3TzNjX2dvbXU2aFdDajFIb3hIbkdBRjg3VlEzUHJlVzQzeThzZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-11T18:54:23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rocca deja atrás la polémica con Milei: invierte US$ 315 millones en un gigante de Brasil y crece en</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Clarin.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQZ0R1ZHJoQUN3dC1pMEhDZEYyLWdtcnFUMGd5ZkRQRmRMUEhNVkhJMmNDTnJMYWNIbmNaVktnVl9DOHptQ01mQVgzb3lBY3cwRDlJUE9BV0RRXzctd1NTWGR6T0JGcEMxTENfdVlMMnE3QlFBSW1SM2xnU3VEem5nM0ZwbDdwN3J1UXVqUXNKaFJxYS1FQUg1Y0NqTTZHMmVxc3JyYTIweUt4cWxidmhlakZoYVVWTlpTckdJLXczTVdReUp4OEIyay05VXk2UXEt?oc=5</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>positivo</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-11T18:34:00</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confía Grupo de Defensa Laboral en venta de AHMSA durante subasta - INFO7</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INFO7</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeDdxV2k1Yy1oa0xqRkRZRjdqYzYzdUlfejVKYVlZdWl3NVRCNVczeFdHYWVRWkdsMUJmUWVidEJleEVNMzhHT1dEMWpiUDFZaGlVcnJIMVZmM0wxeTBzUHFaYjJrVjBtVXl5OG1xd0hqWUtnaWZsZVVxVGJIempXeU42UHZZZ2pYYzlOWlFvQldCRnBWX01NWEhMeU5ndGswaWt0TE9qQmFib1E?oc=5</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-11T16:55:34</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ampliación de convenios entre México y Brasil elevará más de 10% inversiones en ambos en sectores es</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>diariodetabasco.mx</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNTXpOU2RGZkxHdTNTVkF2VWlzVGVzdEdBdDhzLVNEdmxwanJaTVB5UXd1elNRY0hSdkxubS14RWZCOGNwaVhYdTM3Y1pVR0ZVZXphY25SSV83RU1BZFJvS3NxcmJfUGp5U2NYMm00QXlZT3hlTUlBU0NuVnk1U18wd0Ruc21XSWxGVGxQeElWWHJPc3dWNU92ZVVpVHBSU3FYNFZzbzd2RkZpV1MxUGNTRE9xRDdFT0RrV2t0d1ZDTmRyOV9abFlVWUQ3OE9seERwSlRqWUxJVThTbjNERUVONFN3d01XYVRYVDRBZ0JBMFVTbmM?oc=5</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-11T15:31:31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ternium avanza en Brasil y adquiere las acciones de Usiminas - LM Neuquén</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LM Neuquén</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYnhsb0s2NkI5SGdJWlB0YlhKOFZKME9rdVMyb1luUXVNSTU5S2lwTzhkLXA1UTBpME5pYzE2aHZpNWtJZVVOWUl6U21OQnNCVFZKVkZKbGNpS1hMMVJ3OFNqamN5SzdURjRDd0tLbE11SkhpWTJpbU95ay1fbl9nTHdsTDRlcWYyZ2tmbFFNalROeEFYMWVxUUZ4REN4NktI?oc=5</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-11T15:27:32</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tras el cruce con el Gobierno, Techint se quedó con más del 70% de una de las principales siderúrgic</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQeE1CTFdCc0s5c0trM05EVFYzSGl0aE5sZDlwcG5lZzY0bE4teXRCYkREamQxdl9McHd5eGNIeEZ3VmV4NTJtZjhfblRGaC1ncGFFcFhmWnVtSF91Q2RJZVpqS3I3ajIxUE5OLTdJbm52QTR0N1NBLVNYTHBkWFA4UXZvaDczN0pROHFqS0tMUGs0MjVQQk52THgtWDhGd1lHNGZwcXBMaU9OM2p5TDl5TXJmdDFWWXhOS29wTzNVVFI1U0JZRXloM0hzSVdBMl9DQ0ZOX3JsSTM2ZGdKMlHSAfgBQVVfeXFMUGloMVU0Um9kdVlJa2dQWnphRjZOMUpWVGF6ejgxWk9rNDA2Zm00UV8xbWJ4bWdQc1pEdlV3a3pXNnJDMjNGOGh5djZ0ejRQb2JObm1FMEd5d3hrRHlUWWdsNXNwTko4MEh4ZWZCRTcydExVUVhNZ0pGOFV5V1FkVUNwdXl3eDhpa1ZyYlNvMER2X2NFR0JXXy1sOWpVbGNjczRzaG1qbXFPT21pSnhqV2lMR29kVWR5OTctVkxOdWs4MEpWc1hxZG1jZk5CMFAxdkxtSlBORXl1RTY1X09yRG81dlFtX2k2OV9EY2NwbDdtd1RqS0hnTjQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-11T12:00:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Trump amaga con aranceles de 100 % a farmacéuticas mexicanas; quiere su producción en EU - La Crónic</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>La Crónica de Hoy</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPeDdqQWY5ckJuWkpYSXlxMkstNHRtRkFwUDZMcXZrVmZoMk92RHhEM29UeG5Zb1ZKUkFVMHVxVy1OYU11S0lMaUYwVzdGcHZEV01iNVlwNUFtbzBxaWVyUDZuOWRQY0xYbVc4bVhoTDRBS1UySXk4c3l3YmRnbUg3clVZZEJoM2Y3a0hfRkl2M1Fva2diR2dVTlhpZ05tMlVrRE9oS3ZwTmdPRmthRk5RUHl6aE9mRC1jVkh2ckdHd3lFeS13aW5keVd4bzg5QQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>-7.649999999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-11.475</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-3.825</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-11T10:06:18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sugieren que personalidades de la vida pública en México sí tengan protección vehicular de alto nive</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hoja de Ruta Digital</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNNEVBUkRmR1FiaGpReF96cEVSM1lUTVBrd0dEWWdKRDYyVHJLU1FQTU50X2cyRFVUX2lhSWJndkd4R0xOOWVxMXJwM2VCVzFBQ3RMQXRKdWFPV3dCYk9ibndURFBMUlNMSVEweHJYRmZPRFpSZnJhSkZ0ak4za2RoN3hPeE9xZDI2b3U5ZkFEWnQ1OXFvVE1iTDdnY0pCT05ENFd2STdWU29lYy1EZnpBS0VrX0dtQjBJQ2lGUFJ5YVJ2VWxpU1pNbmNJWQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-11T00:20:42</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>La Décima Sexta Zona Naval recibe visita de alumnos de la Escuela Primara “Voluntad de Acero” - Gent</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Gente del Balsas</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPLWUtZjlMbV9KOUw5VEVJSUpiVnpsMVV5eVFDeGFqT0g0S09ZUmppRXZRMVdtTmk5bTFGSzJ0OV9wb0k0OTBQdlhhc19vWlhGLVlTQlVDXzVhcThGbmJBZGRzREhaV1g4QW1SdHY2bDZibl9iSTNZNllpdW1wRU5Lb1ZQOVF6YWdpN2N4ZlRfa3dQMDVxLVdxYVVFZ0RyVUJkcGxKbnAxdldxN0tqSDNjLW9xUDJhMUdkQXIzZThNZDEyVDFLYkhxNg?oc=5</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-11T00:00:00</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Futuro del T-MEC, en riesgo: Trump evalúa sacar a EU del tratado con México y Canadá</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>El Financiero</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.elfinanciero.com.mx/economia/2026/02/11/futuro-del-t-mec-en-riesgo-trump-evalua-sacar-a-eu-del-tratado-con-mexico-y-canada/</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-11T00:00:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ampliación de convenios entre México y Brasil elevará más de 10% inversiones en ambos en sectores es</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Milenio</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://www.milenio.com/negocios/convenios-mexico-brasil-elevaran-inversiones-nuevo-ace</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>positivo</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-10T23:21:44</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mientras se disipa la polémica por los caños, Techint se expande en la industria siderúrgica regiona</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>El Cronista</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPVmV2dGVvaklKdHAyUkd6dFBlQjVoU0dkUmpXbkVXQ1RJeXEwOFU4RFVoNGlOcUtRaUpFZTA1cGFzQ25hS1UzZFpJUWdZckMyR1Z2ZEFuOTJVaFc4V3JSaUZMMjBoQXc4bm8tY2JMdWxPVGFrRmg2WURhU3NHd0l6Q0VENVlhS1Zrd1pIWUQzMm5kQTNOYU1UN3JGNGJYZ3NLb2EtYktSUjBGTktVSXAzbjFjME5tb2sybVNzUkk3V0pLR2VYNldyQnN0WEI0ZExI0gHrAUFVX3lxTE43MVNvdWxNTDNnV3AybWdoSlo0b0NGQXlsSTlReFZsWjlqVFVhYkRORTVPNWk2NzQxUlJ2eldxdnNUcFNPVm5TancyUU03RllHbkd3MThtV1I3UmprX3NJNko0S2dpTnpMNVowNHphQnR3S2hqYmMzSm9MNXY2N2w5S3lsdGlkNmE3T28zZ2txeENxYndIRlJ5RXlMdGY1LUxpcWI3bVo3WmhoT256alNXS3JfbHNvaWNGc0tJYkx5NlRkUHNsZDJXSHV5ZWRaZ1NRZkkzODcyUnpzTEN5YVUzNGw0bDNjdjRYd3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-10T23:21:44</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Mientras se disipa la polémica por los caños, Techint se expande en la industria siderúrgica regiona</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>El Cronista</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxONzFTb3VsTUwzZ1dwMm1naEpaNG9DRkF5bEk5UXhWbFo5alRVYWJETkU1TzVpNjc0MVJSdnpXcXZzVHBTT1ZuU2p3MlFNN0ZZR25HdzE4bVdSN1Jqa19zSTZKNEtnaU56TDVaMDR6YUJ0d0toamJjM0pvTDV2NjdsOUt5bHRpZDZhN09vM2drcXhDcWJ3SEZSeUV5THRmNS1MaXFiN21aN1poaE9uempTV0tyX2xzb2ljRnNLSWJMeTZUZFBzbGQyV0h1eWVkWmdTUWZJMzg3MlJ6c0xDeWFVMzRsNGwzY3Y0WHd30gHrAUFVX3lxTE43MVNvdWxNTDNnV3AybWdoSlo0b0NGQXlsSTlReFZsWjlqVFVhYkRORTVPNWk2NzQxUlJ2eldxdnNUcFNPVm5TancyUU03RllHbkd3MThtV1I3UmprX3NJNko0S2dpTnpMNVowNHphQnR3S2hqYmMzSm9MNXY2N2w5S3lsdGlkNmE3T28zZ2txeENxYndIRlJ5RXlMdGY1LUxpcWI3bVo3WmhoT256alNXS3JfbHNvaWNGc0tJYkx5NlRkUHNsZDJXSHV5ZWRaZ1NRZkkzODcyUnpzTEN5YVUzNGw0bDNjdjRYd3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-10T21:21:00</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ternium completa adquisición de acciones de Usiminas por 315,2 millones de dólares - Investing.com E</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Investing.com Español</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNd1VjUE5fbndlOGdvU2RyNXlpUGhrZ2czSnItbVVPUHVTZjl3bi1felNFWHEydmNqbFZRTUtXenk4UDdpbE5GS2FtekNJLXdwVFhCMkFUSEcwMmN3aHN4ZWVRb0hrZTNBdWVsd0dWZGxQX0IxMW9USmoxNFdIem10eDVBZkEwV0M4ZlhGT3JVa1VyNzZNZ3F4bWtlUlpMeVhHcDVpMGhmeXZxNHR3VVFtWGk4TVVMa0VpcGFsMHBKMWpDRFlQOGdiLVZtdUdncmpCWE1F?oc=5</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-10T17:00:00</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kristi Noem Firma Contrato Para la Compra de Acero para el Muro entre EUA y México - N+</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>N+</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPamxsVURNOGU0aGN5Z1g2QVpTeFZxcFNFY2tJS01MWC05ZWF5bG1tU1hnN0RRSG9Fd2VxM2hqVDBNd1pwdThmeUJkUXVCM19DdEVhSHFiaENnLUdkVXhyYTd6WS1pdy1sM09jUXhoU3BJTVBCUVdTNWIzWTZyb1R1ZWdPLXduNFVmdDhhbURERl9YUkVCR28yamVVZmFrWEpHdGNNeWZYM3RLSmR3SjY5VGJjTWhJWUpVcU4tZW9JS1dkbFMxQkgyMGlCb0F3WUZvdUh6amd3?oc=5</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-10T00:00:00</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cárteles y barras bravas, los principales retos para autoridades mexicanas en la Copa del Mundo 2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Milenio</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.milenio.com/policia/retos-seguridad-copa-del-mundo-2026-mexico-cuales-son</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-10T00:00:00</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Carney contradice a Trump y afirma que ‘Canadá pagó por el puente’ que conecta con EU</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Forbes.com.mx</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://forbes.com.mx/carney-contradice-a-trump-y-afirma-que-canada-pago-por-el-puente-que-conecta-con-eu/</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-10T00:00:00</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>El Volkswagen Virtus 2026 ya tiene precio en México: el sucesor del Vento ofrece dos motores, tres v</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Motorpasión México</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.motorpasion.com.mx/industria/volkswagen-virtus-2026-precio-mexico</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-09T23:23:05</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Empleo formal en México registra en enero su peor inicio de año desde 2009 - bloomberglinea.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bloomberglinea.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNOFcyUXlOZTRTOXBHX0tMRnJtbHNLQXlZSVcwakZSUGdBQmFkTHFZRGxBUXljc1dxYjBpZldMbEEweGRBbXNDM09kSEtjQXNjT2tiUWtjZ2FuMEZlaklBMWx3aU5MTW0zQWRyVUxJTm54R1hvTXM0aFVEVWt3S0d1cjFlNTVHaU9FTUpUTnJ1aHZ4MjB5anhoVzFGU0VldTBreldHZWdaU0ZkVmdPWmpIdTJLNWpMSXhzczJBSi1ENmlJRjlqZUHSAdoBQVVfeXFMTTlTU2xaWENoZnh2NTVhbTNqb3RHbXJkcmMtWFhhSlZYYnhsWlRfdVZlb3k4c3JkTmpEeW1QVzUwSk03RDl1VXBNcTBhZ0pyME10clpPTDlsRUVkRjBWYlBuRHdaQ3lHbXJWRURjTVU5SjdWb0xackxpZ3pYYjkxaHBFR3N0X3Yya2xLeHY3eGF5R3pURnU2MVJQRjFoQldQWEpOc29RUUZVRC1PTGVYZV9FMVZlejVKbzlGS3ZraTJwNkJSR0dEU01IQlRfVTJOaW1iQVJZUTVITUE?oc=5</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-09T21:50:37</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Princess House busca emprendedores en Culiacán y promueve cocina saludable con acero inoxidable - de</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>debate.com.mx</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQSjhxemJYWjhyTndoMlRzTmRjWnlNb2lWOGktbjhuaTRPQmJqTUtwdFZmSjVCZEhtQm42X2VKekZiVG16bXBqNkg1bUVsdXY5TWlCMjlhSDlKLVlQTFZ5ZVBROEsyRVRObWJwZnNxLUxfUzZhSlI5M0FxbGMxb3V5ZldvSGtESHh2SjVIZDRzbnh5dWdRcW9lMTRMSEt4YXBJQ3UzM2tsWGI5TTJRU2ZKODRvMGN6Y0xxNWtHb0RvLWhybXBCMGQ0U2xsSlZpNFFtWEh6TTBuOGtTemlkWG9UYkNKbndDZ0lzQ1JGYXpB0gHzAUFVX3lxTE91cWZDd2ZTWkxNZGV6VFgxOEhkYnBONExjaDJYWXI1ZW9QOFc2Rk5QSzlMSXUySERrbVZ6ckJpNjM3UjlLVVVSUG5MaFRyV1BHY0x4bkJIc2VZYllNNjE3Qm1TU1RiRnI1MlhDOFFaaWM3QkM5RmtOdktjejFsaEtFY01ZMmxGd2R2ZG1vS0M3OWx1bmhfSnQ5amhSREtOb21XQW04T2stV0RVS3FqM2stMmlDSTl4MGNqc2EtXzhzS3NydVlBcHFxbHZyN202dHp5N2hNZzBiN3djYUV3UTI3bDN3UkFiRzllSU40SE9xbmhxdw?oc=5</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-09T09:59:16</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tubos Reunidos registra unas pérdidas de 71,3 millones de euros por los aranceles estadounidenses al</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>MSN</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiogNBVV95cUxPaExJTk5rcW1hc2R6emFudkwwMXBudWxGdHhONkJORUczQ0xwb05kQTdDUnZzS2xBZVVQY2RoQ0JvVHk2Z1NDTThiLVM3RWJJSXNmNm5ITmdCZnhkWHpaZlA5NTkzd0FVcG1IcUZtNDZBTnpKczlScjVhdHVGRmdCdklOOGRUakllWDgzZGhLM0o4aVp1eUZLdVlIazlnZEJrY0k1djU1a0FLbjlJcXI1NnZUd25VMGtWY25XdGdKNjJJU2hfNUJwNXBJZlVhQmVyVFN3NWdqS05TX2EwamJrMmFCZEdqNS1nTTc1WTR4RFlHSFVPOXY4cW1PNDhxVnZtb0d5REpyUzZseGNLalZkbzV4MjJ1ZXo5QzZ3Qk8xdEJfNjBDT0w1eFFkd3lyYjVoajJZWFJ4TlpBWDctTVkxYnpUTVJMZFFxaTl4aTFtbF8tdjJ1dmRkQUt2NTNnQjBDM1pKZGlqemdGejk2VHlVdWVFU2dQUVBKcE5Cc29WVVduZmZBVmJXc3E5YXFCdDdTSzQ2eHVnQVhfa21UbGdMeWtB?oc=5</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>-7.649999999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-11.475</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.825</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-3.825</v>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQWGd2c3B3X3ZadU9tMnp3cWFWSmMySUdMT3ZKTUIxQXRnMmpfWFZfZ3MySlZaNUJJZHhhck01TFVQX3ZMelhNc1ZNQUFsYXVaODVkM0U5aUpzU0V1S01lcFgySDhzNkotUl83OFZVd2ZMd1dRcm9fclZXYVF0VVh0eUdkQ3hmQVhlaXkyQ25fNkxzRFB5d2tvWC13MEZhLVhYZjFjNlZZR3dhZmhQY1YyelQ0Q3JVRmxUUFpsRTRJR3RyS0pURXlaYUREM0ctajFwSkZxUHFITEY1VEwtbEJUbmxxNjVHM0pzNG5iQ1ctYW9RWkFRb29adg?oc=5</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-08T21:20:47</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Jóvenes escalan chimenea de AHMSA en Monclova y se viralizan en redes - vanguardia.com.mx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>vanguardia.com.mx</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeHNyWFhVTVVoNGcySjIzSTZXSGsxM2pfc2VCMC1rbDgweU9odG9IaGp3Y1ROU1lWTGZQbHRyQXVWVWRwX1o1aXduamZ3QzJUOEpGZlVqZEFqU0t3XzBITmU2bmNyX3dMVW5pUWlkaE9hUy05SkU1YS1WX215RWZZMS1BMkt3ZVRQSG5CaUJXckx2QV9lZWJyeXdKbGlxUER6T25zVDBHU3loTEFkdnBKSThpSU5ka2duTllFSXVfSFFYUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-08T18:01:27</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>"Ilegales e injustificados", los aranceles de Trump a acero y aluminio: Canadá; hay "discusiones int</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwNBVV95cUxQREFualdmQ1E5VHIyemE0V3VOdkxXd0xrVXpZcXhhVkpkM2RZVmhDaGJFNTBoZFNuX0FGbEpneHlta3p2S1BHTGN1dWFtVUxGUW9peU8wbVZyY1AwV055SGhxTGdEbTB2TFMwaHEwOTdsd2s1MlZfS2g5UVJoUUpEU2tkY3ZBQmY5ZU1hcWNxYjNQUHByOTJNVV9sSTc3dEVnSlZxZDdYd2lZTkhUMGRLSHdCVFlILVgwWHBCMWlfdF9fRUpPV3lsTFRyNEFqbVgyNXh6X0VsaU40VGZTZ2tQdVc4RjZrcERfVER1eUJJUzNwc0prU2hQcG96X1hyLXdRNEc0ZGpGZFpDbmdYcUswdEUzdFJOcFZ1ZnIwVG83c2pFS2E0bjVhTEw1ZG04UGdmRUg2a3ZJMnZzSU4xa3FOYjFqTk9JVGdBSzBGdkF1dHZDd2hYMjJld0RFQ3ZoNkFvSWhQOTNJREJ0TnlseTVFTld6NmtJQ3lOR2VLSkZFZUlqZTUydEdOZFUydFcxZVYyek1maHpCbw?oc=5</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-08T17:15:11</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Aranceles de EE. UU. y puertos mexicanos: impacto, tensiones y respuestas del sector logístico - Tra</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Transporte.mx</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPMjN3dzFjLW00S1BlRzlGUEZ0R2NKdkZlNVhnLXg4elg3QVU3NF80R3BhWEFuWWI0ZXdEaWFNaTl1WmUxX1hFYlpuUXZWV3F4Q210dVAwdk00NzRneWZmeWRkejRUNDhya0VaV1lYZkpRcEZ1cEZVeFh6RnV4SDJEQTdaNjBWS0RfXzNrbFF3NVFINFFDd21SZ19GMnlqLU1YaENzS1YtTGhlRjZDbzMxRnBJcw?oc=5</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-08T11:19:14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Aranceles a acero y aluminio afectarán precios de la construcción: CMIC Edomex - MSN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gJBVV95cUxOR3h5N1RYZWNBb2pfQlR0dXczajZ1MXVyZmZ0U2VLbHk5OHd6bnkydUF0cWp0VHdjNEhZSUZyUm9xeUlYTXJRLWhheVNuSGxRa2RldEVWdUpWOEpHS0ZFWFd0R0VROHdyZDZTNEcybkh3NHFxbUVHY3QyTnBHcXZEZUJYZ1BxSWxmRWJQY1l3cFlza3lNendtZlNhUkF0OHFaWjdwekFvcnYyb3JZbDhpbTh2UEpGZDNwSGpDYzNBcGw4ZG04dlJEMUJCV2hJb09XZXllYXRFNnhsRm9mNDJGc3ZuNkdIQ1RLbmYtN3cwR04zWmh4em42aEt3dU1jaHFHbml2UHlFQUZQV0ZLWi13cDdqV2EzNGJxcDEyZTdoc0xWZVYwMll2b0dfMld6MlFxOVJESk9Xam81ejNNNWdsQXF1YW5mUGZSRkh3X3ZrSXhLTHJ1RnQxbzB0Y2xJdFlQZEZydHJDRWdGSEFpSnc?oc=5</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>-0.8000000000000002</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-0.4000000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-07T06:09:00</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Aranceles, despidos y silencio en la industria automotriz - El Heraldo de México</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>El Heraldo de México</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNa2l3SVJKUVZzVmNkcWVCOWJLQjBsMjRwWExMSlJyUkZDWTFiZ3lqelpxeUwtOVpKYmxNa2pYc3p5TE95ZG9oQ0ZCT1AxblNlck8yeWNvN0ZiYUk5bU84T0lVNW5RQVU5WmZqUDRmam8tb3BuV3QzejFkd05xcnJvVWxLYlhpN2wwUjBhQmdUUEFaUkt0bUs2VTZzekRqN0xfZmo2MnZPMzdPckNkU1R4ekEzRWrSAboBQVVfeXFMT2c5SUd2cE92ZnhQQnc2OF9GeWlLNmJKMUVKRFRnODRyNEdweTF2SzdGLVVGc0V5SWxkRWxOYjZXVjF4ZmdINU4zR3dqQU5ya2R5S092bjdhYXlWb3NOV2dwZHN1QnhlbFhRNHA4c1FkUkNkOE1fcnVPZzFNbC1lSVVXUGlNYl9Pc2hVRC00LWRndnVqVTlPN2NmVmZCVmNUS29PNERHWG41UGVOZkl1VEFvbUFrSVRMNEdn?oc=5</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-02-07T04:33:00</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acero, aluminio, minerales críticos y el financiamiento: los temas pendientes del acuerdo comercial </t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPNWRtallwbGJmeTFLcXdUeHlXZzVNdzZ5dVFzSVRIU2lvTGtxX3dKVkVQX1Z4U1RDT0QxQm4zX3RJdTRiVzNUdzJ3Y1dOQms0bmdGMnF4aDVmSlZWT1ZweExCYTNrWE5pQ2wzejBDZi1wQnpHbkkzZzRDTjVSXzRtelJSekk0VkZCeU92X3BCdlV6TFRIMVZEeERuN2F6OUFrZVNQMndZMk9rNjRramtFSktQa3RHaEJkZ3VPeE0zTVZWUlhiUmR0Y0VMNXM2UjJjYm9MaUdTblpoeUhEanJaczF6b0_SAf8BQVVfeXFMTkNVXzJxVDVEakNYX3FSR2pHd1RmY0R1OU9XOVc5SGgwX3dqTExmNFpDQlNmRmJpMHYxWHNWc21LMG5mbFJ4dG50Wk9OR0pfeVRxdnJVOGNTbmpYN0sxUEpPRFU4Y3JaaUgxMVdKODVGa1Q0a0tOcllZOEVaYXFTUzlFNlpIX1VPdF9rMVpBYUg2TVBCSXotWGQ1Z0ozZzNUVnB2VEc3R0NoYlJzLW9xbnBfNWVuNXYxNnUwcnZTM2tJdFU1NjdKNWxRck5LNVVPUnBES1MtSDR2ZnF3Ylg2cU1rdkM4Qm4wSk5TR01fd2M4ekNybEh3ZjhURmJtcjg0?oc=5</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-02-06T17:41:00</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Acuerdo comercial: Pablo Quirno aseguró que EEUU se comprometió a revisar los aranceles al acero y a</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ambito</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQa0RLSjJObTlkcXJaQXozRjBHWUttWnQzM2ljRmJYclJtQzdPeTdBVzZqQWR0S0treWhIQURDM3ZJdEVzU1h5b0hhaUY3b0NCU3JSbVg2Y1lfeFFhU2RzOUt2aW5yX1ZyM0dYYjBJUFBZQmhoWjBrbTduUU5STUw0UzFyNFhHMFZwU0MzOU9feHFjNDhQTHJ4Tmk4ME5nUk92OU5OTE93S0ludXA4clNRdFMyMzdEazRfbU13d1hwMW1UaF9OUW9CRnBuYWh0VGd3WjNmb09sR3VoTWZQb2xjTW9B0gHnAUFVX3lxTE94aVhaTkJUQ0U5RDlCRHk5QVc3UWM0OWs2VjM5X3ZiNVVWT1JOekhITUpDWlc4YWRPS0dyS3FmTVFGZEQxdUJMMnA0RUwyUFAxRFE2T25WT3J5c0JwM1V3aVhtWE41QlQwZVNwWG1rUEJKY3Z0RXFsenUxTzdaXzVYMGZIV1BSSzhwaDZjMjVMRGRaS0lHbXp0anpUd2RIYzl2aGtwem82YlNFaUdQZXVCTzRTOEItMnhwY25CbmlYN2NFa1BaeEhoaHU4Rlh4eXAtOVRGY3VuUXhTVUw3aS03LTcyTnQxZw?oc=5</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-02-06T17:30:00</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Carne, autopartes, acero, aluminio y otros puntos clave: cuáles son las definiciones que vendrán sob</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQZXkweUpZSGZ4YzZ4VmJuaGtuMnFQWWpPSzZFc21pSjNJWXdldkpLRUxPQmdUOVF3MzJDXzVwck1TZGZCbE1CNVFtcDdUOHc3S3MzUGhkQTJFWTlsMjNBSEdJcnFfUFJKMm44MmRqT3RScnFUR3pmY3BPOC00Q0tzYXptc2p3bFkxQWhvdTM5LWN2ck01ekpkR2tUZ2QxSWlnSHVuekNxZDM2czA2Q2VhaTRUc3hnVXJXM3dVVF9UZjM2aGJDVjNFSXVTaUJkZEdEWkJPSHFYOGhqSnRHSlQzN0kyUUFDQ2h1cUdsZmJSUlp2bE1pemhZ0gGSAkFVX3lxTE9FT2k4S0dVdDJKNWxGSkZIb3VBYU5fMWY0b2VhSWM1QjF5T2RmSlJkM1hUSWhoYnVLWWhXeVN3TXpkeEZqY1BPWjNjSkFiRFR0SlpQQkFrVDd5VEhQUzk5bEYzMC1POHZ5ajhoaE1BZ3BiSlFlYWpMeGtWckcwNlh1eVJIbVNOLVYydEhORFZzUnFpcmN5eVE4cG9RTHFwSjlSS1djaE1qNVN3dFh3UEZiSlpudFlJTXMzV2lINUlIWmZiWXo1WlNUY2VJSllyMGxyRzgyUV9BeUdlcW43RUZQTUFvZWl1ZTdpNzV1YVA2aHNGN3FBWVg5TUk2UzRTcURZYmlxX0Y3UTRZUVZ6U0l6cnc?oc=5</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-02-06T17:26:58</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Diálogo y cooperación, fortaleza de relación entre México y Estados Unidos - El Diario de Sonora</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>El Diario de Sonora</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQNTBILXVLc2NmOXNENms1NEowS2lfeVNRc1JYd1dUX0hLcVhSV183dnJzWWh5SW9MeF91Z25kMno3LW0wQ1ltVllZTWNJblFNbjFfQ3hrX0wtMHBaaXBzSkFrR3diTGdYX2pCeGV1ZzVYNEFkLXVoY216WFNwU0R1NDlSSk5WRnQzenlXb1owVlluUnlRZzhOVE5KQVlYZnFPWl9FUVdYZFcwR3NxTjNjOE1hWEZFWUU?oc=5</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-06T01:00:44</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Argentina firma acuerdo de comercio e inversión con EE.UU. - DW.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DW.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV3NNdWcwQk1RMjFGMnkzUmVXbld4N29wX2N1d0ZBakdzNHBsWDV1NnVhY1ZOVHpEV0J2SzNQQURjdmRQaDhabkRXcTRxSjltcjQ3amJHQzZGSFBLVFRwRVoyLXFRQkpja2hZQS1XLV8wbmxoRlJ4UWxQRmMyTVpOcXNWOEhwYnpCdWc0NXFqUnJOOXhPS0owSkpB0gGaAUFVX3lxTE13NFZoWVpEYWdseWJOcUgtY1BoTkpqR0RIclNhaHpnUVp6dkdxdUZBcDFIM01CLTEydnhJVzd6MVpWUGNieGxOUXgyRm9tRGVWdnNuM3h5TnQ5YTlfWDJBRU5NR1NKQmlSWXJIQWZ6Q3hhQU9ZeWg0dWd1WEx1TG5mb1VzLTBGeDFwdmlzMVlBaVk5d0tlQS1YTGc?oc=5</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-06T00:26:00</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Reliquia del protomártir San Felipe de Jesús estrena lugar especial en la Catedral de la Ciudad de M</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ACI Prensa</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeEUxUlVBbHMwclBWa0VOSlF4S2J1RVR1TGpxMEExeE1ZM3JxTnRaSkpaeUVlUzBVODdqYzVLeUtKZzhNcTNUMUZTaDJPN2ZtWXZFYUh4aWpXaDc1UnUyLXg5V3BvSGNUTW53QnFOLXQzWGpyeHJjYngxLVFBTHVyTFA2dGJ1OFhPN3Y5RGMtM1F3MXhfVXBtaXE3Zm5QalA1ZzNqZzNZTXVXVnNGczBxTURhbXdOT1A4bjdZNG1nTVZMZ0lG0gHKAUFVX3lxTE9KQy1UVFJNMVpwMFhrMGpXLXllRjladDlWT0hiZXRqRDdoZHIxNkRwSlRlNkcySEg5OXFpcjliTl9ZNHRWd1h3c2ZNQ1NOOHMwc0Jkb0FxMGZFMzNnOVFjWTlxQmF5T1RfbkxtX1VSdVpEV0RpLUtLb3BEZFdFOVBYaDZQODFHLVlrbVlkUWl5YW8tMjk4ZV8wTE8wdkFHTFVIYmFTb1o1UTZ0VHhKXzF6Rnlnd3JRUUl3MUU0MmVyQzZmdkpWUS1sQ3c?oc=5</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-06T00:00:00</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>El día después del acuerdo comercial con Estados Unidos: dólar estable y rebote la Bolsa porteña</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>La Nacion</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/economia/el-dia-despues-del-acuerdo-comercial-con-estados-unidos-dolar-estable-y-rebote-la-bolsa-portena-nid06022026/</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>-0.3200000000000001</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>-0.9600000000000002</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-0.6400000000000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-05T19:01:53</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>El dinero que usas todos los días cambiará en 2026: así serán las nuevas monedas de 10 pesos en Méxi</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Xataka México</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQekdzejQ4OGZXTFhiYWtWVUFZeTk5eXJaNjhBUTZHX0hxSHZYM1hKVXFRX0MxUEJ1dXYzQWgzSndpVFYxTFpRNDBLbHdLWnVXeVY5X3l0Tk9ZTC01bjl6UFNaZDBIOHZrODR0dlpzd2lWUUNzWE1IdFhPOHFHSnhCOGtiVUtrLWF6RUhWRUEyemU5MzZuQVNzSGtBbi1wb3VUVXlKbWxXMTYyZDhLSmVqc2h0WDUwQdIBuwFBVV95cUxNRE5Gc29RQlBCZkExenE5MTREYWRjWlEzWndsYXNJb1dhRVE0WEdzbzByeWpubExzZGlmOUxVZUxrb0x1cDRZaklLX19meVhrVWh6RW0zUzFYeHpUYWNhWWx3XzJ3RzA5OXVlRWZKM0JUVTdtM1ZzYktCc3ByaXAyYmVnd3ZYckhiSlVkSURybWowVzloTmxIU2dzM3hpc3dLY0ZyQmZfVWV6MVJKOUcyajdiUXVwNVFYTVdz?oc=5</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-02-05T18:36:00</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Choque entre tráiler y auto particular deja dos muertos en la carretera México-Texcoco - La Jornada</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>La Jornada</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQOVl2VjVIU3NIVWVCblRVdGFwclBXZExXeEJrcWYyc3EtbHpSR1NKQUNDYUFpNzdUSkV2Um5nVHFFNFVUR25WdDFHZno0YXYtVjJpeVB3LUdsVmNjLXhQTnB2UGUxZDZhSUhxMFNrS3ZVbFFtQVpScFhVb3ByT25aQnNhcjZTd1BRa1ppUVNtM3NaV2ZJQjZ6eEhubk96eHYtQ3ZSTDFoSU1ZV242QzJPZ1pRZy1rSFVhQWJtV21vUFRDVWduLUJwbWoxQ3FESHRFXzk0UUJB?oc=5</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-02-05T17:07:00</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>México ante el injerencismo de Estados Unidos en Cuba - Cambio de Michoacán</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cambio de Michoacán</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQS1AyRzFaejdCbXlISHQyR3NwbURiTXQzNmowWjY0ekFJb0RTaUZONWhrUW1MTWpZSU1FM3FPWFlVdzNZY3ZFZW9BUDdIYmVlVGY2X3kwUG9FZ19rLWFSTW9lRjlxZ3BiSzgzT0xZVGtZam1LNlZ0eWU3S19LSlZxTzRja0x5Z1VMcWo1QlJhUHgxZ2JVN2tMOGhXb3MxV2fSAacBQVVfeXFMT0hwTklVSXhVZFZRaEp6TXM1VHdGdll5a0xwWm84cEVDYmg5b0xEYWhOUkd5WWcxcVZFLXliS2VMUF94YW1nSXlSZ3hicHNpV3JiN3JSd3BzLXM0NjJJS3ptZHFhM2xZRzNRcTFucllqTVJWNThOTDRjdHRIdHhPNEkzQWM4cmlmNHNLbnpvZ1d5LWZUaURPeVNiRW9PRDU3ZUhRUmxydm8?oc=5</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-02-04T00:00:00</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Paolo Rocca sienta su postura sobre la licitación para el gasoducto de Vaca Muerta</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>La Nacion</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/politica/paolo-rocca-sienta-su-posicion-sobre-la-licitacion-de-tubos-para-el-gasoducto-de-vaca-muerta-nid04022026/</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.1200000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.08000000000000007</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-02-03T00:00:00</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Cuatro décadas de BASE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>El Financiero</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.elfinanciero.com.mx/opinion/de-jefes/2026/02/03/cuatro-decadas-de-base/</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-02T00:00:00</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Mercados: caen bonos y acciones en el inicio de febrero, y rebota ligeramente el dólar</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>La Nacion</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/economia/dolar/mercados-caen-bonos-y-acciones-en-el-inicio-de-febrero-y-rebota-ligeramente-el-dolar-nid02022026/</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.9239999999999999</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>-1.6632</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-2.2176</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-1.1088</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-2.771999999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-28T00:00:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Acereros y gobierno empujan blindaje de la región T-MEC rumbo a la revisión del tratado</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Milenio</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.milenio.com/negocios/acereros-gobierno-empujan-blindaje-revision-t-mec</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-26T00:00:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Techint evalúa presentar un recurso antidumping contra la llegada de tubos de la India</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>La Nacion</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/economia/techint-evalua-presentar-un-recurso-antidumping-contra-la-llegada-de-tubos-de-la-india-nid26012026/</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.6400000000000001</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>-6.400000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-9.600000000000001</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.200000000000001</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-3.200000000000001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-23T00:00:00</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tecnológica uruguaya Arkano sella alianza con brasileña Math Group y acelera expansión en el país no</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Diario EL PAIS Uruguay</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.elpais.com.uy/el-empresario/tecnologica-uruguaya-arkano-sella-alianza-con-brasilena-math-group-y-acelera-expansion-en-el-pais-norteno</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-15T00:00:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>ONU exige saber el paradero de activistas mexicanos desaparecidos hace 3 años</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Aristeguinoticias.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://aristeguinoticias.com/150126/mexico/onu-exige-saber-el-paradero-de-activistas-mexicanos-desaparecidos-hace-3-anos/</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-15T00:00:00</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ternium adquirió Tubos Argentinos por US$24 millones y suma capacidad</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>La Nacion</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.lanacion.com.ar/economia/negocios/ternium-adquirio-tubos-argentinos-por-us24-millones-y-suma-capacidad-nid15012026/</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CAP vende filial Tubos Argentinos a mayor grupo acerero de ese país</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Latercera.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.latercera.com/pulso/noticia/cap-vende-filial-tubos-argentinos-a-mayor-grupo-acerero-de-ese-pais/</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Grupo CAP vende acerera en Argentina en US$ 24,4 millones y sale del mercado trasandino</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Www.df.cl</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.df.cl/empresas/industria/grupo-cap-vende-acerera-en-argentina-y-sale-de-ese-mercado-para-enfocarse</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/Output/reporte_REAL.xlsx
+++ b/Output/reporte_REAL.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-12T09:51:45.540427</t>
+          <t>2026-02-12T10:10:22.868807</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.165494736842105</v>
+        <v>-1.042687719298246</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.74899298245614</v>
+        <v>-1.55601052631579</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5585298245614037</v>
+        <v>0.435722807017544</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6666140350877193</v>
+        <v>-0.6139824561403509</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.394442105263158</v>
+        <v>-1.236547368421053</v>
       </c>
     </row>
   </sheetData>
@@ -1911,22 +1911,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09T09:59:16</t>
+          <t>2026-02-09T14:01:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tubos Reunidos registra unas pérdidas de 71,3 millones de euros por los aranceles estadounidenses al</t>
+          <t>El Chevrolet Onix 2026 baja de precio en México: más interesante que Aveo y ahora más barato - Motor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>Motorpasión México</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxQWGd2c3B3X3ZadU9tMnp3cWFWSmMySUdMT3ZKTUIxQXRnMmpfWFZfZ3MySlZaNUJJZHhhck01TFVQX3ZMelhNc1ZNQUFsYXVaODVkM0U5aUpzU0V1S01lcFgySDhzNkotUl83OFZVd2ZMd1dRcm9fclZXYVF0VVh0eUdkQ3hmQVhlaXkyQ25fNkxzRFB5d2tvWC13MEZhLVhYZjFjNlZZR3dhZmhQY1YyelQ0Q3JVRmxUUFpsRTRJR3RyS0pURXlaYUREM0ctajFwSkZxUHFITEY1VEwtbEJUbmxxNjVHM0pzNG5iQ1ctYW9RWkFRb29adg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8zS0lrcFRsSkhCNmpodzZJU25nc3llWGx2d1J2ejNpMXVEQzBJUjZVX25STUg4WGxXNGRSZXVGTHR2WmJKUTREMUl2eEVzdnRFcmJLTUx1MFQ5X2FnOVBQV2JLQzBadGt4WDQ4blJfaUYzaTJicVN5aUpZdnQ2YknSAYQBQVVfeXFMTW53d3kyVG10MjNkVnkxUGJPaU42VzFvdzlpU1I3OEFuR0o4WHQzaVhkSU9HckJ3RFB4X0NZR2ZNR3k5VUFOd2wyQmxFS2txZUpYNTdyMzVtczhoWXdGbGo5UUlwMTFYNUJwR0ktR2J6YnM0bnh0bE56SndZeEJSVGpwc0JF?oc=5</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1938,16 +1938,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="H33" t="n">
-        <v>-15</v>
+        <v>-4</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="J33" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="34">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Argentina firma acuerdo de comercio e inversión con EE.UU. - DW.com</t>
+          <t>Argentina firma acuerdo de comercio e inversión con EE.UU. - dw.com</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DW.com</t>
+          <t>dw.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">

--- a/Output/reporte_REAL.xlsx
+++ b/Output/reporte_REAL.xlsx
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.05</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-12T10:10:22.868807</t>
+          <t>2026-02-17T11:52:24.794483</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.042687719298246</v>
+        <v>-0.6715306122448979</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.55601052631579</v>
+        <v>-1.021224489795919</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.435722807017544</v>
+        <v>0.433265306122449</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.6139824561403509</v>
+        <v>-0.3092857142857144</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.236547368421053</v>
+        <v>-0.8225510204081631</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,26 +609,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-12T15:11:01</t>
+          <t>2026-02-17T07:36:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>México pide a EU revisar aranceles a acero, aluminio y sector automotriz: Ebrard - Tiempo La Noticia</t>
+          <t>El nuevo Plan de Inversión en Infraestructura para el Desarrollo - El Financiero</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tiempo La Noticia Digital</t>
+          <t>El Financiero</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNajFrU3ZnYTV0NE4yd1ZBLWNidEExT2JicmdjVWhWaWJRU1Q5TWUzT3MxVW5rWjE3bFo0YjVUTy1UUDdtN3NtbHdxSng5RHNTMy1uSTZPSklxeHRMNzhxQ2NkUWNQWFpnVWg5OEQ0TktlbDBSNTJpb2JIczEwSjUtRXhBUm1lTkJWVXVtbWNaSDlfQzJkbWlraVFsQ3dUWE5IVk9IU0xfRVhKZjVjalV3dg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNTm5hR1pVWG1YLUFWd1NRdmJFd1BLWS00OTBHdFhkSmRMUktvUWwzQjdQOFBpUzVtWmktLW03RnpFTWxXVThBc3haWWtSNUpYRmZHaWI3S3VaSVVjOTd5R1FHSXMwalJjanVOOXZIZzV5S2RnWVBac0VwNHZnXzFOaEVGOEFXLU1jN3JaWnVPWVlGSi04R1kwclhDSVBGdGlaTW4zeGhUQ1hZRUcyM3ktMFRGOWJzWjVJUDhwZzVCQXlsR1o5QnVoa2h0MjI3ZnJjSzFz?oc=5</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>-0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -636,37 +636,37 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-3.4</v>
+        <v>0.78</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.7</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-12T14:07:00</t>
+          <t>2026-02-17T05:01:03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ternium toma el control de Usiminas tras comprar la participación de Nippon en Brasil - La Nación</t>
+          <t>Una publicación unifica la terminología sobre economía circular - Residuos Profesional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La Nación</t>
+          <t>Residuos Profesional</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOd2s0M1NwcVpIQVdGNDhEdXQ2RzR4Wkc0VHFkcTZCZmxoNl84NkVqYWpXdURHOWlObmRuLWxnRWljU3BzdmtXX3dqS283dDJqQ3JMeU1nU2ROOXpERTFoWHgzQ09aM0hyRkV5NjJYU1ZybHNmbkRya1ZoX0V2czk4YXUta3FkSzlURjA1blpvME16N1JVclY4V0d2d3RsMVRVSWcteE5fLVp3OWpsM29Ra2xndnA3emFpeGI5TnoxTDczZ0psYlpBaWxSQUdzVHc5Q1I0YVF2RjRCWDVS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPRVg4YmFpNDNDemhNZUN6V0VkYjBhQTh6b1dnaTB0UHVIMUxPRFNpaXRPeV9sWWo0YjlkTWJYQlJJMk90UF8zcVY5aFpVc25pSjJUNFJlWTZBU0xCRWd4QXVTSTJKbXNGSkZSVTFhTlZlU091bXZ0ZGc5OXJTQ3FOeF90NFlZOWVIRnJPNC1mLVA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -693,26 +693,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-12T13:56:03</t>
+          <t>2026-02-17T03:47:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ternium toma el control de una acerera de Brasil - Ejes</t>
+          <t xml:space="preserve">México y Canadá perfilan plan de acción económico; incluye minerales, inversiones e infraestructura </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ejes</t>
+          <t>Contralínea</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQVUxyZk9HTE4wQXhYeEV6dUpoamlSM3FpWkFMNVB6VHNINW9KbTFiOVNMejZtLUVnX2duek04MllENHpYUmRYWEp3R245Qk5kYjdZTGRYUWNnMWpabmJtR3NBUFJtaWM0MDFBLUxNeW1XcDhwd2hLVzRiT1VMamgyeW1hWk5FVUhyR1RranNadzNGQlpJR3BqWS1WMzM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYTFkSHN4SXBxX1J4TkZ5WXNJY3Z0YURYTFpVb19URmhpakx1a25kQkxRV1Y0MHVJS3NqbzQtNE14SXB1RUVOM3dBZU0tbm9GUW1tQ2VoWVRtcHp6Z2w1UTRDTkM4am9KZ1JYamNOVGZUVjZCMUVmcEljNjdkNTlhczh3NW80MGh5c1RGWmVteWJ2eTlxQjhiOG8zYlBrdFRWQVRwZjB6a1dBSXNHeE1kOUpTZWJEYjZaajdkSHZBeTRhTlpqVE5venBHR3poZm42Wng2V0EyUQ?oc=5</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -720,41 +720,41 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-12T12:15:18</t>
+          <t>2026-02-17T01:57:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>China y México mantienen conversaciones en medio de tensiones comerciales por aranceles - El Economi</t>
+          <t>CFE e ICA supervisan infraestructura eléctrica del Estadio Ciudad de México para el Mundial 2026 - M</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>El Economista</t>
+          <t>MVS Noticias</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOT0lpWWt2MXo2Ym1fbHdrVEF6V2loR25WSkZkLXVuTHNtOUp5dW41bWZ0a2V3dFAyY25ONmhGMHlrT1JMRE1fWmNIS0hRSXAwM1dUa3UwblBNR0dySkktRmpKdF9aTVFoZXpVbFF4MlEtRmwzSTd2Yzc1OWxUNXBYUFJ6empNLTY3NlFKZFVmcXhwX2ptWUdZZmZIOTNPbm02a2RENmpUb0h3LTFIbEtBeERzWGFxZlBPLVdsOUQyaXlIZ1Utekl5UUFsWndXdHJwUGlJ0gHYAUFVX3lxTE1aZVMxYU9VdjdqUzMzUW9aVEdMVWN4elpjX013R1RkQ0VDb2V3WjRyMEx4VFhYRjRDUTlVb29XVFBxNkxtRGZJZ0hpV2V5LXVuOGRadE5NSHRPRGdkRzJaVUN2bjNkUEpnbHdVUnVXN3FfQlhtZGhheDFUTHdNdE81aXdNZEozYTdKampaajJNZWdtc1RnTUx0Tmw5UWY4ME5iRHROLXJhLTZoSVFiUUl1TzdZTDd4T3E2WHZLSjNKWkZkdG5NcGdmWmpGNkxhR2RtQndUck1iVg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQTlVOWVc2MnpCOW45ZFhwVTRMbFZ0MlZkbGxTM3Z3NmJlQl9TcmE4ZzhpY3dJR0dBVmtzdFI0S3FyVTN3NktRN1M5bGZuV21qUkZrVl9pSjJkSnRNcmY4X0VFUTJOUlVtWFNCajY4VUgyeUVVVm82cFM1c3JtVjFGcFRkaEd6SG9rTjdtd3FGZ2N1aFpmeUNZcVBhbkhKZDVlNG5pQWUtaFVrVzdPMTRtY0F1blhGNEs5MFhyY0xyU0xyeHNQSUpzTHBjSzBPUDNELS1wLV9jNEZmb0lNVkhmRXF4a9IB4wFBVV95cUxQTlVOWVc2MnpCOW45ZFhwVTRMbFZ0MlZkbGxTM3Z3NmJlQl9TcmE4ZzhpY3dJR0dBVmtzdFI0S3FyVTN3NktRN1M5bGZuV21qUkZrVl9pSjJkSnRNcmY4X0VFUTJOUlVtWFNCajY4VUgyeUVVVm82cFM1c3JtVjFGcFRkaEd6SG9rTjdtd3FGZ2N1aFpmeUNZcVBhbkhKZDVlNG5pQWUtaFVrVzdPMTRtY0F1blhGNEs5MFhyY0xyU0xyeHNQSUpzTHBjSzBPUDNELS1wLV9jNEZmb0lNVkhmRXF4aw?oc=5</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -762,125 +762,125 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-3.4</v>
+        <v>0.78</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-12T11:16:54</t>
+          <t>2026-02-17T01:24:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CEO de Thyssenkrupp: Aranceles mejoran panorama del acero y negociaciones con Jindal - Investing.com</t>
+          <t>La CFE supervisa infraestructura eléctrica del Estadio Ciudad de México para el Mundial 2026 - Infob</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Investing.com México - Finanzas, Bolsa y Forex</t>
+          <t>Infobae</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxQNXhjRHJNNzRkSHN2eTNWcGdaX1FCYzRLNGtvQkx2Si1fcjB3X2sxS1dYWnhpUWtZdnU4SmlwR01ZVklSUGdQOHg3Y0RzanFSUWgza25VSmNwaERiOWdJbk11c0NjMnJ2X2NiaFJwam9KVEoyTHNTNTl2Y1lvZFhHZkhQMmJiLUdJcWc4RDAxamVmcmJWSHBVN3F1MlBnS0hWYWJ3TlpwTFRTcWRwYXoyZExGVjZITjhsTnVxeEh1YVF3TnlJd0l0WWFsT1ZGZkdQTXhoZzB6MnRobnNO?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNVVFNY0NHcFBNQXo1dGVwNEdIY3RWNGM5T3JPQnNORU9idUQxRmY5cHdtMm04eG1sWUJoUi1aZHNiU1dtNGx1OEM2bzBwNFNxa1Nuc1J2am95RDRVejBNTHBXMkpvWjNnSWhVNlhmOTZwalNUbURoc2NONjZzSTN4ZTU4eUQzcDRzQWtxOGJxX0lpWEJ5MkFqWWxURjN6Nkd6MGlxQnJjVWtkcWFsdzVXZ0tManZVSTM1RDNjVkkxYUVvbVMwYXdlNVJnQU05QlR60gHrAUFVX3lxTE9oaDBJVElWTHAxS2ViN2xMbHpmb1QzN3ZsNjZ2Q3o2R2pfa19MMzhEYV8xMVB1M3dudGxmbjI5TnViTElrbzMtbzAwbDNyVVU3dE9FTzZ3NkF5WWhvNUxqem1mN0E4d2ZMQlZ2VUNTZElJUF95N3BLR2NFT0tCeWRQclMyZngzNllIYlJBdEQ5cFNSemNXbGloNVhOcmZ2SVczVlBrcUVKd2pPa3ZTQmFQNmVvREJVSWVEckhXaGJhcVB3LU5WVkk0UUJ0M3VITDJBWFpwcU9vdlpsb0lKOWRFdC1DNEFEb2NaSjg?oc=5</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-6.6</v>
+        <v>0.78</v>
       </c>
       <c r="H6" t="n">
-        <v>-9.899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>0.52</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.3</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-12T11:15:00</t>
+          <t>2026-02-16T22:03:44</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director ejecutivo de Thyssenkrupp: Aranceles impulsan la confianza en el acero y negociaciones con </t>
+          <t>Confirman una inversión de u$s 7000 millones para el desarrollo de megaproyecto minero - El Cronista</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Investing.com Español</t>
+          <t>El Cronista</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxONkdtb3FEbmNsUmZWVEdHdFBJazNWQ0R1bTFzek9uOVJBSkR3cVFRTTRJTFA2VERoYV9KYXBuWm9hdWdHc2RpV3E0U0ZfdWswYzMxelBlVjlwUUFZdGszTFNocGY5c1hlcDY4ZnR2Q284cnM1WjBGaG40WldhcmZTYmJ0MjNyVFVzRzhJZzNuaWVDYzkwVHhQeDk2Zk9pbHVaVlNQLW5TcHF0cGxfTGg3WDlaS1dPZ1NUa0lBV0dTV1ZybEhaMUwtcC1rbDM2X0lWOEkwTGxSTXVvbmxtQkktMnZVLWZfa3Z0a1BLUWdaM3l1X25GNU9Ua2hR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaF9zMlBqQUVxeGNXSEZUSnZTWjAxbFB6YUtRcWlmaTRfUk1vQWg0cFJ4ejlzbnE3SW9pSGFqM1BkS3RTZ3VocW9oMHBPaGJFYW1FOUM1MnR6V1pzWlpHMU1xVXRIblN2MEw4UVNOanhNVm5tZHJydXE0R2tKSTduVldGOUVLY3VJSGtvM2J4eTFqSGxDWG8yQkk1aU00elRDWlpaQk11bGQ2WVM5WnBLbWNFTkRJZHUtUFZ3WU8xM01qRW03bExFMUVfcDVBZzBIZEVBaXNfONIB1wFBVV95cUxOaF9zMlBqQUVxeGNXSEZUSnZTWjAxbFB6YUtRcWlmaTRfUk1vQWg0cFJ4ejlzbnE3SW9pSGFqM1BkS3RTZ3VocW9oMHBPaGJFYW1FOUM1MnR6V1pzWlpHMU1xVXRIblN2MEw4UVNOanhNVm5tZHJydXE0R2tKSTduVldGOUVLY3VJSGtvM2J4eTFqSGxDWG8yQkk1aU00elRDWlpaQk11bGQ2WVM5WnBLbWNFTkRJZHUtUFZ3WU8xM01qRW03bExFMUVfcDVBZzBIZEVBaXNfOA?oc=5</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.6599999999999999</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-6.6</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>-9.899999999999999</v>
+        <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>-0</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.3</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-12T03:55:00</t>
+          <t>2026-02-16T21:56:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arcelormittal fuerza la subida de sus precios objetivo a lomos del escudo arancelario - TradingView</t>
+          <t>Ebrard anuncia plan México-Canadá en minería e infraestructura - La Silla Rota</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TradingView</t>
+          <t>La Silla Rota</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE96QmZVdjBPNDY1RXBtUUwxVDNKaktlODdpcXhhS043UHJZcFdIZDY4M1JmSHZuczR1ZFBSOUF0Q3R2MGprLVpkU3FJdDVRUGxrRFFFN0FwaDFuUnhpRU5IbnhlR09KWHNI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNOFMxYjBoenZWX00yVzNScWtNSUtWdTd2d2xYSVVNVkM2emFQOVF3QWNVX3E2VVIyTlNZWHBCWXZhcjEybWxRdWktbzdCaDlmT1UycElLUWxvOHNIdm9hLThEWGYzaVZMUkc0cVFqaWN5SG9rY1RieEpxcVNWSFVROF9mQUg2WFA5cll0LTR3THo5UFlndmxua2s3aUFlS1liOEx5WjZjRzZ3bGQzTlN4VS1FekFSUdIBtgFBVV95cUxNOFMxYjBoenZWX00yVzNScWtNSUtWdTd2d2xYSVVNVkM2emFQOVF3QWNVX3E2VVIyTlNZWHBCWXZhcjEybWxRdWktbzdCaDlmT1UycElLUWxvOHNIdm9hLThEWGYzaVZMUkc0cVFqaWN5SG9rY1RieEpxcVNWSFVROF9mQUg2WFA5cll0LTR3THo5UFlndmxua2s3aUFlS1liOEx5WjZjRzZ3bGQzTlN4VS1FekFSUQ?oc=5</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>-0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -888,41 +888,41 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>-3.4</v>
+        <v>0.78</v>
       </c>
       <c r="H8" t="n">
-        <v>-5.100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-12T00:30:00</t>
+          <t>2026-02-16T20:59:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hay una grave persecución sindical y laboral en Coahuila: Mejía Berdeja - Sociedad Noticias</t>
+          <t xml:space="preserve">Sector electromecánico en México busca certificarse ante expansión de inversión • Infraestructura - </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sociedad Noticias</t>
+          <t>Forbes México</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNRllJNURiZ0ZraXU5Ny0xc05WX3NJLUowT1U0NlQ3MERpeF9JU1gxZ21FTktVMEV3MGlKdmdvYndtdG9zZDdKRndJUi1fckFNRUx5aHJPOFQ5R0hFM0lKZ1RtLWJnZE0xc2tVb3FaYkwxaGMyZGZ5WW9VVm9RMjlta3UyLUh4R1RBdl85dlJFb2JyRmVaVDEydHpCZXBtR3JNQlNsYUlvVkhoUDdfamRLUmVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZ2xDZWlKWWJZQmxhQkpnVGFEcnMwMWdaX2JhZkNaNlJBUEF0cmNMTkxsQTBjQ3N5YU5WSFkyS2pOTGZZS0kzN05oNlNLTGt0WVN5TWNnZFE4dE9jbDJYRkY2U2diT1ROVnF1NUcyb1h5WW03Y1ZSejFuRU9TcEkzRHlSQ25EUVAyZEkwRUZoNl9DNHZkalFaU1VtenZpeU5LaTNzaQ?oc=5</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -930,79 +930,79 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H9" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-12T00:20:12</t>
+          <t>2026-02-16T20:57:25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Exige PT se Liquiden a extrabajadores de Altos Hornos de México Tras la Quiebra de la Empresa - Tecn</t>
+          <t>México inicia investigación antidumping contra acero de EU, China y Malasia - EL CEO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tecnoempresa</t>
+          <t>EL CEO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxNUHJkdFFiaDBiLVlPOV9CczZlLWFIWFFVbGJOd2UycWNqeU5wdVNtazNGMTJDbVZPdm1qQmt5VlFUYXV6S2ItZ0tSYnZNNE1pOEhKa2pvWXFKaG5tb2ZWaFBjTWZfUlpVZm9mNFZPZGJ6Y0tFRVY2NklSTlRJWkV6UkF4cVBaR0prRXNIQTNfSzVsUW9RbHRGMjNOYmZudEMxUnVqQ0dDTGtQenpxRWlENHFqcjFidWc1ZEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQb2ZfazlCdERaTXB1SHF3Wm1lQ1BpRE96MFVZZ1liaEtyM0dsY2ljaERobDFpU0RHWlBpMVA3NWxTREhVQ21fNVVGdWV6T09qMkUtUVFHY1VYZHhOZldwSUgyTDJBVk5CemNZM0VLNXNMaVBSOVlwZUdyR3UzZDAtWHhiTmxHek9lNWN6aURsQTR6aEhISUd3bGJlU0ZLaDRJMHR2eA?oc=5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>-4</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-2</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>-5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-11T23:16:00</t>
+          <t>2026-02-16T17:15:03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Inversionistas buscan adquirir AHMSA en Monclova: subasta el 27 de febrero - Periódico La Voz</t>
+          <t>Chile: AZA eleva producción de acero verde y reciclaje de chatarra tras inversión histórica - BNamer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Periódico La Voz</t>
+          <t>BNamericas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNOUxFNHBERUNtdTdISXpQaE1wd1pQT2dpdk50cnBMN25fSnlvSDh6S012SVpNbEhqTzRDR0VOd3FvVG5OWEVONUJUZnUyaFh5aTE2VWU0REV0XzR1VDVIUjBzeW9qN0N2SEItRmEyS3M2LUt0eUtFT2wySGtSRGZrV2FHTlBicDc3Q2YwcE9nZWh3VERZZzNzOU52RmVFb1l4RHhfWlZ30gGrAUFVX3lxTE9YTFZZcGFEUHZsbXIxaHpPci1KTzJDbUU1NUwxc0VMR1p5aV9rdHFFRU5rcXVmU3B5MnhwVkFlbkFuWERTbUVBeUs0azN3Z1l3Qi0xX3RnTnIwWV9TcTJZWVFDWDFzMkJXNWp3VWRwbjdNNThBdmpGSERIUm55c0xlTFd4LXBkZzhGdGFlRklyRnFKOE1lOUhWczJWRjE0azloX2MtakVhNDM0WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPa0w5UGJUSUkzel9DcG5rcE5FSVpIc3ZtRVN1cXA5ZS1vS1ZXMGJYN2sySkxZWkF0cmZJMHZyMG1aNTdNZ3U1bjJSck54dDFMZXVpUGlJMXUzVzQyZ0JQaVlva3EwcjVTZGRqejUyRkFPaF9KNGxhYjk0cXFKcTU5Sk1HS3JLN1FwaF94RWV0RDItNkJnVktiR19ETXl2YzRaZ3FIUS1hT1Q3b0pZTkZUeml0ZUZJal93YlkzWjBLamgyUzBwM1hTa1FEYw?oc=5</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1029,22 +1029,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-11T21:04:44</t>
+          <t>2026-02-16T14:04:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Después de la polémica con la Casa Rosada, Techint concretó una fuerte inversión en Brasil - El Canc</t>
+          <t>México es clave en 10 minerales críticos para EU - La Jornada</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>El Canciller</t>
+          <t>La Jornada</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPQjVYZ0ZLZ0JkbWVmXzQ1OF8wREpoZ1loWGhYY0hnejdhZ0tmUVE0RFA3SDBrd0ZzMG5GbTJya2JDcmFTN3BZQlJMQ0k4MnltZkx1dnMwaE9aclBGUkNhYmZOOTRkQlF2QkFqaVB1Zk91Vy1veVhtb2tlNDdzVXB4UHN1UTl6VFNpZXduM0JCMXpJY0JRUXdGa3k0REk1R1ExNURLcUJ3eGlXOHBobk1TS3VjY1Z0UXljQ0k4SHlia091VWxydk5VU0Z6WGVEdkViWTZBLThkSGwyd0JEMzRuVk4wa9IB8gFBVV95cUxPSHJGQ0pYbjdJN01oNThSRTlzT2tTSXZrTl9RSXZlUUFuUmZBdHRsSmRaWE1TZm5hZlBaVWNsVDY2VXBKZ3RkR1J2SDRMaFhuRkM0T0lDaUwtejM4bXkwNXpwZGlyS05pcjZfNmlqTUo3SW9WMXhfTmZPLXRxQ0xFUzBJS2I0SmFoLW1jSzRlMjhSQzZuME5WejJxcXlIRXhWRld6b2VUZ2NkRVZOWkdqMVVBSlZoaVdGY0ZNWVNNcjdJOV9PSjJLdlRMME56TS1TZVcwSXVONU5YTVdfS2Fnbk0tZnhVRC12LU04NHRIUnpvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNYXpXaGN2em9DVzQ5S2N5Y1dDMlMteGhoUTVPQU9hamlNSTAxaHdub2hfZGQtSXFxMlNuS0laZEk3UUVlYllWYlNWR0hjVEJMU0ViclpKbkpfd19tWDE1MWxNQ3lUS3d2Sk5wQkU3VTRSRzYzVHBuZHdzWXVndERfRlAtdGh3bDV1TjBMc1Vrc3kySTBfZHlYMTd1am9vTGdNRU05QVJn?oc=5</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1071,26 +1071,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-11T20:35:00</t>
+          <t>2026-02-16T06:48:34</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Avanza venta de AHMSA; compiten seis compradores por la siderúrgica - PostaMx</t>
+          <t>Japón evita la recesión técnica pero el PIB incumple expectativas en el cuarto trimestre - Bolsamani</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PostaMx</t>
+          <t>Bolsamania</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxPWHNSM1dUWHNGbkdVTlcwMHdlRVk1bzZWZGZiaVkyOTdpRDNqWHdmb1ljNk1sNjNWVGp0akJLTVRRY3ptZElHcGl5MktlODNCcG5saXhyd2RfZHZ0RzlzNV9MSlR0VlFzSjlNLVh6QTN5Zk5EdG9lNXEzbG93dG1RN295UVFSQVI5TmZaRVdfbWh3WEhRV0hMSGtzbHpyczBlMWVEUzA1THJycXlfX2RZ0gG0AUFVX3lxTE93eXF1V0ZvbWVhRndVaWtqVmtNVkJJbFZhcmhZZUZ6T3NoaGZ1aWhCSzZHX0NGWUFCLTVrWkFEbC12ZnBGb2s0a0x0SU81d0tsUmVITVd1OWNaT0RYZWpiak1pRkYxWG1UTGJpUHZXZ0ZPVWt5U3E1WnZvRmhNcnJNRXVoOFc5b2E4QTBINGc3TzNjX2dvbXU2aFdDajFIb3hIbkdBRjg3VlEzUHJlVzQzeThzZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOUUR0Y0F0X0N2aktwTmkwMHBJVW9jV1RnVDVKa1pvWVJ0bnNsUWVucmpvZEdZYWtPQ2M1SnAwNTAxMEhVYjBUdGk5T3BzSzdXajNYbFo4bEk4cndwMUFLMG9GWVJsT3Mxc0Q3UWJIYkFrNV81Y3JqbGM5ZzkzUGNrWkVwOHNjWTFNVWZRWUg0dmN6NDcxNlBqX3RIU2dLdDRwSGdmZG16Y0lrYzEwZnFNbFRjZHJ1V3U4V083VXFONVV4TkVaVVpFM0JmZ9IB0AFBVV95cUxQNUFnd08zckdfMVVVblRDZlZ0eXZOSkF1dmpOZFNiZC0tUnBENTFkSmtJZV9tbXFKakFHWVIxYmFhbTg4QUJDTk5DazIyY3BGVTVfdVA4bVhuRjF3YS1ORDdxNWp1VjhCM2F6NE1XZ21VWmUtcTh3WnlZNnRPeDFZTE96RktUNWlaVWt0b0dSVDl1SjdSZjBNN0c3b0RaZjNLZkYyVFNGdXdXeFdMai1fRmk5aDNBa0FoU09oc0FWNDE1cVFjNnhxaUllRkRrc1pu?oc=5</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-0.3200000000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1098,83 +1098,83 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>-0.9600000000000002</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>-1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>-0.6400000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-0</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-11T18:54:23</t>
+          <t>2026-02-16T05:01:13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rocca deja atrás la polémica con Milei: invierte US$ 315 millones en un gigante de Brasil y crece en</t>
+          <t>Tras salvar el coche de combustión, la industria pelea para desmontar el mercado de emisiones - info</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Clarin.com</t>
+          <t>infoLibre</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxQZ0R1ZHJoQUN3dC1pMEhDZEYyLWdtcnFUMGd5ZkRQRmRMUEhNVkhJMmNDTnJMYWNIbmNaVktnVl9DOHptQ01mQVgzb3lBY3cwRDlJUE9BV0RRXzctd1NTWGR6T0JGcEMxTENfdVlMMnE3QlFBSW1SM2xnU3VEem5nM0ZwbDdwN3J1UXVqUXNKaFJxYS1FQUg1Y0NqTTZHMmVxc3JyYTIweUt4cWxidmhlakZoYVVWTlpTckdJLXczTVdReUp4OEIyay05VXk2UXEt?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQYUF3LVVZU09lWmlfS0RtSDBNNWV2QUpoQkxkOHRydHhjNGJHa21KUzlxZ0NzMWppeXliZ2p4TG81ZjlaVVV4ZV9FTFpWSjlOZzJ1amVNdHp6RGRxRmIyYWdqbGpPdjkwRXl0dkg5YndOYlJSR3dLSXBVc3ViVmhLY1hISUhaV2pyd04zdDNhRFZqaUhXd3FuOGZtaGFCY01rR3lrVkI4YmROUWZmRHNPeUJObUtxdENORHNTamJxel9TU2s?oc=5</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-11T18:34:00</t>
+          <t>2026-02-16T03:02:40</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Confía Grupo de Defensa Laboral en venta de AHMSA durante subasta - INFO7</t>
+          <t>Sector de la construcción en Querétaro reportó débil actividad en el 2025 - El Economista</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFO7</t>
+          <t>El Economista</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOeDdxV2k1Yy1oa0xqRkRZRjdqYzYzdUlfejVKYVlZdWl3NVRCNVczeFdHYWVRWkdsMUJmUWVidEJleEVNMzhHT1dEMWpiUDFZaGlVcnJIMVZmM0wxeTBzUHFaYjJrVjBtVXl5OG1xd0hqWUtnaWZsZVVxVGJIempXeU42UHZZZ2pYYzlOWlFvQldCRnBWX01NWEhMeU5ndGswaWt0TE9qQmFib1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMmxHYXR4TXdIRzBkVVJIbHQyZ2dhWjVMeFE4YVdmd1RHZ1RnUzRuRmhyQVNBSHVROWdrOFNtSG9VeGFSUG1YSy1BVGVHUkJ3QmJsNUQ0Qmx0S0Vhd3N6SXBmcnh4LUNtS1hwR0RTR3ZWVEYybmx1OEFJLXpMSFowQTY0M0xJbnQtdWtlNEJYRG9uN0R6czdjTFNTTUtZYjB1WEZvTXdJWDNaUHozTEZQTUNMZWzSAboBQVVfeXFMTzNFdnd0Y29yWGpEa0x1UkljMWVvOU81dXZBa0JEN0NjblhzbTJycXpKbnNUMHNvQk5CVGh5eXZFVTlLSHo2OFBkdVlOeVUtWTZ3WDN3RUlFMW5EQUE0S1hrLWRZY3BfeW1EZHNCOHdKejFtU2NWR2xjOXo0TEV5cl9vSWxURWtHdnZ3YnRwTkZtbjIxdUk3aFBZU0tHUTNmRExGZmlBR2lIazdYTmtEZnpVODhvWWtScjlR?oc=5</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1182,79 +1182,79 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J15" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-11T16:55:34</t>
+          <t>2026-02-16T01:19:19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ampliación de convenios entre México y Brasil elevará más de 10% inversiones en ambos en sectores es</t>
+          <t>Cae México en 'trampa' del estancamiento - Reforma</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>diariodetabasco.mx</t>
+          <t>Reforma</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxNTXpOU2RGZkxHdTNTVkF2VWlzVGVzdEdBdDhzLVNEdmxwanJaTVB5UXd1elNRY0hSdkxubS14RWZCOGNwaVhYdTM3Y1pVR0ZVZXphY25SSV83RU1BZFJvS3NxcmJfUGp5U2NYMm00QXlZT3hlTUlBU0NuVnk1U18wd0Ruc21XSWxGVGxQeElWWHJPc3dWNU92ZVVpVHBSU3FYNFZzbzd2RkZpV1MxUGNTRE9xRDdFT0RrV2t0d1ZDTmRyOV9abFlVWUQ3OE9seERwSlRqWUxJVThTbjNERUVONFN3d01XYVRYVDRBZ0JBMFVTbmM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9xREY0MHMwLVh2UUpDcE9MdDUxSEpuWjNRMTAxS2FnUFVZZ0dJcjNSaTQzc0poM01sM0NiaUFIb0NaY2doLXdpTWJEZ01kYXB2MXJHb1FSY2JBYzhac19zOHpzbmRUSzBTYWgzNVVMMlZhWkFCZFh4dDlVVC0?oc=5</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>-3</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>-4</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>-2</v>
       </c>
       <c r="J16" t="n">
-        <v>-0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-11T15:31:31</t>
+          <t>2026-02-15T21:27:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ternium avanza en Brasil y adquiere las acciones de Usiminas - LM Neuquén</t>
+          <t>Los buques rusos Sparta IV y RFS Aleksandr Otrakovsky cruzan el estrecho de Gibraltar bajo vigilanci</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LM Neuquén</t>
+          <t>Europa Sur</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQYnhsb0s2NkI5SGdJWlB0YlhKOFZKME9rdVMyb1luUXVNSTU5S2lwTzhkLXA1UTBpME5pYzE2aHZpNWtJZVVOWUl6U21OQnNCVFZKVkZKbGNpS1hMMVJ3OFNqamN5SzdURjRDd0tLbE11SkhpWTJpbU95ay1fbl9nTHdsTDRlcWYyZ2tmbFFNalROeEFYMWVxUUZ4REN4NktI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTlBMY2lxa3lJaGtxMzRzc1pCOGdudkFiZVpIWDFIc3dDc1FJQXBpaDF2OURYYU1meFBNVHJ2Si1jTzBMQmRsTl9lUzEzU2Z4cnhHdU1lWWlWdkNNRU9PdkdFa1h0MEdGdkRrZGhnWUJHUHduRzdVUXBXd1lqVzNiUUFkblNGNGtNSEpiWTJ2NkNuOXktN1ptbTY4QUtmeS0taExVZWtIY0plUHJwMGJublpzS3NoYjlxMFN1NzhLVmfSAcYBQVVfeXFMT1BzTnRLWXRuaHNoTlA3STJNTkp6MWNpOFluUE11MFBmZjkzVVZqcWswSEpTcUJIZ3RLR25GZmE5Snd3RFFUQ0dzdWtUVzdnYkczMGtlUXNUcmFkNy1ob0lGZFdCWGNzRkZNQjA0bEp4NURBQ01HejY4VjI4bllZSmtNV0xfcUhEV2Jud0ZfX3luVUZUYVdWWmszUEt6aWQtamp2V003RWtueUdScVdKVmpnN1JISVBySFEtUTdzekFGSFpsbWln?oc=5</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1281,22 +1281,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-11T15:27:32</t>
+          <t>2026-02-15T20:09:26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tras el cruce con el Gobierno, Techint se quedó con más del 70% de una de las principales siderúrgic</t>
+          <t>Bancos que respaldan el acero ecológico aportan “soluciones falsas”, según un informe - bloomberglin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>bloomberglinea.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQeE1CTFdCc0s5c0trM05EVFYzSGl0aE5sZDlwcG5lZzY0bE4teXRCYkREamQxdl9McHd5eGNIeEZ3VmV4NTJtZjhfblRGaC1ncGFFcFhmWnVtSF91Q2RJZVpqS3I3ajIxUE5OLTdJbm52QTR0N1NBLVNYTHBkWFA4UXZvaDczN0pROHFqS0tMUGs0MjVQQk52THgtWDhGd1lHNGZwcXBMaU9OM2p5TDl5TXJmdDFWWXhOS29wTzNVVFI1U0JZRXloM0hzSVdBMl9DQ0ZOX3JsSTM2ZGdKMlHSAfgBQVVfeXFMUGloMVU0Um9kdVlJa2dQWnphRjZOMUpWVGF6ejgxWk9rNDA2Zm00UV8xbWJ4bWdQc1pEdlV3a3pXNnJDMjNGOGh5djZ0ejRQb2JObm1FMEd5d3hrRHlUWWdsNXNwTko4MEh4ZWZCRTcydExVUVhNZ0pGOFV5V1FkVUNwdXl3eDhpa1ZyYlNvMER2X2NFR0JXXy1sOWpVbGNjczRzaG1qbXFPT21pSnhqV2lMR29kVWR5OTctVkxOdWs4MEpWc1hxZG1jZk5CMFAxdkxtSlBORXl1RTY1X09yRG81dlFtX2k2OV9EY2NwbDdtd1RqS0hnTjQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcXh4bUE2R0xXQkpTUG92NHptZVVaUU5DaTQyR1ZZRXBGR2swS0F6OThYZXFia3hRdHVYLVY5V3c4VVZWTVl3M1lYeW9rZ0Rid3Q4Y0pLM3dmVVNadW1IaEttMmJLelFsZ1VMWkdrZDBhWXhwWDBhNTB2T1FpN1I3c3d5Rm9JbDl0NFBrNXlZbDM4VFlvTmpOZ3hUalRUZ05IQ2V5UEZsbXZoc1o3UHNHRGVqOGMtVlJzcmhQZm5yaWRIenfSAdcBQVVfeXFMTkttNGxZUXZLOHVwcmhUWWhmN3FUOEEzcWY3WUJnS3N6aUhlQ0QtSG5tVU5nQ3dzQ2QtS0MwTnp3MkxmbWRDQjBIT1RweFFIQThLQ0g5ejFKVklLRlVGenk0a1lVLVFwZjZNVVJEWWhaOXZhZXROd0w1aXJFOVdKOUUyNzUzWlFtS0JXUWZ6c0JwZmxiOVM1SEYxaF94dlRGelVwazE2aWs3OXNFMzFQM3lQMWh4cjllVkwxZkpzbGJRa2NtczgtSGZYOFp4VTNHSTAwTUNVOHM?oc=5</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1323,26 +1323,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-11T12:00:01</t>
+          <t>2026-02-15T18:30:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Trump amaga con aranceles de 100 % a farmacéuticas mexicanas; quiere su producción en EU - La Crónic</t>
+          <t>Variación en el precio de las actividades del sector construcción - El Economista</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>La Crónica de Hoy</t>
+          <t>El Economista</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPeDdqQWY5ckJuWkpYSXlxMkstNHRtRkFwUDZMcXZrVmZoMk92RHhEM29UeG5Zb1ZKUkFVMHVxVy1OYU11S0lMaUYwVzdGcHZEV01iNVlwNUFtbzBxaWVyUDZuOWRQY0xYbVc4bVhoTDRBS1UySXk4c3l3YmRnbUg3clVZZEJoM2Y3a0hfRkl2M1Fva2diR2dVTlhpZ05tMlVrRE9oS3ZwTmdPRmthRk5RUHl6aE9mRC1jVkh2ckdHd3lFeS13aW5keVd4bzg5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNWTVzc3MxQjBVTXE3a3BzZ29EMFZIdDZqajdrc0tWd3Z6UkZhT3REWG9QZEhqVWF3LUNkM2ZVYS12dWhJTnBQa3UyMHZieWJUX2RRRDcyYzM4bzJtOWdBbW51WU5SWm4weHRvZzMzdG5GR2JTTFFmTkNxa0xFaTFSWTFTRTVNRk5SUlJIUW13ZVdvODZRZE1kN2RQOEdudkJIZzRXVmJRQy1XbUtSUm1wWkRGUWnSAboBQVVfeXFMTzI5VTgtTzJ2VncwdThSM1huMVlMQmZvbWRGSXNfejBnaXdIUl9ualNMMkxETmxHbTlxVjBJMl9ZTzJuRU9FQzZiZkkwQnBzMGphNHc4bFgzVE1VOWxvU2tWX0pkUWRjNmpXY0pSVVJQcXFfX0o0YmJiZXFqX3FyYnhmOHh0XzhVcE03OGJDQmNaNExCVkI4Sm9XYVVQZVdnaFBfRDd0NEJ3NV8xcHd5R0hSTy1CbnZGb3p3?oc=5</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>-0.51</v>
+        <v>0.26</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1350,37 +1350,37 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>-7.649999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.475</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>3.825</v>
+        <v>0.52</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.825</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-11T10:06:18</t>
+          <t>2026-02-15T18:23:49</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sugieren que personalidades de la vida pública en México sí tengan protección vehicular de alto nive</t>
+          <t>Proponen al Congreso inspección y regulación del transporte público - El Heraldo de Puebla</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hoja de Ruta Digital</t>
+          <t>El Heraldo de Puebla</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNNEVBUkRmR1FiaGpReF96cEVSM1lUTVBrd0dEWWdKRDYyVHJLU1FQTU50X2cyRFVUX2lhSWJndkd4R0xOOWVxMXJwM2VCVzFBQ3RMQXRKdWFPV3dCYk9ibndURFBMUlNMSVEweHJYRmZPRFpSZnJhSkZ0ak4za2RoN3hPeE9xZDI2b3U5ZkFEWnQ1OXFvVE1iTDdnY0pCT05ENFd2STdWU29lYy1EZnpBS0VrX0dtQjBJQ2lGUFJ5YVJ2VWxpU1pNbmNJWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPLVg1WS1EaU83akdtaEU0bUdBbUlMVFlnd2hJc2c4cmNKc19tcnF3UXFMa2I4MUk5bnlvdndNTmNsZkVBUk1nUzJBRGVmZDZuTDN2a05FOXFJLXJrVG9nT2FaenJPaklJSWZod2YtSEoyRWhNYU01eUxyYTV3aU5BUlFmaEdEU01UMHZQVXlMaXJGcDg1ZkhTR21EdV9BQWJua2gtZFkxTURTTUk?oc=5</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1407,26 +1407,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-11T00:20:42</t>
+          <t>2026-02-15T17:33:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>La Décima Sexta Zona Naval recibe visita de alumnos de la Escuela Primara “Voluntad de Acero” - Gent</t>
+          <t>Presidenta Claudia Sheinbaum presenta Plan de Inversión en Infraestructura para el Desarrollo con Bi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gente del Balsas</t>
+          <t>Gob MX</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxPLWUtZjlMbV9KOUw5VEVJSUpiVnpsMVV5eVFDeGFqT0g0S09ZUmppRXZRMVdtTmk5bTFGSzJ0OV9wb0k0OTBQdlhhc19vWlhGLVlTQlVDXzVhcThGbmJBZGRzREhaV1g4QW1SdHY2bDZibl9iSTNZNllpdW1wRU5Lb1ZQOVF6YWdpN2N4ZlRfa3dQMDVxLVdxYVVFZ0RyVUJkcGxKbnAxdldxN0tqSDNjLW9xUDJhMUdkQXIzZThNZDEyVDFLYkhxNg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR1plamhZb2VOaHNsa2dWV3I1LS0wVkNzSnBZdV9WbG9zazRlazgxUVdrd0NzY0ozMkwtZEMxc1ptQnV2MVJjM2hPUDZ4VHJNT2syczc3dmNlS2F6QWg0YV9TWHF3bDg0a2J0RzNxQkhoaThGbzh3Yjl2cVNMN1RWYU9mWl9kLUtnTVRidXF3WUdtcnFwWGpQNG4tbjl4dWNCR2J6N3prZXlLRmNTeHVKMkdETHBaUU9UVnJBY3V4ZEFjMnotdi1WdVlncFdNM0VKOUtCMzI0cGY2S1Q3WktGcnRkNXI4d1FET2ZvUEhDbGRQX1JIT1MxSzhmbldZOS0tRTR3QkhB?oc=5</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1434,167 +1434,167 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H21" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I21" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J21" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-11T00:00:00</t>
+          <t>2026-02-15T02:17:59</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Futuro del T-MEC, en riesgo: Trump evalúa sacar a EU del tratado con México y Canadá</t>
+          <t>Entrega Gómez Álvarez infraestructura diversa en el Edomex - Marcaje Legislativo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Financiero</t>
+          <t>Marcaje Legislativo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.elfinanciero.com.mx/economia/2026/02/11/futuro-del-t-mec-en-riesgo-trump-evalua-sacar-a-eu-del-tratado-con-mexico-y-canada/</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcXNPNkMzMGxXR29aOFctTWtVTnR6ZXNmRHl6TW1vMlZvVWNCZ2JSWVRrektuTHFDS25lb3RWN0dxQjEwZ1lsekxyQS1iRVdseEdKb1RIR3IzRVdYb1B6S1laeGhJRUxQd3Zqd1ZOUVNiQVR2WldrRF9ROVR6Rm5kd2t0WE45b3R4MUV0ZjRBZnB0d1hwM1kw?oc=5</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-1</v>
+        <v>0.26</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>-3</v>
+        <v>0.78</v>
       </c>
       <c r="H22" t="n">
-        <v>-4</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>-2</v>
+        <v>0.52</v>
       </c>
       <c r="J22" t="n">
-        <v>-2</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-11T00:00:00</t>
+          <t>2026-02-14T02:28:39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ampliación de convenios entre México y Brasil elevará más de 10% inversiones en ambos en sectores es</t>
+          <t>CMIC Yucatán refrenda unidad y visión de futuro del sector construcción - tintapublicanoticias.com</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milenio</t>
+          <t>tintapublicanoticias.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.milenio.com/negocios/convenios-mexico-brasil-elevaran-inversiones-nuevo-ace</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYmtwYW0wXzdZZFZTa3YyazAtdHN0bHYtMjFtYzE5aGJTRnFVNHU3VkZSdi1TRzgxRTVDWEU1VENVUkhrejhORDRKbktiSDNub3lBSmM4ZkY4WGRaTXpJRHRpb2RQX0hKbHlDRjlIX1VnYVNpQ2ZfbE9PTnowQzJJWElnYW1seWs0S2RWdWNQY2FWYndNSnNoVDdTcHdfNjhua1lIb1Nxdlc?oc=5</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0.78</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0.52</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-10T23:21:44</t>
+          <t>2026-02-14T00:48:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mientras se disipa la polémica por los caños, Techint se expande en la industria siderúrgica regiona</t>
+          <t>México alista reforma audiovisual con cuotas para cine nacional y regulación del uso de IA - BajaNew</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>El Cronista</t>
+          <t>BajaNews</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPVmV2dGVvaklKdHAyUkd6dFBlQjVoU0dkUmpXbkVXQ1RJeXEwOFU4RFVoNGlOcUtRaUpFZTA1cGFzQ25hS1UzZFpJUWdZckMyR1Z2ZEFuOTJVaFc4V3JSaUZMMjBoQXc4bm8tY2JMdWxPVGFrRmg2WURhU3NHd0l6Q0VENVlhS1Zrd1pIWUQzMm5kQTNOYU1UN3JGNGJYZ3NLb2EtYktSUjBGTktVSXAzbjFjME5tb2sybVNzUkk3V0pLR2VYNldyQnN0WEI0ZExI0gHrAUFVX3lxTE43MVNvdWxNTDNnV3AybWdoSlo0b0NGQXlsSTlReFZsWjlqVFVhYkRORTVPNWk2NzQxUlJ2eldxdnNUcFNPVm5TancyUU03RllHbkd3MThtV1I3UmprX3NJNko0S2dpTnpMNVowNHphQnR3S2hqYmMzSm9MNXY2N2w5S3lsdGlkNmE3T28zZ2txeENxYndIRlJ5RXlMdGY1LUxpcWI3bVo3WmhoT256alNXS3JfbHNvaWNGc0tJYkx5NlRkUHNsZDJXSHV5ZWRaZ1NRZkkzODcyUnpzTEN5YVUzNGw0bDNjdjRYd3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPSVRDY0hoeGZIRkdCTUh0QTVGVmt3MjRZMjFIMVcyQjVXZlVvRDNjY1YzYXgtRGF0MjdubEFRMm5QWHdsejkxek9ybC1rLWQ1T1ZTQjB3VnFSV0FlTm1PM1FHVHZqTnI0S1ZabTJGZGFnRDZGRV91VW5jNFVsUkZreDJsaHhJcGIwajBFMkpHM2JsRWFRWkRkc0pwRzNQSnNIRF84VXprSWtxLWg2eEtoeUFJNTRZMy1PY1B4VlU2ZHktSHM?oc=5</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-0</v>
+        <v>-10</v>
       </c>
       <c r="H24" t="n">
-        <v>-0</v>
+        <v>-15</v>
       </c>
       <c r="I24" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-10T23:21:44</t>
+          <t>2026-02-14T00:30:41</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mientras se disipa la polémica por los caños, Techint se expande en la industria siderúrgica regiona</t>
+          <t>Construcción: del ajuste de 2025 a la inflexión de 2026 - Centro Urbano</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>El Cronista</t>
+          <t>Centro Urbano</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxONzFTb3VsTUwzZ1dwMm1naEpaNG9DRkF5bEk5UXhWbFo5alRVYWJETkU1TzVpNjc0MVJSdnpXcXZzVHBTT1ZuU2p3MlFNN0ZZR25HdzE4bVdSN1Jqa19zSTZKNEtnaU56TDVaMDR6YUJ0d0toamJjM0pvTDV2NjdsOUt5bHRpZDZhN09vM2drcXhDcWJ3SEZSeUV5THRmNS1MaXFiN21aN1poaE9uempTV0tyX2xzb2ljRnNLSWJMeTZUZFBzbGQyV0h1eWVkWmdTUWZJMzg3MlJ6c0xDeWFVMzRsNGwzY3Y0WHd30gHrAUFVX3lxTE43MVNvdWxNTDNnV3AybWdoSlo0b0NGQXlsSTlReFZsWjlqVFVhYkRORTVPNWk2NzQxUlJ2eldxdnNUcFNPVm5TancyUU03RllHbkd3MThtV1I3UmprX3NJNko0S2dpTnpMNVowNHphQnR3S2hqYmMzSm9MNXY2N2w5S3lsdGlkNmE3T28zZ2txeENxYndIRlJ5RXlMdGY1LUxpcWI3bVo3WmhoT256alNXS3JfbHNvaWNGc0tJYkx5NlRkUHNsZDJXSHV5ZWRaZ1NRZkkzODcyUnpzTEN5YVUzNGw0bDNjdjRYd3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9zcU1QNkxVSjlwb2ZfbUhBSUhrWUE4NWZ4THhObG4yUGFvMGFiTGp1aUlXQ005OXhZekswSjZIci1uWjlBR0swc2VweW9ia2Q0eUw0R3pyblFidHdwcGxveXpBUEJhb0lUVjZ3dEtmVzJuY0h6S1NXM1Rncw?oc=5</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1602,37 +1602,37 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H25" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J25" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-10T21:21:00</t>
+          <t>2026-02-13T23:10:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ternium completa adquisición de acciones de Usiminas por 315,2 millones de dólares - Investing.com E</t>
+          <t>Vale fija plazo de tres semanas para recuperar Viga y Fábrica y reabrir con aval ambiental - Minería</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Investing.com Español</t>
+          <t>Minería en Línea</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNd1VjUE5fbndlOGdvU2RyNXlpUGhrZ2czSnItbVVPUHVTZjl3bi1felNFWHEydmNqbFZRTUtXenk4UDdpbE5GS2FtekNJLXdwVFhCMkFUSEcwMmN3aHN4ZWVRb0hrZTNBdWVsd0dWZGxQX0IxMW9USmoxNFdIem10eDVBZkEwV0M4ZlhGT3JVa1VyNzZNZ3F4bWtlUlpMeVhHcDVpMGhmeXZxNHR3VVFtWGk4TVVMa0VpcGFsMHBKMWpDRFlQOGdiLVZtdUdncmpCWE1F?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNUHlBd2NCX19GaGhxa3lsLXJBRFljbUhVX0pacjV1SXBqblJCN0pTbkZIZHAyeFlKS25jbmdYaGNHOGtRUmhSMHI2aGM5Wm12VVp1YWRiaE1LcTdSdzFYUUFnMXZER04yVG9UdEtrMkZma05TeXlVOVNIUkJ0d0FwUXhpS3ExUDBhaHUwSDhFNW1Vb0lBMXJpTUdLdWNRajhzODZPRzZPbjNiZEw2RHZIMEtKVkljNWRVS3dLcTlhODRBa0Uy?oc=5</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1659,68 +1659,68 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-10T17:00:00</t>
+          <t>2026-02-13T15:54:00</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kristi Noem Firma Contrato Para la Compra de Acero para el Muro entre EUA y México - N+</t>
+          <t>Los precios de los metales se desploman mientras Trump reduce los aranceles al acero y al aluminio -</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>N+</t>
+          <t>Cryptopolitan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPamxsVURNOGU0aGN5Z1g2QVpTeFZxcFNFY2tJS01MWC05ZWF5bG1tU1hnN0RRSG9Fd2VxM2hqVDBNd1pwdThmeUJkUXVCM19DdEVhSHFiaENnLUdkVXhyYTd6WS1pdy1sM09jUXhoU3BJTVBCUVdTNWIzWTZyb1R1ZWdPLXduNFVmdDhhbURERl9YUkVCR28yamVVZmFrWEpHdGNNeWZYM3RLSmR3SjY5VGJjTWhJWUpVcU4tZW9JS1dkbFMxQkgyMGlCb0F3WUZvdUh6amd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAzQVBYc1QzNW85djVnMEJvdk1zODZmOTEtWFBqdWp5eU5XdkNZUDhNZ3pTajZzNlV0bENUcjZlUFN3cEJsWGh6bzVqOThyNXZFbWM1MnNfRmJqNG41REE4cU5xUmZEd19oOTgtY0Y1STZIbk1G?oc=5</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-0</v>
+        <v>-10</v>
       </c>
       <c r="H27" t="n">
-        <v>-0</v>
+        <v>-15</v>
       </c>
       <c r="I27" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-10T00:00:00</t>
+          <t>2026-02-13T15:50:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cárteles y barras bravas, los principales retos para autoridades mexicanas en la Copa del Mundo 2026</t>
+          <t>México presiona en T-MEC por aranceles “costosos” al acero y autos - Industry &amp; Energy Magazine</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milenio</t>
+          <t>Industry &amp; Energy Magazine</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.milenio.com/policia/retos-seguridad-copa-del-mundo-2026-mexico-cuales-son</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUXFPQ2NuUVIxcEVtVU1ta2VZME8xcjI5UHNtMHRIMVMxS3Rtc0tBOEVhR2pEOHFYcFB5SHN1NHp1eTdHM2FwYzYtbUduMV81NkJsWWRGdjNjbm11cmg0TElOMkdYbjhOaDBlbTRPaHZzQUM0MlpCTFJqMDRkR2lkTVY1b0c4d1JxR2ZrMWJpNjIwcU5lSkFZYmNyYmhkQ25p?oc=5</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1728,41 +1728,41 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H28" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-10T00:00:00</t>
+          <t>2026-02-13T11:27:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Carney contradice a Trump y afirma que ‘Canadá pagó por el puente’ que conecta con EU</t>
+          <t>EEUU sacude al acero: Acerinox y ArcelorMittal se hunden - XTB.com</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Forbes.com.mx</t>
+          <t>XTB.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://forbes.com.mx/carney-contradice-a-trump-y-afirma-que-canada-pago-por-el-puente-que-conecta-con-eu/</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOajJiWFZfZFpxVUtDYUFKamxjbWw2blBMbDRSb18yNGdtTmVGZUh4Ni1DS2RPZUdYbFp0azRNeHJnWGQtRk1OclRwcDRIWXRjREwxLTRmdjVTY3ZKWHEzclRGUnpmaEZiZVUwV2p6OU1VZnBWOUNGRy1QX1Q1dlFvZXdSeEFJcjhjNGtoRWZNSW1wSjM2bXN6SWROUzFJM1did3U5RXFyNnZVb0lFM3NZbWxVTWt1SGJmZHJIcXpRQTFBNXVmZm1sSUREa0FseWk1QUE?oc=5</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1770,125 +1770,125 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.78</v>
+        <v>-0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
       <c r="I29" t="n">
-        <v>0.52</v>
+        <v>-0</v>
       </c>
       <c r="J29" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-10T00:00:00</t>
+          <t>2026-02-13T08:36:54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>El Volkswagen Virtus 2026 ya tiene precio en México: el sucesor del Vento ofrece dos motores, tres v</t>
+          <t>La economía de Rumanía entra en recesión técnica debido a la caída de la demanda por el déficit y el</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Motorpasión México</t>
+          <t>MarketScreener España</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.motorpasion.com.mx/industria/volkswagen-virtus-2026-precio-mexico</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOTWRNb3lnT0N5bU9tUzc2NURGSWpSZFNaeWhVTFZldlZzbHhBdmJqV2pxSkV6V20tUUFPSHF5cGhpYm5RUy1vNVJfaVl6bF9UZHRVaEVZLUl3eGZjbnRQcXYyMTdlckc5dkZEVjZncWNhLU85Y0lQUDEya0oySGNnNkpoNGxuX3ZZckxYNnpOOUsxaVdSQksxalo5akItaTJxV1FVUVZSSHBmSGU3RWtPeDRaYVpmd3Fzc09pX1VDSzF1SU52dmFSd05QSzNtd3Jndm4wNG1iUjFRMUlrdDd0eXFNcGJVeGVJQzNMeg?oc=5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-0</v>
+        <v>-6</v>
       </c>
       <c r="H30" t="n">
-        <v>-0</v>
+        <v>-4</v>
       </c>
       <c r="I30" t="n">
-        <v>-0</v>
+        <v>-4</v>
       </c>
       <c r="J30" t="n">
-        <v>-0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-09T23:23:05</t>
+          <t>2026-02-12T23:36:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Empleo formal en México registra en enero su peor inicio de año desde 2009 - bloomberglinea.com</t>
+          <t>Infraestructura de recarga impulsa movilidad eléctrica - Energy21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bloomberglinea.com</t>
+          <t>Energy21</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxNOFcyUXlOZTRTOXBHX0tMRnJtbHNLQXlZSVcwakZSUGdBQmFkTHFZRGxBUXljc1dxYjBpZldMbEEweGRBbXNDM09kSEtjQXNjT2tiUWtjZ2FuMEZlaklBMWx3aU5MTW0zQWRyVUxJTm54R1hvTXM0aFVEVWt3S0d1cjFlNTVHaU9FTUpUTnJ1aHZ4MjB5anhoVzFGU0VldTBreldHZWdaU0ZkVmdPWmpIdTJLNWpMSXhzczJBSi1ENmlJRjlqZUHSAdoBQVVfeXFMTTlTU2xaWENoZnh2NTVhbTNqb3RHbXJkcmMtWFhhSlZYYnhsWlRfdVZlb3k4c3JkTmpEeW1QVzUwSk03RDl1VXBNcTBhZ0pyME10clpPTDlsRUVkRjBWYlBuRHdaQ3lHbXJWRURjTVU5SjdWb0xackxpZ3pYYjkxaHBFR3N0X3Yya2xLeHY3eGF5R3pURnU2MVJQRjFoQldQWEpOc29RUUZVRC1PTGVYZV9FMVZlejVKbzlGS3ZraTJwNkJSR0dEU01IQlRfVTJOaW1iQVJZUTVITUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPT3FYNEZHMVNiOUZFMFdBYkFxM0RFSENFMmRCbjJxSnZ2ajZzREtCSU90ZnJ4TUZHOVhKbURBMEJ5TDJVTmlyVUU1cXhGVzlOS191N2E1VkFicFZpVnFLejRTOTl3c3RuUjE5aU8zT1Y3LUZjZHdiLWlmVjVCb2J4bUx6OS01QQ?oc=5</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="H31" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-09T21:50:37</t>
+          <t>2026-02-12T18:44:22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Princess House busca emprendedores en Culiacán y promueve cocina saludable con acero inoxidable - de</t>
+          <t>Busca México aranceles homogéneos en industria automotriz - Reforma</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>debate.com.mx</t>
+          <t>Reforma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxQSjhxemJYWjhyTndoMlRzTmRjWnlNb2lWOGktbjhuaTRPQmJqTUtwdFZmSjVCZEhtQm42X2VKekZiVG16bXBqNkg1bUVsdXY5TWlCMjlhSDlKLVlQTFZ5ZVBROEsyRVRObWJwZnNxLUxfUzZhSlI5M0FxbGMxb3V5ZldvSGtESHh2SjVIZDRzbnh5dWdRcW9lMTRMSEt4YXBJQ3UzM2tsWGI5TTJRU2ZKODRvMGN6Y0xxNWtHb0RvLWhybXBCMGQ0U2xsSlZpNFFtWEh6TTBuOGtTemlkWG9UYkNKbndDZ0lzQ1JGYXpB0gHzAUFVX3lxTE91cWZDd2ZTWkxNZGV6VFgxOEhkYnBONExjaDJYWXI1ZW9QOFc2Rk5QSzlMSXUySERrbVZ6ckJpNjM3UjlLVVVSUG5MaFRyV1BHY0x4bkJIc2VZYllNNjE3Qm1TU1RiRnI1MlhDOFFaaWM3QkM5RmtOdktjejFsaEtFY01ZMmxGd2R2ZG1vS0M3OWx1bmhfSnQ5amhSREtOb21XQW04T2stV0RVS3FqM2stMmlDSTl4MGNqc2EtXzhzS3NydVlBcHFxbHZyN202dHp5N2hNZzBiN3djYUV3UTI3bDN3UkFiRzllSU40SE9xbmhxdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQMGcwbHFvSERsc0FiR1NNNGpwam42bXo4d2lhVmhDNjc4Z3hxaUZkby11R2ZVREMxQXE1RXVIRVFnUktjaUtwdW1GVDhPYko4N1pVQklETFdMWXN3QldEUHpyMWlpVC1wR2xBbVE3bjFIbWQ4S3RCTGlsVk4zbFRhTWI5VGlZYnQ5dC14NE1GemZrRHZyNUE?oc=5</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1896,79 +1896,79 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H32" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J32" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09T14:01:02</t>
+          <t>2026-02-12T17:53:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>El Chevrolet Onix 2026 baja de precio en México: más interesante que Aveo y ahora más barato - Motor</t>
+          <t>México va contra aranceles al acero, aluminio y a la industria automotriz en revisión del T-MEC: Ebr</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Motorpasión México</t>
+          <t>El Sol de México</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTE8zS0lrcFRsSkhCNmpodzZJU25nc3llWGx2d1J2ejNpMXVEQzBJUjZVX25STUg4WGxXNGRSZXVGTHR2WmJKUTREMUl2eEVzdnRFcmJLTUx1MFQ5X2FnOVBQV2JLQzBadGt4WDQ4blJfaUYzaTJicVN5aUpZdnQ2YknSAYQBQVVfeXFMTW53d3kyVG10MjNkVnkxUGJPaU42VzFvdzlpU1I3OEFuR0o4WHQzaVhkSU9HckJ3RFB4X0NZR2ZNR3k5VUFOd2wyQmxFS2txZUpYNTdyMzVtczhoWXdGbGo5UUlwMTFYNUJwR0ktR2J6YnM0bnh0bE56SndZeEJSVGpwc0JF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNSWtjRVdiVEZTanhLTllZOEZEVno2WjBoYmIyOXBMVkZOVW04ME4xUUZ3TExpanVIX0RNOHBjYU12dXYtZmlneVlwYjBKZkljUWE4dUpfMUNXb3lteDdGMEdfX3FaQzl2aVl6LUtxRm02Wno0TUVrVU15SWthTFYxSkw2cXZGQjhhT25oOTNucUk0dW5yR1VCY3o2TURyUHl4YVhqUGFRZVE5X0dsaTRodjRQSE10bzhRWHRFaWJ2dklmQXo1NE1NN0luMnh2U3dqTVhCdnBVMFBxOVVoWDFsTkkwZFVtRms?oc=5</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="H33" t="n">
-        <v>-4</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-2</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-08T21:20:47</t>
+          <t>2026-02-12T09:30:27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jóvenes escalan chimenea de AHMSA en Monclova y se viralizan en redes - vanguardia.com.mx</t>
+          <t>Este descomunal horno eléctrico convierte coches, motores y chatarra en acero verde sin quemar una s</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>vanguardia.com.mx</t>
+          <t>Diariomotor</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxOeHNyWFhVTVVoNGcySjIzSTZXSGsxM2pfc2VCMC1rbDgweU9odG9IaGp3Y1ROU1lWTGZQbHRyQXVWVWRwX1o1aXduamZ3QzJUOEpGZlVqZEFqU0t3XzBITmU2bmNyX3dMVW5pUWlkaE9hUy05SkU1YS1WX215RWZZMS1BMkt3ZVRQSG5CaUJXckx2QV9lZWJyeXdKbGlxUER6T25zVDBHU3loTEFkdnBKSThpSU5ka2duTllFSXVfSFFYUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQY3IyMHJPSTdjRGVmR2N0N1B3LUx4SlNTNG52elFpcGp3OTZlbzJkV3IwZFhSTmhTWDl0XzBINzN4UllESjRJR0xCbFJlZnp2eHpIcEpiTnBpUDNySkxrTy00S0ROMWRqZEFnRGdSbXRqdVE3QmNaY2dUeDFBLWlMU2RJa2NCNXZuTV9ZWnR5YkFDeFdUUVhDS2hxOG9KZmZ2b2Rkdk5R?oc=5</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1995,26 +1995,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-08T18:01:27</t>
+          <t>2026-02-12T08:00:00</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>"Ilegales e injustificados", los aranceles de Trump a acero y aluminio: Canadá; hay "discusiones int</t>
+          <t>Desplome en construcción pública: inversión retrocede más de 30% - Industry &amp; Energy Magazine</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>Industry &amp; Energy Magazine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwNBVV95cUxQREFualdmQ1E5VHIyemE0V3VOdkxXd0xrVXpZcXhhVkpkM2RZVmhDaGJFNTBoZFNuX0FGbEpneHlta3p2S1BHTGN1dWFtVUxGUW9peU8wbVZyY1AwV055SGhxTGdEbTB2TFMwaHEwOTdsd2s1MlZfS2g5UVJoUUpEU2tkY3ZBQmY5ZU1hcWNxYjNQUHByOTJNVV9sSTc3dEVnSlZxZDdYd2lZTkhUMGRLSHdCVFlILVgwWHBCMWlfdF9fRUpPV3lsTFRyNEFqbVgyNXh6X0VsaU40VGZTZ2tQdVc4RjZrcERfVER1eUJJUzNwc0prU2hQcG96X1hyLXdRNEc0ZGpGZFpDbmdYcUswdEUzdFJOcFZ1ZnIwVG83c2pFS2E0bjVhTEw1ZG04UGdmRUg2a3ZJMnZzSU4xa3FOYjFqTk9JVGdBSzBGdkF1dHZDd2hYMjJld0RFQ3ZoNkFvSWhQOTNJREJ0TnlseTVFTld6NmtJQ3lOR2VLSkZFZUlqZTUydEdOZFUydFcxZVYyek1maHpCbw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNUExLT2RPUkVsTnRrMmdrWGtDeWlBaHRGUk5BTlRTZjRfdHlMNmVTMDlzeDdHTE1uRDRhcmc0UFFhLUNQa0VkR1JmTmdqVVIweFpPdG5zSmVFamxPbDNRbHR4bFgtVHJLcmJFZmMxYWNMb3BpR0lBbUJOYTdkYTZZQnczNWdOZk1WazhoVFFMVzIwT3RvQ0kwam1MaVI5QQ?oc=5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.34</v>
+        <v>-0.09000000000000008</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2022,41 +2022,41 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-3.4</v>
+        <v>-0.4050000000000004</v>
       </c>
       <c r="H35" t="n">
-        <v>-5.100000000000001</v>
+        <v>-0.5400000000000005</v>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>-0.2700000000000002</v>
       </c>
       <c r="J35" t="n">
-        <v>-1.7</v>
+        <v>-0.6750000000000006</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-08T17:15:11</t>
+          <t>2026-02-12T05:41:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aranceles de EE. UU. y puertos mexicanos: impacto, tensiones y respuestas del sector logístico - Tra</t>
+          <t>Kyle Larson imparable en dominante victoria en Bristol en NASCAR Cup - MSN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Transporte.mx</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPMjN3dzFjLW00S1BlRzlGUEZ0R2NKdkZlNVhnLXg4elg3QVU3NF80R3BhWEFuWWI0ZXdEaWFNaTl1WmUxX1hFYlpuUXZWV3F4Q210dVAwdk00NzRneWZmeWRkejRUNDhya0VaV1lYZkpRcEZ1cEZVeFh6RnV4SDJEQTdaNjBWS0RfXzNrbFF3NVFINFFDd21SZ19GMnlqLU1YaENzS1YtTGhlRjZDbzMxRnBJcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxPUEdFT0Y5b0FnM2ppT3Z4TVZ6QzdGaGh0N0llUDFMd1lWdTRjcFNiRWZYcjM5LXI4azZ0Y1M2dG11V0FDcVRFUnpLSWc2Z21QZ3ZuUzNoMlNBT3p2MVBBNllPT1Z2WU9vVGFsc015RDlVMWtKMDU4ZTE4TGRUWUdNcjBtVnhsVGRYSDRQaDk1dWVvcGl5RFlhNjBWeW95d085ajF4N2hibFl5Q3JGQmZ1dk5LTjFHQUk1VnVBYVNMbTdIRWg1WXpvSmFhamRlMnhwUkZRQlhXUEI0U2dramlCWFFLblJUQ2RYVmVybldMNUo0Zk9Da2FBU0pxejBrOEdXYVBlRndKaXlzSS1QU1RGVmZ2MEZEUGxXRDk4QXI3Y3pZMThmT3pBTXNnbi1lb044ZjV2OHdCeTlrcW83Yk12TmJwSmM2anJIUHVJeU1CVlFzMmh2?oc=5</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2064,41 +2064,41 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>-3.4</v>
+        <v>-0</v>
       </c>
       <c r="H36" t="n">
-        <v>-5.100000000000001</v>
+        <v>-0</v>
       </c>
       <c r="I36" t="n">
-        <v>1.7</v>
+        <v>-0</v>
       </c>
       <c r="J36" t="n">
-        <v>-1.7</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-08T11:19:14</t>
+          <t>2026-02-11T23:57:17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aranceles a acero y aluminio afectarán precios de la construcción: CMIC Edomex - MSN</t>
+          <t xml:space="preserve">Ante crisis del maíz en México, Márquez Márquez pide frenar importaciones por caída de precios - El </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>El Sol de México</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gJBVV95cUxOR3h5N1RYZWNBb2pfQlR0dXczajZ1MXVyZmZ0U2VLbHk5OHd6bnkydUF0cWp0VHdjNEhZSUZyUm9xeUlYTXJRLWhheVNuSGxRa2RldEVWdUpWOEpHS0ZFWFd0R0VROHdyZDZTNEcybkh3NHFxbUVHY3QyTnBHcXZEZUJYZ1BxSWxmRWJQY1l3cFlza3lNendtZlNhUkF0OHFaWjdwekFvcnYyb3JZbDhpbTh2UEpGZDNwSGpDYzNBcGw4ZG04dlJEMUJCV2hJb09XZXllYXRFNnhsRm9mNDJGc3ZuNkdIQ1RLbmYtN3cwR04zWmh4em42aEt3dU1jaHFHbml2UHlFQUZQV0ZLWi13cDdqV2EzNGJxcDEyZTdoc0xWZVYwMll2b0dfMld6MlFxOVJESk9Xam81ejNNNWdsQXF1YW5mUGZSRkh3X3ZrSXhLTHJ1RnQxbzB0Y2xJdFlQZEZydHJDRWdGSEFpSnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPVzRxTzdOc1BWV3hfRkRRSVFUTEZFZTRxWVkyWm9TSGNjRC13c09FWGp5LS1QNUlqSGVIM3FHYTRPemcwb1VhaEk0dDIxTU1MN3RGNDdhU1BpS2VfRkFlRWQwcWZ3N1NKekRiVWJ0eUR0U3RmMnNQRzl3TW1JeXlvM0F4ZjJ6REZpVl9ERXpOMmhmaHdWZGQxd1RONTdlbzdNcjRoNk8zT1ZLNlhZcFRfdmRMaURUN2VST2pxVkhKTVJNZ21oTUZzTjQ1S21SeG15NjVn?oc=5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.08000000000000002</v>
+        <v>-0.6200000000000001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2106,41 +2106,41 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-0.8000000000000002</v>
+        <v>-1.86</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2</v>
+        <v>-2.48</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4000000000000001</v>
+        <v>-1.24</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4000000000000001</v>
+        <v>-3.100000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-07T06:09:00</t>
+          <t>2026-02-11T23:46:42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aranceles, despidos y silencio en la industria automotriz - El Heraldo de México</t>
+          <t>El mercado interno ofrece espacio para el crecimiento en la industria del acero. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>El Heraldo de México</t>
+          <t>Vietnam.vn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNa2l3SVJKUVZzVmNkcWVCOWJLQjBsMjRwWExMSlJyUkZDWTFiZ3lqelpxeUwtOVpKYmxNa2pYc3p5TE95ZG9oQ0ZCT1AxblNlck8yeWNvN0ZiYUk5bU84T0lVNW5RQVU5WmZqUDRmam8tb3BuV3QzejFkd05xcnJvVWxLYlhpN2wwUjBhQmdUUEFaUkt0bUs2VTZzekRqN0xfZmo2MnZPMzdPckNkU1R4ekEzRWrSAboBQVVfeXFMT2c5SUd2cE92ZnhQQnc2OF9GeWlLNmJKMUVKRFRnODRyNEdweTF2SzdGLVVGc0V5SWxkRWxOYjZXVjF4ZmdINU4zR3dqQU5ya2R5S092bjdhYXlWb3NOV2dwZHN1QnhlbFhRNHA4c1FkUkNkOE1fcnVPZzFNbC1lSVVXUGlNYl9Pc2hVRC00LWRndnVqVTlPN2NmVmZCVmNUS29PNERHWG41UGVOZkl1VEFvbUFrSVRMNEdn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPeUw4MTA3S0JQN1ptTHp0ME96cmRld2hZd0hveFoxejZxb1A2dFNhNWdIS3ZXWnlFNWhtNC1KVFFVNUx5VDIwZzhsbVpXWVA4cWVJZWk5bTNTcXR6dHZqQ29UU2lFdG0wNEpTT2pwMjUtNXVSTDRua2k4STJybk1yWjRKRVdKdHAyVFpfcQ?oc=5</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2148,41 +2148,41 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-3.4</v>
+        <v>-0.9000000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>-5.100000000000001</v>
+        <v>-1.2</v>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.7</v>
+        <v>-0.6000000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-07T04:33:00</t>
+          <t>2026-02-11T13:40:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acero, aluminio, minerales críticos y el financiamiento: los temas pendientes del acuerdo comercial </t>
+          <t>¿Un desplome bursátil desencadenaría una recesión global? - Investing.com México - Finanzas, Bolsa y</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>Investing.com México - Finanzas, Bolsa y Forex</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPNWRtallwbGJmeTFLcXdUeHlXZzVNdzZ5dVFzSVRIU2lvTGtxX3dKVkVQX1Z4U1RDT0QxQm4zX3RJdTRiVzNUdzJ3Y1dOQms0bmdGMnF4aDVmSlZWT1ZweExCYTNrWE5pQ2wzejBDZi1wQnpHbkkzZzRDTjVSXzRtelJSekk0VkZCeU92X3BCdlV6TFRIMVZEeERuN2F6OUFrZVNQMndZMk9rNjRramtFSktQa3RHaEJkZ3VPeE0zTVZWUlhiUmR0Y0VMNXM2UjJjYm9MaUdTblpoeUhEanJaczF6b0_SAf8BQVVfeXFMTkNVXzJxVDVEakNYX3FSR2pHd1RmY0R1OU9XOVc5SGgwX3dqTExmNFpDQlNmRmJpMHYxWHNWc21LMG5mbFJ4dG50Wk9OR0pfeVRxdnJVOGNTbmpYN0sxUEpPRFU4Y3JaaUgxMVdKODVGa1Q0a0tOcllZOEVaYXFTUzlFNlpIX1VPdF9rMVpBYUg2TVBCSXotWGQ1Z0ozZzNUVnB2VEc3R0NoYlJzLW9xbnBfNWVuNXYxNnUwcnZTM2tJdFU1NjdKNWxRck5LNVVPUnBES1MtSDR2ZnF3Ylg2cU1rdkM4Qm4wSk5TR01fd2M4ekNybEh3ZjhURmJtcjg0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPNTlaTi04cHhmZWtrZmh6cU5Zc1ZvM1NTMVI4YkRBMHJtZ3VTNkVid3g2MERWdUlxckFYN0xLZ3ZTYTBXRWliNGx6X1ZyM1JNdndzNVJ2RzBWaWYwUzlRNnhXLXRYb2tCQUpkRzlMNnRzNzJfclRQZ2lRVlFtV1dwaTRtNkJoeUpDUWdJNjRQSnhFU1NLMlEyVFhJc2NLaFFQakRIdjhGdkZ4cGE2d3kwVTlRTUdSNlY4TndVUGVoYmtIUQ?oc=5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-0.3200000000000001</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2190,79 +2190,79 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-0</v>
+        <v>-0.9600000000000002</v>
       </c>
       <c r="H39" t="n">
-        <v>-0</v>
+        <v>-1.28</v>
       </c>
       <c r="I39" t="n">
-        <v>-0</v>
+        <v>-0.6400000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>-0</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06T17:41:00</t>
+          <t>2026-02-11T12:44:42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Acuerdo comercial: Pablo Quirno aseguró que EEUU se comprometió a revisar los aranceles al acero y a</t>
+          <t xml:space="preserve">Megapuerto de Chancay: fallo judicial blinda inversión china y reduce poder del regulador estatal - </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ambito</t>
+          <t>MasContainer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQa0RLSjJObTlkcXJaQXozRjBHWUttWnQzM2ljRmJYclJtQzdPeTdBVzZqQWR0S0treWhIQURDM3ZJdEVzU1h5b0hhaUY3b0NCU3JSbVg2Y1lfeFFhU2RzOUt2aW5yX1ZyM0dYYjBJUFBZQmhoWjBrbTduUU5STUw0UzFyNFhHMFZwU0MzOU9feHFjNDhQTHJ4Tmk4ME5nUk92OU5OTE93S0ludXA4clNRdFMyMzdEazRfbU13d1hwMW1UaF9OUW9CRnBuYWh0VGd3WjNmb09sR3VoTWZQb2xjTW9B0gHnAUFVX3lxTE94aVhaTkJUQ0U5RDlCRHk5QVc3UWM0OWs2VjM5X3ZiNVVWT1JOekhITUpDWlc4YWRPS0dyS3FmTVFGZEQxdUJMMnA0RUwyUFAxRFE2T25WT3J5c0JwM1V3aVhtWE41QlQwZVNwWG1rUEJKY3Z0RXFsenUxTzdaXzVYMGZIV1BSSzhwaDZjMjVMRGRaS0lHbXp0anpUd2RIYzl2aGtwem82YlNFaUdQZXVCTzRTOEItMnhwY25CbmlYN2NFa1BaeEhoaHU4Rlh4eXAtOVRGY3VuUXhTVUw3aS03LTcyTnQxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNXFxaWJpTUdsM3VDanY2YTBJeGNHNlRRM2hlRXp2M2p2R2FGZElUWUVRQkNjQW1OOGhvVXdUd2JtR0U3RFR6WTY1OVNfNHZidEFzU21QQmNaUTFFenV1ZnBVd3djSzJtdEFhZ3RtZ0FyelRKVWFEMUZkY3hubEhiZWx5NFpScFdoTUJ2SHBCQVllQmlJbW9SZnJQdEVQMFVZanE4SzRleU5Yc1YySnFQdndHUVZzaFlFUHlwVUxfMA?oc=5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-0.34</v>
+        <v>-1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.100000000000001</v>
+        <v>-4</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>-2</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-06T17:30:00</t>
+          <t>2026-02-11T10:54:17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Carne, autopartes, acero, aluminio y otros puntos clave: cuáles son las definiciones que vendrán sob</t>
+          <t>Cleveland-Cliffs Stock Falls 16% From Recent Highs: Here’s What Analysts Are Watching Next - TIKR.co</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>TIKR.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxQZXkweUpZSGZ4YzZ4VmJuaGtuMnFQWWpPSzZFc21pSjNJWXdldkpLRUxPQmdUOVF3MzJDXzVwck1TZGZCbE1CNVFtcDdUOHc3S3MzUGhkQTJFWTlsMjNBSEdJcnFfUFJKMm44MmRqT3RScnFUR3pmY3BPOC00Q0tzYXptc2p3bFkxQWhvdTM5LWN2ck01ekpkR2tUZ2QxSWlnSHVuekNxZDM2czA2Q2VhaTRUc3hnVXJXM3dVVF9UZjM2aGJDVjNFSXVTaUJkZEdEWkJPSHFYOGhqSnRHSlQzN0kyUUFDQ2h1cUdsZmJSUlp2bE1pemhZ0gGSAkFVX3lxTE9FT2k4S0dVdDJKNWxGSkZIb3VBYU5fMWY0b2VhSWM1QjF5T2RmSlJkM1hUSWhoYnVLWWhXeVN3TXpkeEZqY1BPWjNjSkFiRFR0SlpQQkFrVDd5VEhQUzk5bEYzMC1POHZ5ajhoaE1BZ3BiSlFlYWpMeGtWckcwNlh1eVJIbVNOLVYydEhORFZzUnFpcmN5eVE4cG9RTHFwSjlSS1djaE1qNVN3dFh3UEZiSlpudFlJTXMzV2lINUlIWmZiWXo1WlNUY2VJSllyMGxyRzgyUV9BeUdlcW43RUZQTUFvZWl1ZTdpNzV1YVA2aHNGN3FBWVg5TUk2UzRTcURZYmlxX0Y3UTRZUVZ6U0l6cnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOTmVtUnhscmt2ZGNxU2dPaEo3M0FnSkFiNkJkbkdMN05jbGpOSUNoR1NEajBNdHNXT2ZxV1hVbXRjOFQtY01mdkNHOWtkbUYwZm8tZ1FYLTdqNlJsUENfMHY5UGRBZ1ZGN3kwVk1VRFFab1dtem5PbWoxSTNDZTVMNDN2c0xwYkpXZXdhRWJYejY1UUUzd3FzNzhFWGZ5OGhmSjROODVFTm41R0J6djFFYUtXUW80Xzg?oc=5</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2289,106 +2289,106 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-06T17:26:58</t>
+          <t>2026-02-11T10:33:10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Diálogo y cooperación, fortaleza de relación entre México y Estados Unidos - El Diario de Sonora</t>
+          <t>Subidas de precio en ArcelorMittal por la mejora regulatoria y la previsión de un ciclo del acero fa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>El Diario de Sonora</t>
+          <t>Bolsamania</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQNTBILXVLc2NmOXNENms1NEowS2lfeVNRc1JYd1dUX0hLcVhSV183dnJzWWh5SW9MeF91Z25kMno3LW0wQ1ltVllZTWNJblFNbjFfQ3hrX0wtMHBaaXBzSkFrR3diTGdYX2pCeGV1ZzVYNEFkLXVoY216WFNwU0R1NDlSSk5WRnQzenlXb1owVlluUnlRZzhOVE5KQVlYZnFPWl9FUVdYZFcwR3NxTjNjOE1hWEZFWUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQTWFRMmQ3TVRGVXFSeTQ1dmhUa0NvR2RsZDdhTVJoQlZRbld4dzBXSmJOZU84YXNxbENTdTEwTDVxWjdvSXNCVFotR1VSV043MzRCNGVUU0lJc0tuR2dBVDNyRXJwbEU5X202bGVUSEZncDk2NVpWeV9GTmI4WEZ1X0d1Sm53ZU5HRlI5TEtWaFY1YUFPV1FCVFljQURpOTVJaDdNT01lV0g1Q1l2NGs2UmhHeHFWa1FiTVc5R19uRzJXbmh6RkxPdHZ0a1IwSXF3bkxobmdBdUh4QUhZcVHSAeMBQVVfeXFMTWt5b3dxbWVINkMxMVpoVlBBSk1JVF9iSnJwN05uRFQ3UlNuNElfaEtpdU9ZRlU4UEptX1hKbnFYLUJtUEh2eklKMnE2UmlEaFVRcGdhb09mcERadEhjaml4azExUWdpdFFkQU4wMFZ3czR0R1RpakhKUHdOOWlMUUtzRUNkcTc0WmoyeW1xSVRMeDFMbjBQTlhtbi04RWV4bWJNb1B3S2x4eUl6aU43Q214d2tCSFlpMnB6VENxcGNZcDhKa2U4Slo1b3VGdVNWWjl6YmQyTmxCTTFIQU82VXJRRzA?oc=5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-06T01:00:44</t>
+          <t>2026-02-11T09:40:09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Argentina firma acuerdo de comercio e inversión con EE.UU. - dw.com</t>
+          <t>Macron impulsa el horno eléctrico ArcelorMittal Dunkerque como modelo de acero limpio - ECOticias.co</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>dw.com</t>
+          <t>ECOticias.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxQV3NNdWcwQk1RMjFGMnkzUmVXbld4N29wX2N1d0ZBakdzNHBsWDV1NnVhY1ZOVHpEV0J2SzNQQURjdmRQaDhabkRXcTRxSjltcjQ3amJHQzZGSFBLVFRwRVoyLXFRQkpja2hZQS1XLV8wbmxoRlJ4UWxQRmMyTVpOcXNWOEhwYnpCdWc0NXFqUnJOOXhPS0owSkpB0gGaAUFVX3lxTE13NFZoWVpEYWdseWJOcUgtY1BoTkpqR0RIclNhaHpnUVp6dkdxdUZBcDFIM01CLTEydnhJVzd6MVpWUGNieGxOUXgyRm9tRGVWdnNuM3h5TnQ5YTlfWDJBRU5NR1NKQmlSWXJIQWZ6Q3hhQU9ZeWg0dWd1WEx1TG5mb1VzLTBGeDFwdmlzMVlBaVk5d0tlQS1YTGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTEMzOXpVS0ZadDNOZHFlRFF1ckoyazhRSHVRQ3ZWNzRwS19lUmJLZkFQYnVncHZfZlhTQ1VGaDdJMmQ3WjFzLUYxZm40VTE1ZHVVN1duVFdCMVpROElseHJ6V09tTjZ4Q080MzlGZmNwUFN6NlNGMW43Q3ZRYktwSjN1Sm9JTTBZVGtnTlpvQmctX2c4UzRVUVgtUmpJZw?oc=5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-06T00:26:00</t>
+          <t>2026-02-11T08:52:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reliquia del protomártir San Felipe de Jesús estrena lugar especial en la Catedral de la Ciudad de M</t>
+          <t>Precios del acero verde en 2026: primas de hasta 170 euros por tonelada en Europa - El Boletín</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ACI Prensa</t>
+          <t>El Boletín</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNeEUxUlVBbHMwclBWa0VOSlF4S2J1RVR1TGpxMEExeE1ZM3JxTnRaSkpaeUVlUzBVODdqYzVLeUtKZzhNcTNUMUZTaDJPN2ZtWXZFYUh4aWpXaDc1UnUyLXg5V3BvSGNUTW53QnFOLXQzWGpyeHJjYngxLVFBTHVyTFA2dGJ1OFhPN3Y5RGMtM1F3MXhfVXBtaXE3Zm5QalA1ZzNqZzNZTXVXVnNGczBxTURhbXdOT1A4bjdZNG1nTVZMZ0lG0gHKAUFVX3lxTE9KQy1UVFJNMVpwMFhrMGpXLXllRjladDlWT0hiZXRqRDdoZHIxNkRwSlRlNkcySEg5OXFpcjliTl9ZNHRWd1h3c2ZNQ1NOOHMwc0Jkb0FxMGZFMzNnOVFjWTlxQmF5T1RfbkxtX1VSdVpEV0RpLUtLb3BEZFdFOVBYaDZQODFHLVlrbVlkUWl5YW8tMjk4ZV8wTE8wdkFHTFVIYmFTb1o1UTZ0VHhKXzF6Rnlnd3JRUUl3MUU0MmVyQzZmdkpWUS1sQ3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTVZGRFQ1U2lrT2RYdzNINEFxLVIxV2M0bTJ2OFo2Y1EwRzJsR29BM3lhVlZVNm5DdldTQTZkZ1FNbnBZZUFqSnRhVlMwVUJmSERCUU9NazhqRXNrUzZfbURxc0k4SnFUekNpZDhQYTFEU2NNUDU4OWUzN2NUSGx4S3F3bWRTRWtIODRYVXN5MmZQUzctUzlHOXZUZFlMbjg4ZTl4TzdHQmxxbU3SAbABQVVfeXFMTjBYQWJtRjJsNnJNYS1RaGRNY1UxMndXTi00Y2Y1QzZ0emtJWGtUNmp4a2pnd1RXdmdlZ2NMeGJRNjU3S2QyM0oxNm82WlRaQXNsLUt4b0x2SklwWG9aVTVkWDBURTZ0TWxZQVJ2RzNpNmYyT2x4UEZCSnFiT2lETkY0UnY2RDJTemg3a1JCQmJJTlNua3MzcFBBOGpVeGR5eENBU3I1c3dOZU5keHJTY1A?oc=5</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2415,22 +2415,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-06T00:00:00</t>
+          <t>2026-02-11T08:05:37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>El día después del acuerdo comercial con Estados Unidos: dólar estable y rebote la Bolsa porteña</t>
+          <t>Minería de México acumula caída de 7% con la 4T y entra en proceso de redefinición - EL CEO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>La Nacion</t>
+          <t>EL CEO</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/economia/el-dia-despues-del-acuerdo-comercial-con-estados-unidos-dolar-estable-y-rebote-la-bolsa-portena-nid06022026/</t>
+          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1MVGU1ZG9BYTF2T3lMVm9JME10SlY2ekMyUThWS1RMa0hjUk9BMy1uQ0s3SHdVekVhMHp4RzRaX1d5LUhMUUVNSXJtajBiYk9GYXRXRVFmUWJYWWxMcWZDWHo2eG9JcW1L?oc=5</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2457,68 +2457,68 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-05T19:01:53</t>
+          <t>2026-02-11T06:37:32</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>El dinero que usas todos los días cambiará en 2026: así serán las nuevas monedas de 10 pesos en Méxi</t>
+          <t xml:space="preserve">Precios del acero hoy, 11 de febrero: El mercado interno se mantiene estable, los precios mundiales </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Xataka México</t>
+          <t>Vietnam.vn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQekdzejQ4OGZXTFhiYWtWVUFZeTk5eXJaNjhBUTZHX0hxSHZYM1hKVXFRX0MxUEJ1dXYzQWgzSndpVFYxTFpRNDBLbHdLWnVXeVY5X3l0Tk9ZTC01bjl6UFNaZDBIOHZrODR0dlpzd2lWUUNzWE1IdFhPOHFHSnhCOGtiVUtrLWF6RUhWRUEyemU5MzZuQVNzSGtBbi1wb3VUVXlKbWxXMTYyZDhLSmVqc2h0WDUwQdIBuwFBVV95cUxNRE5Gc29RQlBCZkExenE5MTREYWRjWlEzWndsYXNJb1dhRVE0WEdzbzByeWpubExzZGlmOUxVZUxrb0x1cDRZaklLX19meVhrVWh6RW0zUzFYeHpUYWNhWWx3XzJ3RzA5OXVlRWZKM0JUVTdtM1ZzYktCc3ByaXAyYmVnd3ZYckhiSlVkSURybWowVzloTmxIU2dzM3hpc3dLY0ZyQmZfVWV6MVJKOUcyajdiUXVwNVFYTVdz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOd2p3a3JQZllFSTlQT3lOanp5MFp4SlBOR0hZRkVTZVVhZlQ3T3RpR3NUYXB6eG8wT2xiak5TNU9wcldCNnYxUXBMaVlMUEZOX2x6R25WRk9zOGpmSFpaSzBaYVFMUW5vV2M4TGVqaXI3SlBzdzViTERFNzVqLS1TcGZNZ0FiWjV4TU13QU5qS3ZIM3BlcXNZZnN4RkNvZw?oc=5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>-0</v>
+        <v>-3</v>
       </c>
       <c r="H46" t="n">
-        <v>-0</v>
+        <v>-4</v>
       </c>
       <c r="I46" t="n">
-        <v>-0</v>
+        <v>-2</v>
       </c>
       <c r="J46" t="n">
-        <v>-0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-05T18:36:00</t>
+          <t>2026-02-11T05:14:35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Choque entre tráiler y auto particular deja dos muertos en la carretera México-Texcoco - La Jornada</t>
+          <t>Boletín informativo extraordinario - Impuestos Corporativos - Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>La Jornada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQOVl2VjVIU3NIVWVCblRVdGFwclBXZExXeEJrcWYyc3EtbHpSR1NKQUNDYUFpNzdUSkV2Um5nVHFFNFVUR25WdDFHZno0YXYtVjJpeVB3LUdsVmNjLXhQTnB2UGUxZDZhSUhxMFNrS3ZVbFFtQVpScFhVb3ByT25aQnNhcjZTd1BRa1ppUVNtM3NaV2ZJQjZ6eEhubk96eHYtQ3ZSTDFoSU1ZV242QzJPZ1pRZy1rSFVhQWJtV21vUFRDVWduLUJwbWoxQ3FESHRFXzk0UUJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWk15VjJ4SnNUczEtRWp1ekM1ejNfRzZqblBKVzhYSmNGUE5rSFpiVHFsVVlXYVpCV19rN2ZKRnp2alB6VmFxdHZLMWFXWmh4d1pJUm5rY2VHWGhBdWU3cmVjVWFJTENwOWtWSUl0THQxa3dzOTAxUkd6X1Y3TWcyUFNSLXFOM3R6Zkc0T3BZNGNFanM2Q3MtdXVPU0ZUWnJyTTZmTmd3Q010RXZyQWtBd0pJeXBDVElLT2t1MzFMUQ?oc=5</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2526,41 +2526,41 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.78</v>
+        <v>-0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.52</v>
+        <v>-0</v>
       </c>
       <c r="J47" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-05T17:07:00</t>
+          <t>2026-02-10T22:56:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>México ante el injerencismo de Estados Unidos en Cuba - Cambio de Michoacán</t>
+          <t>Sergio Argüelles pide más inversión en infraestructura logística en México - Pulso Diario San Luis</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cambio de Michoacán</t>
+          <t>Pulso Diario San Luis</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQS1AyRzFaejdCbXlISHQyR3NwbURiTXQzNmowWjY0ekFJb0RTaUZONWhrUW1MTWpZSU1FM3FPWFlVdzNZY3ZFZW9BUDdIYmVlVGY2X3kwUG9FZ19rLWFSTW9lRjlxZ3BiSzgzT0xZVGtZam1LNlZ0eWU3S19LSlZxTzRja0x5Z1VMcWo1QlJhUHgxZ2JVN2tMOGhXb3MxV2fSAacBQVVfeXFMT0hwTklVSXhVZFZRaEp6TXM1VHdGdll5a0xwWm84cEVDYmg5b0xEYWhOUkd5WWcxcVZFLXliS2VMUF94YW1nSXlSZ3hicHNpV3JiN3JSd3BzLXM0NjJJS3ptZHFhM2xZRzNRcTFucllqTVJWNThOTDRjdHRIdHhPNEkzQWM4cmlmNHNLbnpvZ1d5LWZUaURPeVNiRW9PRDU3ZUhRUmxydm8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNld5eFFPX180dWRwNFYycmhLeTNTMG5vS3JUQjZqZlpsYVlXc1RRRWh2NTdoWE1ZSzl0RVhGNVJNRnlHUW5pQlVHdElvVWRtejdNS0lYVFRZNGllU0VCam5TeHdYZWdlZEFNX09TUDdISS1YaUNNMEJkNW8zSGtlRnlHTHlFUFhlaTVISGxmOFd0WnY3QjlpWkpRNm11M2VUTWfSAacBQVVfeXFMTjBiTlp2eFVESkM1RnRCUDlkWVF0dC16TGU3ZGJXQjFTTTliMUh2NmJ5aFN2cHZFTDNzang4V3FCZ3BkNWY5RnRkT3Z0YWZiWDliVEx1QnFSbVhiN1J2QktiSTFSc0VtcXdKcmNQQ2RnX096aEhJQUljSWFoM290c2lJa2Z4djR3T083cG1VRHk1Ykd3RnUwU050eGFQNS1ZUExpdXBiQlU?oc=5</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2568,83 +2568,83 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H48" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I48" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J48" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-04T00:00:00</t>
+          <t>2026-02-10T18:37:57</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Paolo Rocca sienta su postura sobre la licitación para el gasoducto de Vaca Muerta</t>
+          <t>Boom de zonas francas de República Dominicana impulsa demanda de energía - BNamericas</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>La Nacion</t>
+          <t>BNamericas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.lanacion.com.ar/politica/paolo-rocca-sienta-su-posicion-sobre-la-licitacion-de-tubos-para-el-gasoducto-de-vaca-muerta-nid04022026/</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNMW5JS1ZydU9mTGk2YU9pSFpGdDR1LTdCSjJPR3NrXzk3Tko1TWJaNWNjYzRMcG92SDU3WHA4MjRmMXVjX2JhRlpCZnJLT1NxeWZocGhnWHFQMzVsZzNvQm9zTFhEUm5Ic1pFT2k2VlE5dnZRa05CdTZ4ckFPYmp2bG1WSFI5ZmNZZWNjRHpvc1lyOTdMN0IxYm42cWc0UjUtSnZGZUR1a1h2RUZHXzJyOEQ5UTJzWWg3UUxPMUJPSQ?oc=5</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-0.04000000000000004</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>-0.1200000000000001</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.08000000000000007</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.08000000000000007</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-03T00:00:00</t>
+          <t>2026-02-09T08:01:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cuatro décadas de BASE</t>
+          <t>La automotriz china BYD presenta una demanda contra los aranceles de Trump</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>El Financiero</t>
+          <t>Aristegui Noticias</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.elfinanciero.com.mx/opinion/de-jefes/2026/02/03/cuatro-decadas-de-base/</t>
+          <t>https://aristeguinoticias.com/0902/dinero-y-economia/la-automotriz-china-byd-presenta-una-demanda-contra-los-aranceles-de-trump/</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2652,352 +2652,16 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H50" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J50" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2026-02-02T00:00:00</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Mercados: caen bonos y acciones en el inicio de febrero, y rebota ligeramente el dólar</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>La Nacion</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://www.lanacion.com.ar/economia/dolar/mercados-caen-bonos-y-acciones-en-el-inicio-de-febrero-y-rebota-ligeramente-el-dolar-nid02022026/</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>-0.9239999999999999</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>negativo</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>-1.6632</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-2.2176</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-1.1088</v>
-      </c>
-      <c r="J51" t="n">
-        <v>-2.771999999999999</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2026-01-28T00:00:00</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Acereros y gobierno empujan blindaje de la región T-MEC rumbo a la revisión del tratado</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Milenio</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://www.milenio.com/negocios/acereros-gobierno-empujan-blindaje-revision-t-mec</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-5.100000000000001</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J52" t="n">
         <v>-1.7</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2026-01-26T00:00:00</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Techint evalúa presentar un recurso antidumping contra la llegada de tubos de la India</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>La Nacion</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://www.lanacion.com.ar/economia/techint-evalua-presentar-un-recurso-antidumping-contra-la-llegada-de-tubos-de-la-india-nid26012026/</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>-0.6400000000000001</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>-6.400000000000001</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-9.600000000000001</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3.200000000000001</v>
-      </c>
-      <c r="J53" t="n">
-        <v>-3.200000000000001</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2026-01-23T00:00:00</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Tecnológica uruguaya Arkano sella alianza con brasileña Math Group y acelera expansión en el país no</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Diario EL PAIS Uruguay</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://www.elpais.com.uy/el-empresario/tecnologica-uruguaya-arkano-sella-alianza-con-brasilena-math-group-y-acelera-expansion-en-el-pais-norteno</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2026-01-15T00:00:00</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>ONU exige saber el paradero de activistas mexicanos desaparecidos hace 3 años</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Aristeguinoticias.com</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://aristeguinoticias.com/150126/mexico/onu-exige-saber-el-paradero-de-activistas-mexicanos-desaparecidos-hace-3-anos/</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2026-01-15T00:00:00</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Ternium adquirió Tubos Argentinos por US$24 millones y suma capacidad</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>La Nacion</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://www.lanacion.com.ar/economia/negocios/ternium-adquirio-tubos-argentinos-por-us24-millones-y-suma-capacidad-nid15012026/</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2026-01-14T00:00:00</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>CAP vende filial Tubos Argentinos a mayor grupo acerero de ese país</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Latercera.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://www.latercera.com/pulso/noticia/cap-vende-filial-tubos-argentinos-a-mayor-grupo-acerero-de-ese-pais/</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>-0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-01-14T00:00:00</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Grupo CAP vende acerera en Argentina en US$ 24,4 millones y sale del mercado trasandino</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Www.df.cl</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://www.df.cl/empresas/industria/grupo-cap-vende-acerera-en-argentina-y-sale-de-ese-mercado-para-enfocarse</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/Output/reporte_REAL.xlsx
+++ b/Output/reporte_REAL.xlsx
@@ -437,7 +437,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.10</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-17T11:52:24.794483</t>
+          <t>2026-02-19T12:27:06.555745</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.6715306122448979</v>
+        <v>-1.869022727272727</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-1.021224489795919</v>
+        <v>-2.780238636363637</v>
       </c>
     </row>
     <row r="4">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.433265306122449</v>
+        <v>1.267806818181818</v>
       </c>
     </row>
     <row r="5">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.3092857142857144</v>
+        <v>-0.6887159090909093</v>
       </c>
     </row>
     <row r="6">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.8225510204081631</v>
+        <v>-2.299963636363636</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,12 +609,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-17T07:36:00</t>
+          <t>2026-02-19T17:41:46</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>El nuevo Plan de Inversión en Infraestructura para el Desarrollo - El Financiero</t>
+          <t>Aranceles de Trump no redujeron déficit comercial de EU</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -624,53 +624,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNTm5hR1pVWG1YLUFWd1NRdmJFd1BLWS00OTBHdFhkSmRMUktvUWwzQjdQOFBpUzVtWmktLW03RnpFTWxXVThBc3haWWtSNUpYRmZHaWI3S3VaSVVjOTd5R1FHSXMwalJjanVOOXZIZzV5S2RnWVBac0VwNHZnXzFOaEVGOEFXLU1jN3JaWnVPWVlGSi04R1kwclhDSVBGdGlaTW4zeGhUQ1hZRUcyM3ktMFRGOWJzWjVJUDhwZzVCQXlsR1o5QnVoa2h0MjI3ZnJjSzFz?oc=5</t>
+          <t>https://www.elfinanciero.com.mx/bloomberg/2026/02/19/aranceles-de-trump-no-redujeron-deficit-comercial-de-eu/</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.26</v>
+        <v>-1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.78</v>
+        <v>-10</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>-15</v>
       </c>
       <c r="I2" t="n">
-        <v>0.52</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>1.04</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-17T05:01:03</t>
+          <t>2026-02-19T16:15:19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Una publicación unifica la terminología sobre economía circular - Residuos Profesional</t>
+          <t>México lidera las exportaciones a Estados Unidos en 2025 - Mundo Ejecutivo CDMX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Residuos Profesional</t>
+          <t>Mundo Ejecutivo CDMX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxPRVg4YmFpNDNDemhNZUN6V0VkYjBhQTh6b1dnaTB0UHVIMUxPRFNpaXRPeV9sWWo0YjlkTWJYQlJJMk90UF8zcVY5aFpVc25pSjJUNFJlWTZBU0xCRWd4QXVTSTJKbXNGSkZSVTFhTlZlU091bXZ0ZGc5OXJTQ3FOeF90NFlZOWVIRnJPNC1mLVA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPRW1SbWRUTlRqWFZXVnd5TFdidWRGUGxkVm5xWi1jTTJNbVcza01KbVZwdVdERUpUNGFBOTVEX3huWmNRZXVwZlhXVE5aVmdUS2pCNVdiSlVvMUQ4ZWRIMXNyeTk1WUJ2VHllM3BfdnJKdmdLVktrLUlCNDF0QVBXbEgxdHdvaDNYR2JLOGdCRVFudExETkR3QWQ1NmwxTnBVbXJnQkVTOA?oc=5</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -678,41 +678,41 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-17T03:47:00</t>
+          <t>2026-02-19T15:26:10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">México y Canadá perfilan plan de acción económico; incluye minerales, inversiones e infraestructura </t>
+          <t>México se mantuvo en 2025 como el primer exportador a Estados Unidos por tercer año seguido - Yahoo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Contralínea</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYTFkSHN4SXBxX1J4TkZ5WXNJY3Z0YURYTFpVb19URmhpakx1a25kQkxRV1Y0MHVJS3NqbzQtNE14SXB1RUVOM3dBZU0tbm9GUW1tQ2VoWVRtcHp6Z2w1UTRDTkM4am9KZ1JYamNOVGZUVjZCMUVmcEljNjdkNTlhczh3NW80MGh5c1RGWmVteWJ2eTlxQjhiOG8zYlBrdFRWQVRwZjB6a1dBSXNHeE1kOUpTZWJEYjZaajdkSHZBeTRhTlpqVE5venBHR3poZm42Wng2V0EyUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPRjFPZ29DVVRXUkJ0blhqWkJSVlF6eG5hZnk1OVREbHJXM2s1UlZxY0ZVbXJheTlTQkItelRhUmtFWFVMbEJtVzdXNTNNMXRabDJNWi1YaVk3TVh2X09UdUszUThJdVN0S2F6Qk1oazhYQ0pJNFZ6YVZNNnJ3WWJjcFk2NUdobHlqUkoyTWwxV1dIMkdDOHc?oc=5</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -720,37 +720,37 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.78</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>0.52</v>
+        <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-17T01:57:00</t>
+          <t>2026-02-19T14:40:32</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CFE e ICA supervisan infraestructura eléctrica del Estadio Ciudad de México para el Mundial 2026 - M</t>
+          <t>México se posiciona como el principal mercado de las exportaciones de Estados Unidos por primera vez</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MVS Noticias</t>
+          <t>El Economista</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxQTlVOWVc2MnpCOW45ZFhwVTRMbFZ0MlZkbGxTM3Z3NmJlQl9TcmE4ZzhpY3dJR0dBVmtzdFI0S3FyVTN3NktRN1M5bGZuV21qUkZrVl9pSjJkSnRNcmY4X0VFUTJOUlVtWFNCajY4VUgyeUVVVm82cFM1c3JtVjFGcFRkaEd6SG9rTjdtd3FGZ2N1aFpmeUNZcVBhbkhKZDVlNG5pQWUtaFVrVzdPMTRtY0F1blhGNEs5MFhyY0xyU0xyeHNQSUpzTHBjSzBPUDNELS1wLV9jNEZmb0lNVkhmRXF4a9IB4wFBVV95cUxQTlVOWVc2MnpCOW45ZFhwVTRMbFZ0MlZkbGxTM3Z3NmJlQl9TcmE4ZzhpY3dJR0dBVmtzdFI0S3FyVTN3NktRN1M5bGZuV21qUkZrVl9pSjJkSnRNcmY4X0VFUTJOUlVtWFNCajY4VUgyeUVVVm82cFM1c3JtVjFGcFRkaEd6SG9rTjdtd3FGZ2N1aFpmeUNZcVBhbkhKZDVlNG5pQWUtaFVrVzdPMTRtY0F1blhGNEs5MFhyY0xyU0xyeHNQSUpzTHBjSzBPUDNELS1wLV9jNEZmb0lNVkhmRXF4aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPd29tRnJEMFN6eTd2NjViY1BkeDVoYjZhZmdmZGIwY3NZcjlsRWpWMW40dzlZdTcyaVVxUlF3bEJ2YUU5VnJZLXhkSllKV0ZjRll1WjktQmo0TWptM3AtN1J0ek50Z2N3S2NBa3BJVzNaQl9ZZU1tbEJpUjdjSXpPS042RG9zWEZNemdBbUFGcEM4eDlKRXdMOEhoRy1ob2JsR3czNjNOZlRKcExRa3ZiV2s0YlowMGo3TjFqNGlqLUhRR3ViMGs2WDg1alNvUF9HclRj0gHYAUFVX3lxTFBpMGV6SFA5bWc3SjB6NDBkdzFvQmNJb2Zaa0JDX2g5WHhoZkZOSV96SVNyc203Y0xYWHozWnoxZGdfRGNQeVpLNk1uZXFzdXJRM1BJVlB1TG5waUZTRC15aUFGTnNnUzlUY2cwTkFlNXRraEVRQlY2NEhrYzV2alN0bFZIaEpSU1g4MTVGTEpsOE9KRGpHT2M5U1ljd3VVSE9ld0RJQW5pbHR4ZFNBdndETF9oQVVLUTJFenRUNlh5U0ZNVUlEdjc3RkVYbWtXZ051WEpIWjduTw?oc=5</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -765,38 +765,38 @@
         <v>0.78</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I5" t="n">
         <v>0.52</v>
       </c>
       <c r="J5" t="n">
-        <v>1.04</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-17T01:24:00</t>
+          <t>2026-02-19T11:04:07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>La CFE supervisa infraestructura eléctrica del Estadio Ciudad de México para el Mundial 2026 - Infob</t>
+          <t>Nearshoring en México enfrenta límites en infraestructura, energía y talento - THE LOGISTICS WORLD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Infobae</t>
+          <t>THE LOGISTICS WORLD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNVVFNY0NHcFBNQXo1dGVwNEdIY3RWNGM5T3JPQnNORU9idUQxRmY5cHdtMm04eG1sWUJoUi1aZHNiU1dtNGx1OEM2bzBwNFNxa1Nuc1J2am95RDRVejBNTHBXMkpvWjNnSWhVNlhmOTZwalNUbURoc2NONjZzSTN4ZTU4eUQzcDRzQWtxOGJxX0lpWEJ5MkFqWWxURjN6Nkd6MGlxQnJjVWtkcWFsdzVXZ0tManZVSTM1RDNjVkkxYUVvbVMwYXdlNVJnQU05QlR60gHrAUFVX3lxTE9oaDBJVElWTHAxS2ViN2xMbHpmb1QzN3ZsNjZ2Q3o2R2pfa19MMzhEYV8xMVB1M3dudGxmbjI5TnViTElrbzMtbzAwbDNyVVU3dE9FTzZ3NkF5WWhvNUxqem1mN0E4d2ZMQlZ2VUNTZElJUF95N3BLR2NFT0tCeWRQclMyZngzNllIYlJBdEQ5cFNSemNXbGloNVhOcmZ2SVczVlBrcUVKd2pPa3ZTQmFQNmVvREJVSWVEckhXaGJhcVB3LU5WVkk0UUJ0M3VITDJBWFpwcU9vdlpsb0lKOWRFdC1DNEFEb2NaSjg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxQMmVBSEx4WGwtNGxUM1VPaGxSR1c4bHdSTjNHYnk2YTF1dDBKWTFsZXZJNFhuV0NoUDFJWkx5X2p6V3puUzFEZ1Q5Nm9kOTRKd0llUHQ1c2VGN1RMaDV2TFQwYVJHRUY4WFZ5MlRDX1l6M29mdnhuYjFHbHVEVjlySUNiMGpjNE8tcXNGekR1ajU1cnAyOEhLUW56Vk9FQ0FETmhVMUc2NV82S3VpRXd3X2oyWUZEc0Z3QU5YR3REaHgwSzRkN1E?oc=5</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,83 +804,83 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.78</v>
+        <v>1.68</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>0.52</v>
+        <v>1.12</v>
       </c>
       <c r="J6" t="n">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-16T22:03:44</t>
+          <t>2026-02-19T08:56:25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Confirman una inversión de u$s 7000 millones para el desarrollo de megaproyecto minero - El Cronista</t>
+          <t xml:space="preserve">Fitch advierte riesgos en Plan de Infraestructura: Estado de Derecho y T-MEC alejarían inversión de </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>El Cronista</t>
+          <t>El Financiero</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOaF9zMlBqQUVxeGNXSEZUSnZTWjAxbFB6YUtRcWlmaTRfUk1vQWg0cFJ4ejlzbnE3SW9pSGFqM1BkS3RTZ3VocW9oMHBPaGJFYW1FOUM1MnR6V1pzWlpHMU1xVXRIblN2MEw4UVNOanhNVm5tZHJydXE0R2tKSTduVldGOUVLY3VJSGtvM2J4eTFqSGxDWG8yQkk1aU00elRDWlpaQk11bGQ2WVM5WnBLbWNFTkRJZHUtUFZ3WU8xM01qRW03bExFMUVfcDVBZzBIZEVBaXNfONIB1wFBVV95cUxOaF9zMlBqQUVxeGNXSEZUSnZTWjAxbFB6YUtRcWlmaTRfUk1vQWg0cFJ4ejlzbnE3SW9pSGFqM1BkS3RTZ3VocW9oMHBPaGJFYW1FOUM1MnR6V1pzWlpHMU1xVXRIblN2MEw4UVNOanhNVm5tZHJydXE0R2tKSTduVldGOUVLY3VJSGtvM2J4eTFqSGxDWG8yQkk1aU00elRDWlpaQk11bGQ2WVM5WnBLbWNFTkRJZHUtUFZ3WU8xM01qRW03bExFMUVfcDVBZzBIZEVBaXNfOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7wFBVV95cUxQXzI2Tzg5aUJHVGhpOWhsYmtSQlU0ejRHLUJ0ZUhRMWF5NVBFaVg4TFd0SzdORnVfV1Y3ZXpSNjVjUGx0RXhyNG80YXJ5MGN6N2RGOTRCdG5YYWd0ZXU5emZxcGFiY1NzVXdRb1d4eklVYUdDUlF0Q1M1N1RreEtMRTdHaFBLVHBkU0ZZczhodjdnZGdnZUF1N0pVTDE2Q29OX2MzMUdORVZhMHVZcUMtYWtjVEQ5WmdIVDk0N2hVRHVtVlh0SFROaTRPdmQ1WmlJbnRVcEU3WV9nbDhpMDZqOHNkT0FLd0JCQjN6UmZBbw?oc=5</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>negativo</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-0</v>
+        <v>-2.22</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>-2.96</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>-1.48</v>
       </c>
       <c r="J7" t="n">
-        <v>-0</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-16T21:56:00</t>
+          <t>2026-02-19T05:00:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ebrard anuncia plan México-Canadá en minería e infraestructura - La Silla Rota</t>
+          <t>México y Canadá buscan reducción de aranceles al acero y aluminio - La Razón de México</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La Silla Rota</t>
+          <t>La Razón de México</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNOFMxYjBoenZWX00yVzNScWtNSUtWdTd2d2xYSVVNVkM2emFQOVF3QWNVX3E2VVIyTlNZWHBCWXZhcjEybWxRdWktbzdCaDlmT1UycElLUWxvOHNIdm9hLThEWGYzaVZMUkc0cVFqaWN5SG9rY1RieEpxcVNWSFVROF9mQUg2WFA5cll0LTR3THo5UFlndmxua2s3aUFlS1liOEx5WjZjRzZ3bGQzTlN4VS1FekFSUdIBtgFBVV95cUxNOFMxYjBoenZWX00yVzNScWtNSUtWdTd2d2xYSVVNVkM2emFQOVF3QWNVX3E2VVIyTlNZWHBCWXZhcjEybWxRdWktbzdCaDlmT1UycElLUWxvOHNIdm9hLThEWGYzaVZMUkc0cVFqaWN5SG9rY1RieEpxcVNWSFVROF9mQUg2WFA5cll0LTR3THo5UFlndmxua2s3aUFlS1liOEx5WjZjRzZ3bGQzTlN4VS1FekFSUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPYkQ4VG4xN3hYX0t6dlY2Y25FS2tsOEVKUFhXMG9vU2ZROE9VQUJCbnllQ21rLWpma0hYNk9JMXItQmp4M3hwMHVMaVA5WmZub0lwalp0YVNzaEhqVTdoZTZETi0xSVZsVU1MZTExN2dTR2VyT0E0VGtKRk5EbDZKV0hLNnJyc3k2Ui1sUnZ2SXQ0TnNRM2F5WHVLUHNqRFV5NHRVX2twdTRFZHlYd3Rhb9IBywFBVV95cUxPWEZTcDBKaGdndTlyV0J5YW0xRjVtRmdQcjJGc2UyT09tNEthdFE1alN5OTAxTG1UM0s4WXVXQjZkQ2k1TmJ2UGJyQi0ybGszVVhFeGVObC1PRjBXVWVrcS1uYnpoQVFSZndJMmNvcmVrUURnY21vUGFKNnl5NThLcU9ndDNYQzM3V2RsR2dNOTlmV3hTenM2QkFCbUM3eTlzVFR4ZXl1enNwbjlnLTZmZFdvb3pDV2tyb1RHT19jUDVPck45azJ6MlBTTQ?oc=5</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -888,83 +888,83 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.78</v>
+        <v>-3.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.52</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.04</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-16T20:59:00</t>
+          <t>2026-02-19T04:17:31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sector electromecánico en México busca certificarse ante expansión de inversión • Infraestructura - </t>
+          <t>La industria europea se prepara para lo peor: el mayor alto horno del cierra para mejorar su capacid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Forbes México</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZ2xDZWlKWWJZQmxhQkpnVGFEcnMwMWdaX2JhZkNaNlJBUEF0cmNMTkxsQTBjQ3N5YU5WSFkyS2pOTGZZS0kzN05oNlNLTGt0WVN5TWNnZFE4dE9jbDJYRkY2U2diT1ROVnF1NUcyb1h5WW03Y1ZSejFuRU9TcEkzRHlSQ25EUVAyZEkwRUZoNl9DNHZkalFaU1VtenZpeU5LaTNzaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggNBVV95cUxNM3VkX1YwVEx1NlFYWDRHNlJoSS1fMTUzQmtlNVh3bXcxREMyS21QNDVuQVVrOWtaZXZPOFhaZkdjTFpTWnBWZzFJR2FkZDN6NEFiak4zYy1vNjNaQkVpZlpkbFk1Z3hJLWNjM1BFSERzMkdxRl8tRXFjRC13dDdFeU1DN3NVQllOMC1HUTAwcHpCb0J0S211QnJLTDl6QWtVM3Q1MUlKTXdINlV0NEN1X05seVdURlR2bmVrRjRPaTZlUVVhTkpKTS05NVpiLS0wckcwa1p3bnR4enpQaFI1cDRaWktTeXg4aFBBelZfVlViaENpdTc4bkFTQmZLM2NVTWpCQkRWUlFSNF96ZkNJUHVVMllNTkhoNVRWdlk5VlJFZThWRjlQR3o1ZHlzc0oxLXlIUTBJYmowWWNWNmdob2tBSEhaUTU4eUFubzVpVnJDTU9HdlFDREVRZ3RxYkhNSEFEZGV5QlZ3VXFHdVlVU0VYZklyNm5KR2RHei1STDZDdw?oc=5</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.78</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>0.52</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-16T20:57:25</t>
+          <t>2026-02-19T04:17:09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>México inicia investigación antidumping contra acero de EU, China y Malasia - EL CEO</t>
+          <t>Directora de regulación de Solid Biosciences vende $24k en acciones SLDB - Investing.com México - Fi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EL CEO</t>
+          <t>Investing.com México - Finanzas, Bolsa y Forex</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQb2ZfazlCdERaTXB1SHF3Wm1lQ1BpRE96MFVZZ1liaEtyM0dsY2ljaERobDFpU0RHWlBpMVA3NWxTREhVQ21fNVVGdWV6T09qMkUtUVFHY1VYZHhOZldwSUgyTDJBVk5CemNZM0VLNXNMaVBSOVlwZUdyR3UzZDAtWHhiTmxHek9lNWN6aURsQTR6aEhISUd3bGJlU0ZLaDRJMHR2eA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxPZDZVREtXREdUSUR6VXhIMkRHMFI1QVA3dkE2bnVYNnFhc1FnVVZjNW1NYWRHc3hUSFlScUVnVkhZdUtpd3dBX2k0MWE3QnNWaVV5bEVNb2dyZFRVbDl0bGNxZHY3dmNLUkEyU3hxd21qbWZxVkd5azFwaHM0V1FPLXc5OUtmUGpRU3FkbDJyb016YTlXTEpEZHVrZzRMX0FJTWVkRWJOVTlsWmEtYTZCbEYzZzlQWnAwdWhfVDRHLVNvMVFoOHZMNWppWnNHRklR?oc=5</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -972,83 +972,83 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>-3.4</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.100000000000001</v>
+        <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>-0</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-16T17:15:03</t>
+          <t>2026-02-19T02:56:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chile: AZA eleva producción de acero verde y reciclaje de chatarra tras inversión histórica - BNamer</t>
+          <t>Trump sube a 50% los aranceles al acero y al aluminio; le pega a México y Canadá - MSN</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BNamericas</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPa0w5UGJUSUkzel9DcG5rcE5FSVpIc3ZtRVN1cXA5ZS1vS1ZXMGJYN2sySkxZWkF0cmZJMHZyMG1aNTdNZ3U1bjJSck54dDFMZXVpUGlJMXUzVzQyZ0JQaVlva3EwcjVTZGRqejUyRkFPaF9KNGxhYjk0cXFKcTU5Sk1HS3JLN1FwaF94RWV0RDItNkJnVktiR19ETXl2YzRaZ3FIUS1hT1Q3b0pZTkZUeml0ZUZJal93YlkzWjBLamgyUzBwM1hTa1FEYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiugNBVV95cUxQaEtBQmYtdmU1Ri1pckE0SUVJQTVtcHd5SjNLWE82N2wxSi12ZTFkdXlrdFJLZ2hKYjFwVHZNSkt1MnNsWi1tZmhwaG51RnFLV01KQm9mUmVEdVUyV1E2SzBMck9yb2k3WlEtc0ZQckRSbG1PZ2s4Vm8tT0Zia0xGdDRqZi1jVTdPV0JraVI0X2ZZckZuTG8tMDhyd29YWndNNXd3WURsSWt2YUtYMldFT1owdlE0dWVaZnAxWkItTGFzM0lWcjJNT2c4UXE2WnZwbjR5UWVNdUtNbTAxc3ZNYWVHM0d0WUJvenZnS19ObS1fLTJyX0dzNE9FbDB5VUZtWmVlazF6NnR0Sk40UmNnSEw1QXpRQVYxUDJFUWo4STIxa09QYUhqY2Y4REJ3QXJnOEI5T2VuRWFySVhwTDI4OFpoMklHdWViODlCRVJSZzM0NnZTbFlCT19jcnZGWVpjNmptQlBwdDh6NjhJejFNSVVCVk1xeFdSTldCdGMxakVEeUQzVHBjVkxOT0NOc2hJSncxZ1cyRFdTYldIZGtYZ01sNFJYWEl4TFZnazdYb2lOazQtYXRtZDRn?oc=5</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.9899999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>-0</v>
+        <v>-14.85</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>-22.275</v>
       </c>
       <c r="I11" t="n">
-        <v>-0</v>
+        <v>7.424999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>-0</v>
+        <v>-7.424999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-16T14:04:00</t>
+          <t>2026-02-19T01:34:18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>México es clave en 10 minerales críticos para EU - La Jornada</t>
+          <t>Puebla albergará el México vs Ghana de preparación; afición e infraestructura garantía: FMF - El Eco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La Jornada</t>
+          <t>El Economista</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNYXpXaGN2em9DVzQ5S2N5Y1dDMlMteGhoUTVPQU9hamlNSTAxaHdub2hfZGQtSXFxMlNuS0laZEk3UUVlYllWYlNWR0hjVEJMU0ViclpKbkpfd19tWDE1MWxNQ3lUS3d2Sk5wQkU3VTRSRzYzVHBuZHdzWXVndERfRlAtdGh3bDV1TjBMc1Vrc3kySTBfZHlYMTd1am9vTGdNRU05QVJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxPbGZkb0FvdmU0cXIzblJlTVdhZjduLThXQzRUQkVGWjJsQXMtclhrTldleHgwR0xJb1U5bktqdU9NbEZWZ05SN2M2R2FtUTlNb0VSWW5fR3JtMGh2UUUxLU9uSXFhd1liY0dsc25BQTdVeHNIMXhZTXJLMFlwQzNXWWlkck42X3l0dEMtNzhJTDFDLW5JWnNkNUtlTGd4Y2tIaEtab290bWE5V0dWRDBvMVZVNTdpWUNKQTYxZWlreXlSOWFFdEtDWFVhal9XREFZMDE4bjlfMGtGdTdxdkHSAeMBQVVfeXFMT01HRGUybWhEWlp5c0hUaGpLME5DVnh0TjdiSW9lUnlTOW5sckVFZXNkUkx1eU0zMTIxdG91N2hCRDBJaEEzbS1ZTlhianVzRTdKVU53dTNoTHc5M2hiS0U2ZXg3VmhfcW5wWVc1bGxBYnBuaFViTWJMcGFxR005TzBMOGJDUVE5TjNxNDdrTGRYRGxQX1drbmt3c1hKalFjODFERFluQ1J5TDlpalhwRG1Qb0pBT0xob2dSOC1uZThUTlBkLXo2dEFDbUxPMmtYRTctemFmWFZLclpUT2tURTV2MTQ?oc=5</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1056,41 +1056,41 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>-0</v>
+        <v>0.78</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0.52</v>
       </c>
       <c r="J12" t="n">
-        <v>-0</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-16T06:48:34</t>
+          <t>2026-02-19T00:33:24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Japón evita la recesión técnica pero el PIB incumple expectativas en el cuarto trimestre - Bolsamani</t>
+          <t>Ternium inicia operaciones en dos nuevas líneas de producción; inversión alcanza 4 mil mdd - Industr</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bolsamania</t>
+          <t>Industry &amp; Energy Magazine</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxOUUR0Y0F0X0N2aktwTmkwMHBJVW9jV1RnVDVKa1pvWVJ0bnNsUWVucmpvZEdZYWtPQ2M1SnAwNTAxMEhVYjBUdGk5T3BzSzdXajNYbFo4bEk4cndwMUFLMG9GWVJsT3Mxc0Q3UWJIYkFrNV81Y3JqbGM5ZzkzUGNrWkVwOHNjWTFNVWZRWUg0dmN6NDcxNlBqX3RIU2dLdDRwSGdmZG16Y0lrYzEwZnFNbFRjZHJ1V3U4V083VXFONVV4TkVaVVpFM0JmZ9IB0AFBVV95cUxQNUFnd08zckdfMVVVblRDZlZ0eXZOSkF1dmpOZFNiZC0tUnBENTFkSmtJZV9tbXFKakFHWVIxYmFhbTg4QUJDTk5DazIyY3BGVTVfdVA4bVhuRjF3YS1ORDdxNWp1VjhCM2F6NE1XZ21VWmUtcTh3WnlZNnRPeDFZTE96RktUNWlaVWt0b0dSVDl1SjdSZjBNN0c3b0RaZjNLZkYyVFNGdXdXeFdMai1fRmk5aDNBa0FoU09oc0FWNDE1cVFjNnhxaUllRkRrc1pu?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQRkFZZFludmRHelFJVUVBbF9zcUp5djlJR0ZUZzI0RXdnbWVKNFhMY0JmdzlqVWNLQmdYMGlDbTJSYmtzMW90cG4wTmhJeG0xQ2JkNG9weVZPRjcxQ0pwRi1rWmFPbVNwemVkY3ZzOVUwMWFIMWpDT3MtLVNJUUhjR3BGaHdBcmF0NlY0NFRjVm5nV045aHRfeC15TTExOGdPOG5zZ1l2VDgtRVNIYVJrNlNRVF9WTmU3V3NlOFBIYXBOUQ?oc=5</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-0.3200000000000001</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1098,41 +1098,41 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>-0.9600000000000002</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.28</v>
+        <v>-0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6400000000000001</v>
+        <v>-0</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-16T05:01:13</t>
+          <t>2026-02-19T00:10:14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tras salvar el coche de combustión, la industria pelea para desmontar el mercado de emisiones - info</t>
+          <t>México ve apertura de EUA para reducir aranceles en acero y aluminio - oncenoticias.digital</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>infoLibre</t>
+          <t>oncenoticias.digital</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQYUF3LVVZU09lWmlfS0RtSDBNNWV2QUpoQkxkOHRydHhjNGJHa21KUzlxZ0NzMWppeXliZ2p4TG81ZjlaVVV4ZV9FTFpWSjlOZzJ1amVNdHp6RGRxRmIyYWdqbGpPdjkwRXl0dkg5YndOYlJSR3dLSXBVc3ViVmhLY1hISUhaV2pyd04zdDNhRFZqaUhXd3FuOGZtaGFCY01rR3lrVkI4YmROUWZmRHNPeUJObUtxdENORHNTamJxel9TU2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNSUExOXhHMGI5cDZpaGw3SlJSSHFmXzFwem11VF9QeXdKMVNLOXNuMi1lVk9vaW5GSTVVWUlELWdZYllTUGZyMkNiOVFxMlBHelREb0xPNFJSV3QxNG92d2VWX3pGUUZueVZFWmk4OWVWczZqdEx6SUxjb0xXenhiODBTZWVhbjgxT2VMd1ZRa2ZpUldsNXh0NHVBdFNjVUU1cUFaR2hLR2VONklNeGM4enE1X3bSAbQBQVVfeXFMTUlBMTl4RzBiOXA2aWhsN0pSUkhxZl8xcHptdVRfUHl3SjFTSzlzbjItZVZPb2luRkk1VVlJRC1nWWJZU1BmcjJDYjlRcTJQR3pURG9MTzRSUld0MTRvdndlVl96RlFGbnlWRVppODllVnM2anRMeklMY29MV3p4YjgwU2VlYW44MU9lTHdWUWtmaVJXbDV4dDR1QXRTY1VFNXFBWkdoS0dlTjZJTXhjOHpxNV92?oc=5</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1140,41 +1140,41 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-16T03:02:40</t>
+          <t>2026-02-18T20:01:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sector de la construcción en Querétaro reportó débil actividad en el 2025 - El Economista</t>
+          <t>Sheinbaum ve posible reducción de aranceles a acero y aluminio - El Universal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>El Economista</t>
+          <t>El Universal</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMmxHYXR4TXdIRzBkVVJIbHQyZ2dhWjVMeFE4YVdmd1RHZ1RnUzRuRmhyQVNBSHVROWdrOFNtSG9VeGFSUG1YSy1BVGVHUkJ3QmJsNUQ0Qmx0S0Vhd3N6SXBmcnh4LUNtS1hwR0RTR3ZWVEYybmx1OEFJLXpMSFowQTY0M0xJbnQtdWtlNEJYRG9uN0R6czdjTFNTTUtZYjB1WEZvTXdJWDNaUHozTEZQTUNMZWzSAboBQVVfeXFMTzNFdnd0Y29yWGpEa0x1UkljMWVvOU81dXZBa0JEN0NjblhzbTJycXpKbnNUMHNvQk5CVGh5eXZFVTlLSHo2OFBkdVlOeVUtWTZ3WDN3RUlFMW5EQUE0S1hrLWRZY3BfeW1EZHNCOHdKejFtU2NWR2xjOXo0TEV5cl9vSWxURWtHdnZ3YnRwTkZtbjIxdUk3aFBZU0tHUTNmRExGZmlBR2lIazdYTmtEZnpVODhvWWtScjlR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQN0hYcTZ6b25Oamp6SW03UDZmWl9kM0ZzeGFKUmFLUHNDcXlua05CLTV0bXQ5WFdDRm51amNzWm9ETU5PY3dQaWVJSTNuZ0tZRUtROF90NW5mUVZaTDFpS194NDJ4Y2I2aDVtXzlxanFGOWlSMEphS2NGdC1uQUhkanF6Uml6VVExcHFHQUFHYkRnaWJjbThZall0Ty04dnJScEphRmpDWkJ0cE5tWjZ0SW1zYURLckVUVFRmTG9EWGVybVRLTEJXd0pB0gHeAUFVX3lxTE1wWVRYZXItVVo1QXZUbHN5MlV5Q09rLXIwMmdCQ2N1M1JsOUZRekh3RGh3MmRocklWZlpBdmtNdDhicjJQc19NdDVCNDlVQm45Z0FpUjJGRmJremxpdkVBN0NGd0o5MlBENUxLQXJBT1NTckd3ZzhiWXRjMURtZjBZNm5tU3h3Q1JTR1gzUS1rc0VRVWdvaEJZSF9iajFJTDB1bWRZZlMwYXV5YThEQ1E0NUhtQ003UHVKTlh3SU9XdEl5UmxZSURKNFBUcnJidE9SZkd5dkFHWEM4TFZjUQ?oc=5</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1182,83 +1182,83 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.78</v>
+        <v>-3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>1.04</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.52</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1.04</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-16T01:19:19</t>
+          <t>2026-02-18T19:50:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cae México en 'trampa' del estancamiento - Reforma</t>
+          <t>EU podría ajustar aranceles sobre aluminio y acero que tiene hacia México - vanguardia.com.mx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reforma</t>
+          <t>vanguardia.com.mx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9xREY0MHMwLVh2UUpDcE9MdDUxSEpuWjNRMTAxS2FnUFVZZ0dJcjNSaTQzc0poM01sM0NiaUFIb0NaY2doLXdpTWJEZ01kYXB2MXJHb1FSY2JBYzhac19zOHpzbmRUSzBTYWgzNVVMMlZhWkFCZFh4dDlVVC0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxOZzJvUl9TT3NuZENHMGF2VndnU3EyUGRCOWVJbEFHMFFiYjBUMXdEZlhOajJHV2Q4enZJaklseTItVkw0dXZlSDFpdUR0SVlVX0NuM05jSnhDV2VtejkxVUwzamx3WWFjODZMQl91R0hPVHFRYTd1MXVNejdWRmp0WGh0ZWh3OFhNaEtyRWJwNVM0Tm5ETGJtWFdDeTFVZi02WlZrX0x2QmpFMk9Ed2RNTy1xbmxLM3lD?oc=5</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>-4</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-15T21:27:49</t>
+          <t>2026-02-18T18:30:31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Los buques rusos Sparta IV y RFS Aleksandr Otrakovsky cruzan el estrecho de Gibraltar bajo vigilanci</t>
+          <t xml:space="preserve">“Es posible que ocurra”: Sheinbaum tras apertura de oficina comercial de EE.UU. a ajustar aranceles </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Europa Sur</t>
+          <t>bloomberglinea.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQTlBMY2lxa3lJaGtxMzRzc1pCOGdudkFiZVpIWDFIc3dDc1FJQXBpaDF2OURYYU1meFBNVHJ2Si1jTzBMQmRsTl9lUzEzU2Z4cnhHdU1lWWlWdkNNRU9PdkdFa1h0MEdGdkRrZGhnWUJHUHduRzdVUXBXd1lqVzNiUUFkblNGNGtNSEpiWTJ2NkNuOXktN1ptbTY4QUtmeS0taExVZWtIY0plUHJwMGJublpzS3NoYjlxMFN1NzhLVmfSAcYBQVVfeXFMT1BzTnRLWXRuaHNoTlA3STJNTkp6MWNpOFluUE11MFBmZjkzVVZqcWswSEpTcUJIZ3RLR25GZmE5Snd3RFFUQ0dzdWtUVzdnYkczMGtlUXNUcmFkNy1ob0lGZFdCWGNzRkZNQjA0bEp4NURBQ01HejY4VjI4bllZSmtNV0xfcUhEV2Jud0ZfX3luVUZUYVdWWmszUEt6aWQtamp2V003RWtueUdScVdKVmpnN1JISVBySFEtUTdzekFGSFpsbWln?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNZ0RZb0ljRlBlZXJYU09mOWhWQ0tEY2hZLVQ1bkNfQjhta3NtLVNVT3YzS3piR2FZS29CNTBhR1NaS2pRUzNKa1RHS2dSV0swWHJQMlFFMnBIQVl1WkF6Y1JscjB4bEtZSlM1NUhzUU03V2NnYm9HLVhHRUJmcE1PNVZ6XzZVMjhSSEFBcjF3bC1hZG5CamZ0SGNLQjg4VFI4Z21wNjVqdWNxNGtqazlsczBLUHhiT3hlQlh4LU1zSkNmQmZCNWloMDdVcmZiZWpJaVR3MmM2bjliNVRmVDVLV2FFSWZ2eVZtbTFCa9IBgAJBVV95cUxQemdEc3huV3VJSDJUdlVlb3MyV3FILXZhUFZUb3BpbWpoRlJ0SEY3Tnd5OVgwZHF2LVZKSkhycnZaMldQQVlSNXlRek8zZ0NpNVpzTVNEcTVnRkJNN3BjTFA0dDV6SjNmX00wZTdlNjBTR1lUcjVfME0xcm5sckFTc1VBYmp1RlVDdGYtTW1ndXhkTmhPTHU4ZldTX2RFZlpLMm1MMEtab1ZocTVRWFRGS3poSm9Nb2lTNkxENzVlWHlFRHZzM29NZmF5UVY4R2ZhYUNPejROSVhaR0hqOVh5bm4tOEt5MEJBc3hYa0lKN0RxQ1BQU3VhTjg4Q1BIYmI2?oc=5</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1266,41 +1266,41 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H17" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-15T20:09:26</t>
+          <t>2026-02-18T18:00:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bancos que respaldan el acero ecológico aportan “soluciones falsas”, según un informe - bloomberglin</t>
+          <t>Sheinbaum confía en ajustes a aranceles de acero y aluminio: "Esperamos que realmente ocurra" - MILE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>bloomberglinea.com</t>
+          <t>MILENIO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcXh4bUE2R0xXQkpTUG92NHptZVVaUU5DaTQyR1ZZRXBGR2swS0F6OThYZXFia3hRdHVYLVY5V3c4VVZWTVl3M1lYeW9rZ0Rid3Q4Y0pLM3dmVVNadW1IaEttMmJLelFsZ1VMWkdrZDBhWXhwWDBhNTB2T1FpN1I3c3d5Rm9JbDl0NFBrNXlZbDM4VFlvTmpOZ3hUalRUZ05IQ2V5UEZsbXZoc1o3UHNHRGVqOGMtVlJzcmhQZm5yaWRIenfSAdcBQVVfeXFMTkttNGxZUXZLOHVwcmhUWWhmN3FUOEEzcWY3WUJnS3N6aUhlQ0QtSG5tVU5nQ3dzQ2QtS0MwTnp3MkxmbWRDQjBIT1RweFFIQThLQ0g5ejFKVklLRlVGenk0a1lVLVFwZjZNVVJEWWhaOXZhZXROd0w1aXJFOVdKOUUyNzUzWlFtS0JXUWZ6c0JwZmxiOVM1SEYxaF94dlRGelVwazE2aWs3OXNFMzFQM3lQMWh4cjllVkwxZkpzbGJRa2NtczgtSGZYOFp4VTNHSTAwTUNVOHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQSS1KMW5JdVVMWXNxMXRZRk8zOVZadFFVd0o0T3pPNElndzNDTVdCZXZmdElpcDNOeWNTVDBmYWVmUnNKSC1ROEpjNnlNMDF6RE9JUUtidXNTTzJ6dl9TUTJzMUJZTk9SVkNvM0llSWpvTS1FYlg3YVg4Y1hSRlJfNzYwR3FYcE5SMnfSAYoBQVVfeXFMUEktSjFuSXVVTFlzcTF0WUZPMzlWWnRRVXdKNE96TzRJZ3czQ01XQmV2ZnRJaXAzTnljU1QwZmFlZlJzSkgtUThKYzZ5TTAxekRPSVFLYnVzU08yenZfU1EyczFCWU5PUlZDbzNJZUlqb00tRWJYN2FYOGNYUkZSXzc2MEdxWHBOUjJ3?oc=5</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1308,41 +1308,41 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H18" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-15T18:30:00</t>
+          <t>2026-02-18T17:00:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Variación en el precio de las actividades del sector construcción - El Economista</t>
+          <t>México espera cambios en aranceles de acero y aluminio - eltiempomx.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Economista</t>
+          <t>eltiempomx.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNWTVzc3MxQjBVTXE3a3BzZ29EMFZIdDZqajdrc0tWd3Z6UkZhT3REWG9QZEhqVWF3LUNkM2ZVYS12dWhJTnBQa3UyMHZieWJUX2RRRDcyYzM4bzJtOWdBbW51WU5SWm4weHRvZzMzdG5GR2JTTFFmTkNxa0xFaTFSWTFTRTVNRk5SUlJIUW13ZVdvODZRZE1kN2RQOEdudkJIZzRXVmJRQy1XbUtSUm1wWkRGUWnSAboBQVVfeXFMTzI5VTgtTzJ2VncwdThSM1huMVlMQmZvbWRGSXNfejBnaXdIUl9ualNMMkxETmxHbTlxVjBJMl9ZTzJuRU9FQzZiZkkwQnBzMGphNHc4bFgzVE1VOWxvU2tWX0pkUWRjNmpXY0pSVVJQcXFfX0o0YmJiZXFqX3FyYnhmOHh0XzhVcE03OGJDQmNaNExCVkI4Sm9XYVVQZVdnaFBfRDd0NEJ3NV8xcHd5R0hSTy1CbnZGb3p3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxPZ1M0WUM4VkRhOHBzemNzRWtrZjFMSXdoUlJrOUZQMTNqX1VNelp4WkRJdVNGSHNnLVdId193eDRGVU5pRkFZRVVYMXpSUlhYOURZUUF6bHhOMzB4R3AxLTJHOHkyRXd6SHR4SGdBdFFGNkxNNGdEek9DV0t1bWlENzlBb3FHX0FPRFQ1VW45c29ZRDBIMFFIWUtGVdIBjwFBVV95cUxNV1pmOVR3VDZNZFFpOHVzZUU4cWVLUGpPeWYwWUJHZExoLUt5aHpoWndjak1TLVdiMkNDWDM2UFJXZUNmdThiT3ZUWkJZRnZyZFZtMFZnVkE5aGhCeVFLV0JlbU5nT1ROd05rYkJrZ1Z3TEsybThONlFrUnBCWi1JUHJfdTBQcnE5cWZQcml2RQ?oc=5</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1350,41 +1350,41 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.78</v>
+        <v>-3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.52</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.04</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-15T18:23:49</t>
+          <t>2026-02-18T16:11:16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Proponen al Congreso inspección y regulación del transporte público - El Heraldo de Puebla</t>
+          <t>Sheinbaum confía en que EU elimine aranceles al acero y aluminio - Revista TyT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El Heraldo de Puebla</t>
+          <t>Revista TyT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPLVg1WS1EaU83akdtaEU0bUdBbUlMVFlnd2hJc2c4cmNKc19tcnF3UXFMa2I4MUk5bnlvdndNTmNsZkVBUk1nUzJBRGVmZDZuTDN2a05FOXFJLXJrVG9nT2FaenJPaklJSWZod2YtSEoyRWhNYU01eUxyYTV3aU5BUlFmaEdEU01UMHZQVXlMaXJGcDg1ZkhTR21EdV9BQWJua2gtZFkxTURTTUk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNaTB2M3JVdkFfbGxpdm1aQk9lVUZRb1NhQmRyRjczTVdTMGlRNlNXSHhiaHdzYzVxYWh1NUt3emtHNmlSQ200ZnFrTkpYdmZ1NEp2dmp4YWY5REwyV2FPY19kSzVVWm04VGZqcWNjNkc0Z182TG1rNnJmUlcyaDgtWmE4bmY2OE5MdTJEWk4zY3BsTEItTjVV?oc=5</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1392,41 +1392,41 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-15T17:33:00</t>
+          <t>2026-02-18T15:15:51</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Presidenta Claudia Sheinbaum presenta Plan de Inversión en Infraestructura para el Desarrollo con Bi</t>
+          <t>Ternium ganó 74% más en 2025; espera un mejor 1T por aumento de sus ventas en México - Yahoo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gob MX</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR1plamhZb2VOaHNsa2dWV3I1LS0wVkNzSnBZdV9WbG9zazRlazgxUVdrd0NzY0ozMkwtZEMxc1ptQnV2MVJjM2hPUDZ4VHJNT2syczc3dmNlS2F6QWg0YV9TWHF3bDg0a2J0RzNxQkhoaThGbzh3Yjl2cVNMN1RWYU9mWl9kLUtnTVRidXF3WUdtcnFwWGpQNG4tbjl4dWNCR2J6N3prZXlLRmNTeHVKMkdETHBaUU9UVnJBY3V4ZEFjMnotdi1WdVlncFdNM0VKOUtCMzI0cGY2S1Q3WktGcnRkNXI4d1FET2ZvUEhDbGRQX1JIT1MxSzhmbldZOS0tRTR3QkhB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOZ1BXRGVPQ0p6NGFsWjB0Wk1YNHpiTTgzQjVjenZzOEM4S2EtVEJ5WkNuWVpnUTRSODVaSHE2ckdxZXJxSFpYbkx5ZFVMNlJZNF9iN0ltNHNLeWNxSmNpUEs0NklsQ1FJT2x4S0dxZWFwYXR6NGNEb19FcHhQNmgtQzlsZk5xN1U?oc=5</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1434,41 +1434,41 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.78</v>
+        <v>-0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.52</v>
+        <v>-0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-15T02:17:59</t>
+          <t>2026-02-18T15:15:51</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Entrega Gómez Álvarez infraestructura diversa en el Edomex - Marcaje Legislativo</t>
+          <t>Ternium ganó 74% más en 2025; espera un mejor 1T por aumento de sus ventas en México - El Economista</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marcaje Legislativo</t>
+          <t>El Economista</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNcXNPNkMzMGxXR29aOFctTWtVTnR6ZXNmRHl6TW1vMlZvVWNCZ2JSWVRrektuTHFDS25lb3RWN0dxQjEwZ1lsekxyQS1iRVdseEdKb1RIR3IzRVdYb1B6S1laeGhJRUxQd3Zqd1ZOUVNiQVR2WldrRF9ROVR6Rm5kd2t0WE45b3R4MUV0ZjRBZnB0d1hwM1kw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPV3p3WmxsWTVIVkd0Z1BRLWpiVFplckFJeVh1ejlEbjQ3alJSNHgzZXF1MHFtdGtlRTZCMWlscFJSMFhzZ250WkRwb1ZzbXhkV3hoanJYZG9VeXE1SXQtejRTUWJlYzFFZEUyeXNuMUoydU00VnBJZF84YnhveFdsU1VOc1k5NU8yZDVjU085MEx4aWt5dk5iRmZ4cW53YUM4dDZoNE9LMDlMSGtybVBmLW1nUU1Gam0zS2RDbdIBwgFBVV95cUxOXzR5Tk1nSTJzNXByQU41UW1vX1NlS1hyYl9JcmpVNWFBVXBNVWNRcE10VVlKU2JXZ1RoTngteTU1bnRUdDRzNjJwTmJyaERHaERDYklfNHhobDJ6ZWhEUXl6R3ROLTJPVkhGMFcxZ1d0OWRNRmRUams5cHBNUDZZTnBtQ3hUdjNTZE5aVm0wY1J2akVFVEJPeXZ4QTBCbFh3bS1TdWFXdTVqZzVUdTBOSE9KQ1ptV0NmcmZhTEZjcF9JZw?oc=5</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1476,41 +1476,41 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.78</v>
+        <v>-0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
       <c r="I22" t="n">
-        <v>0.52</v>
+        <v>-0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.04</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-14T02:28:39</t>
+          <t>2026-02-18T15:12:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CMIC Yucatán refrenda unidad y visión de futuro del sector construcción - tintapublicanoticias.com</t>
+          <t>Aún no hay ajustes de EU sobre aranceles al acero y aluminio: Sheinbaum - La Jornada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tintapublicanoticias.com</t>
+          <t>La Jornada</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPYmtwYW0wXzdZZFZTa3YyazAtdHN0bHYtMjFtYzE5aGJTRnFVNHU3VkZSdi1TRzgxRTVDWEU1VENVUkhrejhORDRKbktiSDNub3lBSmM4ZkY4WGRaTXpJRHRpb2RQX0hKbHlDRjlIX1VnYVNpQ2ZfbE9PTnowQzJJWElnYW1seWs0S2RWdWNQY2FWYndNSnNoVDdTcHdfNjhua1lIb1Nxdlc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxNcDZBckZTUzZxMUV6M01NQk9GU3RMRjRsN3hNdHNpbVlidVhjVFoxLUJFVEdjbTV2NU40aU9LOVVBampnWGpEYTdzVk5oV1poOFN4SlA2cW5GeElyNE5mU0NtdkZDalU0bU55c1JhMVN5Zlo3ZW04eW9HX2pCcURhOVNteHlOUGdHWGMtQVVTc0doZm9RRDhJc09QcWRMeWdSdWpKNFJxWXlVRWpySkpGd3FoX05SMmM0YmFMMkExRElFNjQ?oc=5</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1518,83 +1518,83 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.78</v>
+        <v>-3.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.52</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-14T00:48:53</t>
+          <t>2026-02-18T14:57:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>México alista reforma audiovisual con cuotas para cine nacional y regulación del uso de IA - BajaNew</t>
+          <t>Sheinbaum ve viable reducción de aranceles al acero y aluminio - expreso.com.mx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BajaNews</t>
+          <t>expreso.com.mx</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPSVRDY0hoeGZIRkdCTUh0QTVGVmt3MjRZMjFIMVcyQjVXZlVvRDNjY1YzYXgtRGF0MjdubEFRMm5QWHdsejkxek9ybC1rLWQ1T1ZTQjB3VnFSV0FlTm1PM1FHVHZqTnI0S1ZabTJGZGFnRDZGRV91VW5jNFVsUkZreDJsaHhJcGIwajBFMkpHM2JsRWFRWkRkc0pwRzNQSnNIRF84VXprSWtxLWg2eEtoeUFJNTRZMy1PY1B4VlU2ZHktSHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPWEhWSkJpbkdHMXRNV0c5SzhHS3BFbFNFNUZ6a01mREktamdmT2hWRmJiZ2F0RVhuOHJJNU5yVEVuN25ERnM3Y0Y0S2J0S1llaGlTTU1PWUtnUm5VbGg4N3RhVGh1OUNwZDN4S2M3SXY5ekFHRDFHd3FUcFlVdndmalRaU1M5SDRET3lJSXMzZHl3UGhFMVpNMHFmZDdqY1RlQTFGVFoxRVVpZlNqcEhxTzFaTdIBswFBVV95cUxPWEhWSkJpbkdHMXRNV0c5SzhHS3BFbFNFNUZ6a01mREktamdmT2hWRmJiZ2F0RVhuOHJJNU5yVEVuN25ERnM3Y0Y0S2J0S1llaGlTTU1PWUtnUm5VbGg4N3RhVGh1OUNwZDN4S2M3SXY5ekFHRDFHd3FUcFlVdndmalRaU1M5SDRET3lJSXMzZHl3UGhFMVpNMHFmZDdqY1RlQTFGVFoxRVVpZlNqcEhxTzFaTQ?oc=5</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>-10</v>
+        <v>-3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>-15</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>-5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-14T00:30:41</t>
+          <t>2026-02-18T06:26:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Construcción: del ajuste de 2025 a la inflexión de 2026 - Centro Urbano</t>
+          <t>Analiza EU ajustes a implementación de aranceles al acero - El Financiero</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Centro Urbano</t>
+          <t>El Financiero</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9zcU1QNkxVSjlwb2ZfbUhBSUhrWUE4NWZ4THhObG4yUGFvMGFiTGp1aUlXQ005OXhZekswSjZIci1uWjlBR0swc2VweW9ia2Q0eUw0R3pyblFidHdwcGxveXpBUEJhb0lUVjZ3dEtmVzJuY0h6S1NXM1Rncw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNTUNEYUlLWmY2eFpfczhyVFdMZGoyTE1melhVQjVGSjZpbm9TekVNV21EdFR5WmN3NTI1TUUwU0J6Z1lwN0s1ajNtdnFJeGxBQllqSzBTZHYxNG9fd0hrSFNnd0xTTkNmcGl5R0RleDMyd1BqTnRwOTJYaWlRNEFZR2dmY2FoQU9LSzEzUmlhT2hHNFFYZ1BncU1WWVVuQmtDLXNuZFVVeTRrWF80YUlV?oc=5</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1602,41 +1602,41 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.78</v>
+        <v>-3.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>0.52</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.04</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-13T23:10:15</t>
+          <t>2026-02-18T00:45:03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vale fija plazo de tres semanas para recuperar Viga y Fábrica y reabrir con aval ambiental - Minería</t>
+          <t>Aranceles y controles: así buscan México y Canadá frenar el dumping asiático - Ovaciones</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Minería en Línea</t>
+          <t>Ovaciones</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNUHlBd2NCX19GaGhxa3lsLXJBRFljbUhVX0pacjV1SXBqblJCN0pTbkZIZHAyeFlKS25jbmdYaGNHOGtRUmhSMHI2aGM5Wm12VVp1YWRiaE1LcTdSdzFYUUFnMXZER04yVG9UdEtrMkZma05TeXlVOVNIUkJ0d0FwUXhpS3ExUDBhaHUwSDhFNW1Vb0lBMXJpTUdLdWNRajhzODZPRzZPbjNiZEw2RHZIMEtKVkljNWRVS3dLcTlhODRBa0Uy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOdDNXdkw0Vm1kZHZrM242SHNGV0kwRENiTjRjR2lBcHB0aGtSWlliY2JVX3U0bjdQSXFVRjlnMXg0c2RlS1hDZkwwU0xuSDk5Rl9RenJGalkzQmZkRVY2dGNrSko2eTVWYm16MWxtSVREb19LbG1LbXpPTG1GMXRaaUJXRmJyTll2Z19tcEZOdDVJYTRreFFPcTJYQ1U0UQ?oc=5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1644,79 +1644,79 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H26" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-13T15:54:00</t>
+          <t>2026-02-18T00:19:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Los precios de los metales se desploman mientras Trump reduce los aranceles al acero y al aluminio -</t>
+          <t>Un tropiezo del T-MEC restaría PIB a México: Expertos</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cryptopolitan</t>
+          <t>Aristegui Noticias</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAzQVBYc1QzNW85djVnMEJvdk1zODZmOTEtWFBqdWp5eU5XdkNZUDhNZ3pTajZzNlV0bENUcjZlUFN3cEJsWGh6bzVqOThyNXZFbWM1MnNfRmJqNG41REE4cU5xUmZEd19oOTgtY0Y1STZIbk1G?oc=5</t>
+          <t>https://aristeguinoticias.com/1702/dinero-y-economia/un-tropiezo-del-t-mec-restaria-pib-a-mexico-expertos/</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>-10</v>
+        <v>-0</v>
       </c>
       <c r="H27" t="n">
-        <v>-15</v>
+        <v>-0</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>-0</v>
       </c>
       <c r="J27" t="n">
-        <v>-5</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-13T15:50:27</t>
+          <t>2026-02-18T00:05:10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>México presiona en T-MEC por aranceles “costosos” al acero y autos - Industry &amp; Energy Magazine</t>
+          <t>Greer abre la puerta a cambios de cumplimiento en aranceles de acero y aluminio en EEUU - Minería en</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Industry &amp; Energy Magazine</t>
+          <t>Minería en Línea</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUXFPQ2NuUVIxcEVtVU1ta2VZME8xcjI5UHNtMHRIMVMxS3Rtc0tBOEVhR2pEOHFYcFB5SHN1NHp1eTdHM2FwYzYtbUduMV81NkJsWWRGdjNjbm11cmg0TElOMkdYbjhOaDBlbTRPaHZzQUM0MlpCTFJqMDRkR2lkTVY1b0c4d1JxR2ZrMWJpNjIwcU5lSkFZYmNyYmhkQ25p?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPTW4zYVlpMFdDQVFGRTdkc1Q4SkN5OTUzWmE1Z3hrdHNxRlhoNDBrTnc5a1dKaGpQTk9SQ19sTVdMMjBfV2VSWUQxSDI3aEIxa19VVWRNc0FjYXdTUkw5dnJEYVFRaTY1LV9JVmNZOHpidjdOUXhTa2JCcmtPQzlPSzN0eHhqZ3dZelQ3Nm9Cc25BWndGdWZuTEJ5RGpFQjlURERxYXNtVWNwc2Z1MTBHMGpHTEVMNGVxZ0hzcjJ4a3c?oc=5</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1743,152 +1743,152 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-13T11:27:30</t>
+          <t>2026-02-17T23:11:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EEUU sacude al acero: Acerinox y ArcelorMittal se hunden - XTB.com</t>
+          <t xml:space="preserve">Firman convenio de colaboración AMPI y CMIC, para fortalecer a la industria de la construcción y al </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XTB.com</t>
+          <t>Hoja de Ruta Digital</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxOajJiWFZfZFpxVUtDYUFKamxjbWw2blBMbDRSb18yNGdtTmVGZUh4Ni1DS2RPZUdYbFp0azRNeHJnWGQtRk1OclRwcDRIWXRjREwxLTRmdjVTY3ZKWHEzclRGUnpmaEZiZVUwV2p6OU1VZnBWOUNGRy1QX1Q1dlFvZXdSeEFJcjhjNGtoRWZNSW1wSjM2bXN6SWROUzFJM1did3U5RXFyNnZVb0lFM3NZbWxVTWt1SGJmZHJIcXpRQTFBNXVmZm1sSUREa0FseWk1QUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOZzdpWnc3M09McFh4VFFfSFFGcmtnRVEzY1dIeWY0ekh4a2dwQ1pNdUlDaWtVRmVvQ0tBVmQ2ZENGQ0d3c3pZZDE2dWRwcENTMDNuM0V5dlYxMnA5ZDlnYjA3N0VzNkhwd0VteDVJOXl5OXBjTTgtTk1TU05GRmpteTMwQVpsaVFSV253LVZWaURaR3IxWWh3VDQwZHdCZW5GT05JY0ZyaUZHT093Y2lSNjJodnRJSkM3bWo4UGlxT2dlb0JGcTZqRzJ6aVhOeTFzeTc3aUNZbHJEa2N2dG40Y1Z3?oc=5</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-13T08:36:54</t>
+          <t>2026-02-17T21:43:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>La economía de Rumanía entra en recesión técnica debido a la caída de la demanda por el déficit y el</t>
+          <t>Cemex se posiciona como la marca más valiosa del sector construcción en México - MSN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MarketScreener España</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOTWRNb3lnT0N5bU9tUzc2NURGSWpSZFNaeWhVTFZldlZzbHhBdmJqV2pxSkV6V20tUUFPSHF5cGhpYm5RUy1vNVJfaVl6bF9UZHRVaEVZLUl3eGZjbnRQcXYyMTdlckc5dkZEVjZncWNhLU85Y0lQUDEya0oySGNnNkpoNGxuX3ZZckxYNnpOOUsxaVdSQksxalo5akItaTJxV1FVUVZSSHBmSGU3RWtPeDRaYVpmd3Fzc09pX1VDSzF1SU52dmFSd05QSzNtd3Jndm4wNG1iUjFRMUlrdDd0eXFNcGJVeGVJQzNMeg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gJBVV95cUxQSkhxbUVneERSbDZ6N0tGM3NrUVdfOVAyTGFCZkZJLWVNdng0a2ZBeG5vT1JlNFJEZ3JteDhyOWN4MEFNanNHZWlXT3pYd0pidHVQMHJNSno3UG1ydVZIVzZ3N0c4Ui1YTVBEYTFRdGhTaC1sWjNYanNpY21pLUJKVi0tRjZLbTlZSzdadjB6TnJzNUh3dEVsLVp6bk43XzdDZkpsTFpkM21xSlhUTThOUmx1Zzk3RndGQlJkUEtqUXFWRnZnSUhRdWpSR3JOMUNIQVp6dmVBY0hjUWw0MDB1cDN5SUFUQlpFRWhxOVBocS1CRnNiMkpTWVJRLUJKbDJqcUpLWVRGbXBHWG5HSWlnaFZzNnRwNGdQbWQwUzcxZ1MtNkRjQTdsS1VObm9KWUYzaVdpazdqczF3WDY2Z3pnY3BrOU9WUVZNRHZjLWNabDBJZWhLSzAxWTFIUkRIWjlYR29QRzFUUDJRMmFfMVFvWVdVVkRodw?oc=5</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-1</v>
+        <v>0.26</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>-6</v>
+        <v>0.78</v>
       </c>
       <c r="H30" t="n">
-        <v>-4</v>
+        <v>1.04</v>
       </c>
       <c r="I30" t="n">
-        <v>-4</v>
+        <v>0.52</v>
       </c>
       <c r="J30" t="n">
-        <v>-5</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-12T23:36:30</t>
+          <t>2026-02-17T19:26:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Infraestructura de recarga impulsa movilidad eléctrica - Energy21</t>
+          <t>Calculan que aranceles de EU al acero y aluminio afectarán a 4.7% de las exportaciones mexicanas; se</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Energy21</t>
+          <t>MSN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPT3FYNEZHMVNiOUZFMFdBYkFxM0RFSENFMmRCbjJxSnZ2ajZzREtCSU90ZnJ4TUZHOVhKbURBMEJ5TDJVTmlyVUU1cXhGVzlOS191N2E1VkFicFZpVnFLejRTOTl3c3RuUjE5aU8zT1Y3LUZjZHdiLWlmVjVCb2J4bUx6OS01QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgNBVV95cUxOX2pWVW1ac1dpTW5qUkFpSExTc01BQ2dkNnlfUEVnUUFfcnZZdDRPSkhZaGxKdHpOeDNCNlN0bjRkSVJKVFF1Vzk3MUNEcVlJdGxEd2tNNE95UFlPNXZ5QS1EejFEblZMYzQxUFRJRWJadC1TYk5XMjdVODZ0OUJwY19OcHFlSmlJckVlNjVPYVN4anRJMWhYSnpKc01KTHo5X0hVYlJIYzFUMzZnZFhIR2tkbV91Mll6RGprbC1NdXJ6LURBemd4a0VlZFE5MER2MHQ1cTU5NzVjMHpqNTZNdjZ2QVN5ZExEU2xPVEY5VVRjdzIwSnFoMmtFTWVVYTFzemx1WUEwVjVuMU9zXzlodlhGak5rSFdfenUwS3Y2ZTNQVjdUdmJKTXVocXBsWkF2azI1djhkZUkzOWs1RVhJTVlEdmc5ZHpNQktUWld5Q25WT25yQlM4NWJjbnBtUXhTZXNLQnd4QWNJdEhmc3QzVlNNaEUzTlBjeklFM0tiX1dhWTBpNFRCWmFfb1lVQ2xXQnd2R3pYZThIYktZazBHRDJoZkZmT0RjYkE?oc=5</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>-0.05600000000000001</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>-0.336</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>-0.504</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0.168</v>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-12T18:44:22</t>
+          <t>2026-02-17T19:00:00</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Busca México aranceles homogéneos en industria automotriz - Reforma</t>
+          <t>México y Canadá apuesta por inversión en minería, infraestructura y manufactura avanzada previo a re</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reforma</t>
+          <t>MexicoIndustry</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxQMGcwbHFvSERsc0FiR1NNNGpwam42bXo4d2lhVmhDNjc4Z3hxaUZkby11R2ZVREMxQXE1RXVIRVFnUktjaUtwdW1GVDhPYko4N1pVQklETFdMWXN3QldEUHpyMWlpVC1wR2xBbVE3bjFIbWQ4S3RCTGlsVk4zbFRhTWI5VGlZYnQ5dC14NE1GemZrRHZyNUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxQNllhY0ZtNlV6WVREQ05GSHpsTEwyRjludWNUcG5VX0xlYVp2V3AxQmhYNzlPaWNXY2NXTEJfYWxtNVVnREpvV2NPcGo5VmZpTzZRdFdGWTEycE1ZUmdYaU8yaDZfN1dRM09KV0xab3JNVUN6TFZmT25JVG1TTEdNY0hjYjN2c0tvSk1TbHdFLUotOTIxbE95T1E1ZFk1RHdkZGk5S0VZeHhDNG0xZmpQZ3BhQXh6VHAyQVNnejUzY0ljeDc2eHprdnFFa0ZHcGwxY2J3MGZnT0lubFc3TUJWX0MzU0g?oc=5</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>-0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1896,41 +1896,41 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>-3.4</v>
+        <v>0.78</v>
       </c>
       <c r="H32" t="n">
-        <v>-5.100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.7</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-12T17:53:14</t>
+          <t>2026-02-17T18:30:05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>México va contra aranceles al acero, aluminio y a la industria automotriz en revisión del T-MEC: Ebr</t>
+          <t>Canadá transforma su política de defensa con un aumento de las inversiones y exportaciones - Univers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>El Sol de México</t>
+          <t>Universidad de Colima</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxNSWtjRVdiVEZTanhLTllZOEZEVno2WjBoYmIyOXBMVkZOVW04ME4xUUZ3TExpanVIX0RNOHBjYU12dXYtZmlneVlwYjBKZkljUWE4dUpfMUNXb3lteDdGMEdfX3FaQzl2aVl6LUtxRm02Wno0TUVrVU15SWthTFYxSkw2cXZGQjhhT25oOTNucUk0dW5yR1VCY3o2TURyUHl4YVhqUGFRZVE5X0dsaTRodjRQSE10bzhRWHRFaWJ2dklmQXo1NE1NN0luMnh2U3dqTVhCdnBVMFBxOVVoWDFsTkkwZFVtRms?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBvekVseHIyU0s2empQZl9GR0pBdnVXbHhsVTlHMEhEWmpodEFjQ2NRV0FLU2Ztei12dXBxaThVRENNWlkzSVF3dk5heTU0dms?oc=5</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.34</v>
+        <v>0.26</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1938,41 +1938,41 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>-3.4</v>
+        <v>0.78</v>
       </c>
       <c r="H33" t="n">
-        <v>-5.100000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>0.52</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.7</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-12T09:30:27</t>
+          <t>2026-02-17T18:07:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Este descomunal horno eléctrico convierte coches, motores y chatarra en acero verde sin quemar una s</t>
+          <t>¿Presión de Ebrard funcionó? EU dice que está abierto a modificar aranceles al acero y aluminio - El</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Diariomotor</t>
+          <t>El Financiero</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQY3IyMHJPSTdjRGVmR2N0N1B3LUx4SlNTNG52elFpcGp3OTZlbzJkV3IwZFhSTmhTWDl0XzBINzN4UllESjRJR0xCbFJlZnp2eHpIcEpiTnBpUDNySkxrTy00S0ROMWRqZEFnRGdSbXRqdVE3QmNaY2dUeDFBLWlMU2RJa2NCNXZuTV9ZWnR5YkFDeFdUUVhDS2hxOG9KZmZ2b2Rkdk5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3wFBVV95cUxNRWFSVlJESkhiNE1nSVZJZmdsS1NRT2VVOGlhRjFLM2hKR1lUYXhTQzFOaHpJVlJCZUNJQjVpdmNpQk5peHU5UnFSRDRaWkh3RmF3LU9qUFBtTnMyanotTXRseEstR0FMaWFEMkQ0SnBmTjJLekUyRk5YVmN4d20tNTFPYzJnWXVnTktKaXE5TmZqT2NmaVR0WDJHQWRPb2ZNS2lqb1NmR2tlSGdlVHlCb2RENHpWYkpieTlSenpRNzRoRzgzdk9JVmNZSDlyaFAyb2QxclZhZTNnWTJJSkRF?oc=5</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1980,41 +1980,41 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H34" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-12T08:00:00</t>
+          <t>2026-02-17T13:52:08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Desplome en construcción pública: inversión retrocede más de 30% - Industry &amp; Energy Magazine</t>
+          <t>México y Canadá lanzan plan de infraestructura y minerales ante incertidumbre en el T-MEC - Univisio</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industry &amp; Energy Magazine</t>
+          <t>Univision</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNUExLT2RPUkVsTnRrMmdrWGtDeWlBaHRGUk5BTlRTZjRfdHlMNmVTMDlzeDdHTE1uRDRhcmc0UFFhLUNQa0VkR1JmTmdqVVIweFpPdG5zSmVFamxPbDNRbHR4bFgtVHJLcmJFZmMxYWNMb3BpR0lBbUJOYTdkYTZZQnczNWdOZk1WazhoVFFMVzIwT3RvQ0kwam1MaVI5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxPUHc4VlVTM2pLa0RfdUczejlyOFJITlBTN2ZsZUwyTEtTMUN4RTE2aHQyQWp2d2JtYjdxekphekNNalNsZXQ0c3lEVFphX0piTU9PVU1PeWFTV2hPRzcxazlhWE1YLWRULWJEaGc2cHpXTWRNYjE1VDRVbENSSzV6QnBJcnF0dmpWdXAtS0s0ZHk3aXlwVlh2YVdDd212MU44Y0x6djJud01iRzdES1NpVmdrbUUzYWVNLUN3amQ3MHFrZlBnSHpNRVVHVHJSdlRmazFiYVVIMU5OZGxQQTVOUQ?oc=5</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.09000000000000008</v>
+        <v>0.26</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2022,37 +2022,37 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>-0.4050000000000004</v>
+        <v>0.78</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5400000000000005</v>
+        <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2700000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.6750000000000006</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-12T05:41:46</t>
+          <t>2026-02-17T09:01:02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kyle Larson imparable en dominante victoria en Bristol en NASCAR Cup - MSN</t>
+          <t>‘México es un socio confiable’, afirma De la Fuente ante funcionarios y empresarios canadienses</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MSN</t>
+          <t>Aristegui Noticias</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxPUEdFT0Y5b0FnM2ppT3Z4TVZ6QzdGaGh0N0llUDFMd1lWdTRjcFNiRWZYcjM5LXI4azZ0Y1M2dG11V0FDcVRFUnpLSWc2Z21QZ3ZuUzNoMlNBT3p2MVBBNllPT1Z2WU9vVGFsc015RDlVMWtKMDU4ZTE4TGRUWUdNcjBtVnhsVGRYSDRQaDk1dWVvcGl5RFlhNjBWeW95d085ajF4N2hibFl5Q3JGQmZ1dk5LTjFHQUk1VnVBYVNMbTdIRWg1WXpvSmFhamRlMnhwUkZRQlhXUEI0U2dramlCWFFLblJUQ2RYVmVybldMNUo0Zk9Da2FBU0pxejBrOEdXYVBlRndKaXlzSS1QU1RGVmZ2MEZEUGxXRDk4QXI3Y3pZMThmT3pBTXNnbi1lb044ZjV2OHdCeTlrcW83Yk12TmJwSmM2anJIUHVJeU1CVlFzMmh2?oc=5</t>
+          <t>https://aristeguinoticias.com/1702/dinero-y-economia/mexico-es-un-socio-confiable-afirma-de-la-fuente-ante-funcionarios-y-empresarios-canadienses/</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2079,26 +2079,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11T23:57:17</t>
+          <t>2026-02-17T07:36:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ante crisis del maíz en México, Márquez Márquez pide frenar importaciones por caída de precios - El </t>
+          <t>Investiga SE acero de China y Malasia - La Razón de México</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>El Sol de México</t>
+          <t>La Razón de México</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxPVzRxTzdOc1BWV3hfRkRRSVFUTEZFZTRxWVkyWm9TSGNjRC13c09FWGp5LS1QNUlqSGVIM3FHYTRPemcwb1VhaEk0dDIxTU1MN3RGNDdhU1BpS2VfRkFlRWQwcWZ3N1NKekRiVWJ0eUR0U3RmMnNQRzl3TW1JeXlvM0F4ZjJ6REZpVl9ERXpOMmhmaHdWZGQxd1RONTdlbzdNcjRoNk8zT1ZLNlhZcFRfdmRMaURUN2VST2pxVkhKTVJNZ21oTUZzTjQ1S21SeG15NjVn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPZWp4aEUyV2hLVTZqcDdPOF8zeVFvUHFvVkFnVVNoSVl2ckc5dWZkWUl4SzhLMi1nUkxUN1FjS1oxVUlNVi1SM0ZGY05CTzUtdng3My1HLUstTHQ1TDhoZ21KWDFPa1ZYVHRFNDdXUjJ1NGZERjJEbEowTWxwQW5HU2FLblBlRkdldjFN0gGmAUFVX3lxTFBTd0k2NkZsS3Z4ZHcyOF9aa21xenVBU1NxNDNTVm00N2xIV3F3YlhTTjhiOFpISmZONW9OVTQ3LTExOUgwNWJSM3NDcXlGTXQ2RzFBSklIcmZQcWEtQTRvcTdkSEt5c3FzODRXV3hxUTlhVzdCR0VGc2owQzNJOXhPa1hOenZKc3RBNHJHOHNaZ0E2emd5NHVtOXViOUJGeGVrZ1dXQ0E?oc=5</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-0.6200000000000001</v>
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2106,41 +2106,41 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>-1.86</v>
+        <v>-0</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.48</v>
+        <v>-0</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.24</v>
+        <v>-0</v>
       </c>
       <c r="J37" t="n">
-        <v>-3.100000000000001</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-11T23:46:42</t>
+          <t>2026-02-17T07:10:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>El mercado interno ofrece espacio para el crecimiento en la industria del acero. - Vietnam.vn</t>
+          <t>México abre investigación antidumping a acero de EU, China y Malasia - Meganoticias.MX</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam.vn</t>
+          <t>Meganoticias.MX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPeUw4MTA3S0JQN1ptTHp0ME96cmRld2hZd0hveFoxejZxb1A2dFNhNWdIS3ZXWnlFNWhtNC1KVFFVNUx5VDIwZzhsbVpXWVA4cWVJZWk5bTNTcXR6dHZqQ29UU2lFdG0wNEpTT2pwMjUtNXVSTDRua2k4STJybk1yWjRKRVdKdHAyVFpfcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNd3FnbjlSQ3FWTjJSYnNhRUp2VWVsM21HUDl5RXQ1Mk5GMDU0cEoyMDA5VktiTFd5cnA1U0R6Y0lrS1hpV055cTJ6M25PY3R2X01hOExHR0I5RDlMTnJtU09XMjBfRXdMdTNRTlVfQk1GcXNZX01OamZHd2EwYVhzX3Rkb3c4UWlJeENHVWZzeGFwUjNJVjQ3U2FfRnBrX0lIWlJPSjRidmJ4YkJHaFg1U0JiOFYtQQ?oc=5</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2148,41 +2148,41 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>-0.9000000000000001</v>
+        <v>-3.4</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-11T13:40:45</t>
+          <t>2026-02-17T05:24:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>¿Un desplome bursátil desencadenaría una recesión global? - Investing.com México - Finanzas, Bolsa y</t>
+          <t>Investigan aceros laminados en frío de EU, Malasia y China - Reforma</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Investing.com México - Finanzas, Bolsa y Forex</t>
+          <t>Reforma</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxPNTlaTi04cHhmZWtrZmh6cU5Zc1ZvM1NTMVI4YkRBMHJtZ3VTNkVid3g2MERWdUlxckFYN0xLZ3ZTYTBXRWliNGx6X1ZyM1JNdndzNVJ2RzBWaWYwUzlRNnhXLXRYb2tCQUpkRzlMNnRzNzJfclRQZ2lRVlFtV1dwaTRtNkJoeUpDUWdJNjRQSnhFU1NLMlEyVFhJc2NLaFFQakRIdjhGdkZ4cGE2d3kwVTlRTUdSNlY4TndVUGVoYmtIUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNaGdBTFMzeHRaZVJJeVhHMGJpT21uWWV2cGNqSFEwZjBXUlhpbHphOGFMcXc0UzNwQVlLalM2YUlsNEtUdndKWkx6cmlOSDdCQU9xM1NIUTJ3c09nZlM0Vkt0SVQxNDZpZTEzeXVoVVR2UllyaUI3QjBSQU8tZ1A2SWpsaktrMUdXUGhWRkpDc3JhaHhKSEE?oc=5</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.3200000000000001</v>
+        <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2190,83 +2190,83 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>-0.9600000000000002</v>
+        <v>-0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.28</v>
+        <v>-0</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6400000000000001</v>
+        <v>-0</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.6</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-11T12:44:42</t>
+          <t>2026-02-17T03:47:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Megapuerto de Chancay: fallo judicial blinda inversión china y reduce poder del regulador estatal - </t>
+          <t xml:space="preserve">México y Canadá perfilan plan de acción económico; incluye minerales, inversiones e infraestructura </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MasContainer</t>
+          <t>Contralínea</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNNXFxaWJpTUdsM3VDanY2YTBJeGNHNlRRM2hlRXp2M2p2R2FGZElUWUVRQkNjQW1OOGhvVXdUd2JtR0U3RFR6WTY1OVNfNHZidEFzU21QQmNaUTFFenV1ZnBVd3djSzJtdEFhZ3RtZ0FyelRKVWFEMUZkY3hubEhiZWx5NFpScFdoTUJ2SHBCQVllQmlJbW9SZnJQdEVQMFVZanE4SzRleU5Yc1YySnFQdndHUVZzaFlFUHlwVUxfMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPYTFkSHN4SXBxX1J4TkZ5WXNJY3Z0YURYTFpVb19URmhpakx1a25kQkxRV1Y0MHVJS3NqbzQtNE14SXB1RUVOM3dBZU0tbm9GUW1tQ2VoWVRtcHp6Z2w1UTRDTkM4am9KZ1JYamNOVGZUVjZCMUVmcEljNjdkNTlhczh3NW80MGh5c1RGWmVteWJ2eTlxQjhiOG8zYlBrdFRWQVRwZjB6a1dBSXNHeE1kOUpTZWJEYjZaajdkSHZBeTRhTlpqVE5venBHR3poZm42Wng2V0EyUQ?oc=5</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1</v>
+        <v>0.26</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>-3</v>
+        <v>0.78</v>
       </c>
       <c r="H40" t="n">
-        <v>-4</v>
+        <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>-2</v>
+        <v>0.52</v>
       </c>
       <c r="J40" t="n">
-        <v>-2</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-11T10:54:17</t>
+          <t>2026-02-16T23:44:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cleveland-Cliffs Stock Falls 16% From Recent Highs: Here’s What Analysts Are Watching Next - TIKR.co</t>
+          <t>EE.UU. está considerando ajustes a los aranceles sobre el acero y el aluminio, según Greer - Bitget</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TIKR.com</t>
+          <t>Bitget</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxOTmVtUnhscmt2ZGNxU2dPaEo3M0FnSkFiNkJkbkdMN05jbGpOSUNoR1NEajBNdHNXT2ZxV1hVbXRjOFQtY01mdkNHOWtkbUYwZm8tZ1FYLTdqNlJsUENfMHY5UGRBZ1ZGN3kwVk1VRFFab1dtem5PbWoxSTNDZTVMNDN2c0xwYkpXZXdhRWJYejY1UUUzd3FzNzhFWGZ5OGhmSjROODVFTm41R0J6djFFYUtXUW80Xzg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1KM0ZIckNTa0J1d2JEZy1obEZqU0JadkVCQXN2X0E0UjVhTU44QnRwOVJKVU1iaVBCRl9kWmtJeExibDItVkRVRVh6amsxOGJPVUV2X1pfa3BnUGFxNDJId2Nn0gFnQVVfeXFMTkV3UmRudWVOWEpwT0dDRDAzSnlhRHBSMlZXcGl5WXBnVkFaMG1YVVpmMGZTZ19CdEJ2WGlFTGdEbHE1NzhkbTJDcnM3RTU2ekhSRURzdHJnQzBxUXpWQk1GZVY1V19abw?oc=5</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2274,125 +2274,125 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H41" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-11T10:33:10</t>
+          <t>2026-02-16T22:29:15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Subidas de precio en ArcelorMittal por la mejora regulatoria y la previsión de un ciclo del acero fa</t>
+          <t xml:space="preserve">(Multimedia) Canadá y México buscan desarrollar plan con minerales e infraestructura, dice ministro </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolsamania</t>
+          <t>Xinhua Español</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQTWFRMmQ3TVRGVXFSeTQ1dmhUa0NvR2RsZDdhTVJoQlZRbld4dzBXSmJOZU84YXNxbENTdTEwTDVxWjdvSXNCVFotR1VSV043MzRCNGVUU0lJc0tuR2dBVDNyRXJwbEU5X202bGVUSEZncDk2NVpWeV9GTmI4WEZ1X0d1Sm53ZU5HRlI5TEtWaFY1YUFPV1FCVFljQURpOTVJaDdNT01lV0g1Q1l2NGs2UmhHeHFWa1FiTVc5R19uRzJXbmh6RkxPdHZ0a1IwSXF3bkxobmdBdUh4QUhZcVHSAeMBQVVfeXFMTWt5b3dxbWVINkMxMVpoVlBBSk1JVF9iSnJwN05uRFQ3UlNuNElfaEtpdU9ZRlU4UEptX1hKbnFYLUJtUEh2eklKMnE2UmlEaFVRcGdhb09mcERadEhjaml4azExUWdpdFFkQU4wMFZ3czR0R1RpakhKUHdOOWlMUUtzRUNkcTc0WmoyeW1xSVRMeDFMbjBQTlhtbi04RWV4bWJNb1B3S2x4eUl6aU43Q214d2tCSFlpMnB6VENxcGNZcDhKa2U4Slo1b3VGdVNWWjl6YmQyTmxCTTFIQU82VXJRRzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUHNtTzN6ekV4TDk2VGZ3aXk3YklhMWJ2NElXSmJmaDNPTU55cy1MdDh1VWtYZXZjSlItTVJEM1BJNENoWVJUSnhMTGV0RDV1WXU5b1habWRQcmRqaG5Mb1pWdGhDd2djbHREN01jM05rR0k0WlpGVldNb2s3bl9kMXBVYUo?oc=5</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>0.78</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>0.52</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-11T09:40:09</t>
+          <t>2026-02-16T20:59:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Macron impulsa el horno eléctrico ArcelorMittal Dunkerque como modelo de acero limpio - ECOticias.co</t>
+          <t xml:space="preserve">Sector electromecánico en México busca certificarse ante expansión de inversión • Infraestructura - </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ECOticias.com</t>
+          <t>Forbes México</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPTEMzOXpVS0ZadDNOZHFlRFF1ckoyazhRSHVRQ3ZWNzRwS19lUmJLZkFQYnVncHZfZlhTQ1VGaDdJMmQ3WjFzLUYxZm40VTE1ZHVVN1duVFdCMVpROElseHJ6V09tTjZ4Q080MzlGZmNwUFN6NlNGMW43Q3ZRYktwSjN1Sm9JTTBZVGtnTlpvQmctX2c4UzRVUVgtUmpJZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQZ2xDZWlKWWJZQmxhQkpnVGFEcnMwMWdaX2JhZkNaNlJBUEF0cmNMTkxsQTBjQ3N5YU5WSFkyS2pOTGZZS0kzN05oNlNLTGt0WVN5TWNnZFE4dE9jbDJYRkY2U2diT1ROVnF1NUcyb1h5WW03Y1ZSejFuRU9TcEkzRHlSQ25EUVAyZEkwRUZoNl9DNHZkalFaU1VtenZpeU5LaTNzaQ?oc=5</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0.26</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3</v>
+        <v>0.78</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0.52</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-11T08:52:12</t>
+          <t>2026-02-16T20:57:25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Precios del acero verde en 2026: primas de hasta 170 euros por tonelada en Europa - El Boletín</t>
+          <t>México inicia investigación antidumping contra acero de EU, China y Malasia - EL CEO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>El Boletín</t>
+          <t>EL CEO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNTVZGRFQ1U2lrT2RYdzNINEFxLVIxV2M0bTJ2OFo2Y1EwRzJsR29BM3lhVlZVNm5DdldTQTZkZ1FNbnBZZUFqSnRhVlMwVUJmSERCUU9NazhqRXNrUzZfbURxc0k4SnFUekNpZDhQYTFEU2NNUDU4OWUzN2NUSGx4S3F3bWRTRWtIODRYVXN5MmZQUzctUzlHOXZUZFlMbjg4ZTl4TzdHQmxxbU3SAbABQVVfeXFMTjBYQWJtRjJsNnJNYS1RaGRNY1UxMndXTi00Y2Y1QzZ0emtJWGtUNmp4a2pnd1RXdmdlZ2NMeGJRNjU3S2QyM0oxNm82WlRaQXNsLUt4b0x2SklwWG9aVTVkWDBURTZ0TWxZQVJ2RzNpNmYyT2x4UEZCSnFiT2lETkY0UnY2RDJTemg3a1JCQmJJTlNua3MzcFBBOGpVeGR5eENBU3I1c3dOZU5keHJTY1A?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxQb2ZfazlCdERaTXB1SHF3Wm1lQ1BpRE96MFVZZ1liaEtyM0dsY2ljaERobDFpU0RHWlBpMVA3NWxTREhVQ21fNVVGdWV6T09qMkUtUVFHY1VYZHhOZldwSUgyTDJBVk5CemNZM0VLNXNMaVBSOVlwZUdyR3UzZDAtWHhiTmxHek9lNWN6aURsQTR6aEhISUd3bGJlU0ZLaDRJMHR2eA?oc=5</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2400,41 +2400,41 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>-0</v>
+        <v>-3.4</v>
       </c>
       <c r="H44" t="n">
-        <v>-0</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>-0</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
-        <v>-0</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-11T08:05:37</t>
+          <t>2026-02-16T20:55:16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minería de México acumula caída de 7% con la 4T y entra en proceso de redefinición - EL CEO</t>
+          <t>Secretaría de Economía inicia investigación antidumping a aceros laminados en frío de EU, China y Ma</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EL CEO</t>
+          <t>La Jornada San Luis</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiaEFVX3lxTE1MVGU1ZG9BYTF2T3lMVm9JME10SlY2ekMyUThWS1RMa0hjUk9BMy1uQ0s3SHdVekVhMHp4RzRaX1d5LUhMUUVNSXJtajBiYk9GYXRXRVFmUWJYWWxMcWZDWHo2eG9JcW1L?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxNLXZuYVAxMVhqb0NBb2w4b1Q0MTNfYlZYWFZvUkFCeUh6c3VsZGh1V1Q3T3dKbVJHSUI5Z1lUbElBZFY1ZXpNaVlRLUxKYjdIbFV3OE5odEJOQ2VLaGQ0Q1VPNkVseVZ1UE9tMHZmNFdjMDg1ZnVYU1Y3TWhjNmlsekNZMHJlc0ROMFZTUDRBQ2Q4VHRuYnVHTHMtZ1R0Sno3Um1uN2Jfd3lGWVh3YjIxZlJCaHB6ZnkzRS1sdFQ1dk9SSnp3R0h5ODkzQmhhNmUtb0tF?oc=5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-0.3200000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2442,121 +2442,121 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>-0.9600000000000002</v>
+        <v>-3.4</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.28</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6400000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-11T06:37:32</t>
+          <t>2026-02-16T20:51:03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precios del acero hoy, 11 de febrero: El mercado interno se mantiene estable, los precios mundiales </t>
+          <t>Guerra del acero: México inicia investigación contra China y EE. UU. por dumping - debate.com.mx</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam.vn</t>
+          <t>debate.com.mx</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOd2p3a3JQZllFSTlQT3lOanp5MFp4SlBOR0hZRkVTZVVhZlQ3T3RpR3NUYXB6eG8wT2xiak5TNU9wcldCNnYxUXBMaVlMUEZOX2x6R25WRk9zOGpmSFpaSzBaYVFMUW5vV2M4TGVqaXI3SlBzdzViTERFNzVqLS1TcGZNZ0FiWjV4TU13QU5qS3ZIM3BlcXNZZnN4RkNvZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxQVERQWGNUeUlMVG5xRzR4dk1Pbnhob0JEYmFTSnRtX1d2YWtPWGY4QUhtR1V0b0RlM1lFMjZSaVlHbzRPbHY0NWNVMEZXNzhEQTRQX2tCejA0eEdSNFQ5ZU5INHVVNjlUbUtHVmlZOTNJbjhsdVlZcElfdWZXQ2c0aTNyM01LY3pIbWpkdlJfSHBfYVVrazc1d1dWekFlZTduX2V4UWdNQTdaZFJtbHFSbU1ZUjBXdnRkOXdwUlVUWFJubDl0bHdwUXZzUmZCd9IB0wFBVV95cUxPazNGX0Y0ajRxU1pJZ2lUMHZTTndqM1RMTlBTT1llNHZSU3Bsck4wWHR1c3lVdWVtbWFnU1dzdS1VcUJNMmd3THAzVzIzdTZ4dHZRX3pvYzM5bHhaN3RaRE4yZ2lScjV2dVdSSEdVR0tCal95bWJHTDY1cVJxYkdINm83U0tHNmsxZEFYSE1VWXBvbTBOcmNOazA2OXRZbS1RaGRwcGZvX21uSmJqMUFIQ1BRUExMR3B4QnlLSWNkVW1xbG13MlVsR0o5SkJuS3l3Wjhr?oc=5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-1</v>
+        <v>-0.34</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>negativo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="H46" t="n">
-        <v>-4</v>
+        <v>-5.100000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-2</v>
+        <v>1.7</v>
       </c>
       <c r="J46" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-11T05:14:35</t>
+          <t>2026-02-16T20:23:56</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Boletín informativo extraordinario - Impuestos Corporativos - Deloitte</t>
+          <t>México y Canadá alistan ‘plan de acción’ para inversión y comercio, al margen del T-MEC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Aristegui Noticias</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQWk15VjJ4SnNUczEtRWp1ekM1ejNfRzZqblBKVzhYSmNGUE5rSFpiVHFsVVlXYVpCV19rN2ZKRnp2alB6VmFxdHZLMWFXWmh4d1pJUm5rY2VHWGhBdWU3cmVjVWFJTENwOWtWSUl0THQxa3dzOTAxUkd6X1Y3TWcyUFNSLXFOM3R6Zkc0T3BZNGNFanM2Q3MtdXVPU0ZUWnJyTTZmTmd3Q010RXZyQWtBd0pJeXBDVElLT2t1MzFMUQ?oc=5</t>
+          <t>https://aristeguinoticias.com/1602/dinero-y-economia/mexico-y-canada-alistan-plan-de-accion-para-inversion-y-comercio-al-margen-del-t-mec/</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>positivo</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>-0</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
-        <v>-0</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>-0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-10T22:56:00</t>
+          <t>2026-02-16T19:25:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sergio Argüelles pide más inversión en infraestructura logística en México - Pulso Diario San Luis</t>
+          <t>Ebrard anuncia plan México-Canadá en minería e infraestructura - La Silla Rota</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pulso Diario San Luis</t>
+          <t>La Silla Rota</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNNld5eFFPX180dWRwNFYycmhLeTNTMG5vS3JUQjZqZlpsYVlXc1RRRWh2NTdoWE1ZSzl0RVhGNVJNRnlHUW5pQlVHdElvVWRtejdNS0lYVFRZNGllU0VCam5TeHdYZWdlZEFNX09TUDdISS1YaUNNMEJkNW8zSGtlRnlHTHlFUFhlaTVISGxmOFd0WnY3QjlpWkpRNm11M2VUTWfSAacBQVVfeXFMTjBiTlp2eFVESkM1RnRCUDlkWVF0dC16TGU3ZGJXQjFTTTliMUh2NmJ5aFN2cHZFTDNzang4V3FCZ3BkNWY5RnRkT3Z0YWZiWDliVEx1QnFSbVhiN1J2QktiSTFSc0VtcXdKcmNQQ2RnX096aEhJQUljSWFoM290c2lJa2Z4djR3T083cG1VRHk1Ykd3RnUwU050eGFQNS1ZUExpdXBiQlU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNOFMxYjBoenZWX00yVzNScWtNSUtWdTd2d2xYSVVNVkM2emFQOVF3QWNVX3E2VVIyTlNZWHBCWXZhcjEybWxRdWktbzdCaDlmT1UycElLUWxvOHNIdm9hLThEWGYzaVZMUkc0cVFqaWN5SG9rY1RieEpxcVNWSFVROF9mQUg2WFA5cll0LTR3THo5UFlndmxua2s3aUFlS1liOEx5WjZjRzZ3bGQzTlN4VS1FekFSUdIBtgFBVV95cUxNOFMxYjBoenZWX00yVzNScWtNSUtWdTd2d2xYSVVNVkM2emFQOVF3QWNVX3E2VVIyTlNZWHBCWXZhcjEybWxRdWktbzdCaDlmT1UycElLUWxvOHNIdm9hLThEWGYzaVZMUkc0cVFqaWN5SG9rY1RieEpxcVNWSFVROF9mQUg2WFA5cll0LTR3THo5UFlndmxua2s3aUFlS1liOEx5WjZjRzZ3bGQzTlN4VS1FekFSUQ?oc=5</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2583,85 +2583,1723 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-10T18:37:57</t>
+          <t>2026-02-16T18:35:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Boom de zonas francas de República Dominicana impulsa demanda de energía - BNamericas</t>
+          <t>Investigan aceros laminados en frío de EU, Malasia y China - El Diario de Chihuahua</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BNamericas</t>
+          <t>El Diario de Chihuahua</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNMW5JS1ZydU9mTGk2YU9pSFpGdDR1LTdCSjJPR3NrXzk3Tko1TWJaNWNjYzRMcG92SDU3WHA4MjRmMXVjX2JhRlpCZnJLT1NxeWZocGhnWHFQMzVsZzNvQm9zTFhEUm5Ic1pFT2k2VlE5dnZRa05CdTZ4ckFPYmp2bG1WSFI5ZmNZZWNjRHpvc1lyOTdMN0IxYm42cWc0UjUtSnZGZUR1a1h2RUZHXzJyOEQ5UTJzWWg3UUxPMUJPSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxPM2J1WW9OUDZZc0xIbGpHbWRLd0FBX0pOTmdlWFFUeFlIWmpCbDVRVkpiWktRemFhcXY1RVNyblpHVllfQVhqaXBubXdsakZleE52NHJuaVNXZDZicUk1MHZ2azRJRFZYNS1fQzIxYXFkX2tQRmNlYWJnc0dPOUcxRGFUYlR1blV4ODNWM1NBZlZoUDhpcmdFYUtsVkhTU2MwS2RXRFJObnkxbU4zeUtabmdiTDVFM1ZMTFkzNWlJYXVidXfSAcgBQVVfeXFMTlk4R2tUR2VtVzlpUDRicy1PZzF4QWVPQjlBaVRxV3k3NVFuX1g4UTBvR2Y2WXVXc3JqMVVTQVUwZUdTanhISzVSZ0w1bHB6T1QzVXFNVkFvVUNLbXRFZHZLU0gzX3RQa3BVcEd4a0FQM2JyMHhRNmlLX093TVBEUUhkTVZLSHc0UWhjZVVWVkkxN2hkOWtRVzhaVkhXOGVWMEdUN0NHMlhTem9rUFVlbDRiUVJackViUkJfTDhsSGtSNGxYTUhDa2c?oc=5</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>positivo</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>-0</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>-0</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-09T08:01:44</t>
+          <t>2026-02-16T18:03:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>La automotriz china BYD presenta una demanda contra los aranceles de Trump</t>
+          <t>México y Canadá presentarán en segundo semestre plan de acción en minerales e infraestructura: Ebrar</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Aristegui Noticias</t>
+          <t>GBM</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://aristeguinoticias.com/0902/dinero-y-economia/la-automotriz-china-byd-presenta-una-demanda-contra-los-aranceles-de-trump/</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQNERoRjRXYnRsTVFtQnljeGhkMThBblo5MGxyRi1mOFBHMnpNaEtsSzBITnpXN18wTTBuX3RCakJ2ZXk1bEs3N3AzYWlieVk5dnhrRVB4cVBTYkdnTVozLUd6T180R2ZIOWFZbk5DdzdWZzZOVnNIMjdDdGpLN0s1ZW96MDlBU2ZuSkNrRTRRdlA2S0theW5JV2JNNW5pbnFuTWx6ek9PY3ZnNF9qS3I4ZUlVNThBRDVlS3RTaTFQNm5LMVg5OXJCd3dEWQ?oc=5</t>
         </is>
       </c>
       <c r="E50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-02-16T17:15:03</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chile: AZA eleva producción de acero verde y reciclaje de chatarra tras inversión histórica - BNamer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BNamericas</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPa0w5UGJUSUkzel9DcG5rcE5FSVpIc3ZtRVN1cXA5ZS1vS1ZXMGJYN2sySkxZWkF0cmZJMHZyMG1aNTdNZ3U1bjJSck54dDFMZXVpUGlJMXUzVzQyZ0JQaVlva3EwcjVTZGRqejUyRkFPaF9KNGxhYjk0cXFKcTU5Sk1HS3JLN1FwaF94RWV0RDItNkJnVktiR19ETXl2YzRaZ3FIUS1hT1Q3b0pZTkZUeml0ZUZJal93YlkzWjBLamgyUzBwM1hTa1FEYw?oc=5</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-02-16T15:04:00</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía emite nueva NOM para productos de acero en la construcción - Forbes México</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Forbes México</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNb2FLLWhhMk12WHFEMVdCZUFZV0FaQy1rOGxYT1haY2ZoSzNDby03Wi1ySm9iUWJHWU5PdVVCVVZGSzRRZUdMdUhZaE1PTkNRVzZWODlZNHhQc0J0dERVTU9RYmx2am9JWGZ4eW04SGJOcWFZb3VscTctVXFiLThNZ1ROelR2ZVBEU2JZMlQ5S2JTYUlQV3dfQXZfSWdKb1dZQkZZeEM5NA?oc=5</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-02-16T15:03:00</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Aceros AZA eleva producción a 511 mil toneladas y supera las 640 mil de chatarra reciclada en 2025 -</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Diario Financiero</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPRkhRbEM3NUROZ0hLWHdON2JhQlFyVGkyUjkxNVQ4S2J5UnRuTmxJM0lNT0VQQ0xzSlppMDRqY2FqaDZvcUduN2hLdUY4SlA4aThrWHc0eE1mNkpvT3BhSXV2alFFdUt0OUNOVS0yMnVCTkFMRzR2T3kyaVdwWTdZcExVWEdnOF9OV1ItbjJSbVJLQjdKY1BrdXl0aV9MYXpCb1FWcTVkSlNBeWND?oc=5</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-02-16T14:09:14</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Tras inversión histórica: Aceros AZA cerró 2025 con 511 mil toneladas de acero producidas y superó l</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>diarioestrategia.cl</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNUC16RlpzZEl4bzI1Z0JGX3B3OEROSU5uWXhOcW9sVjhfU1dENTF4eUw4aXpKVHp0M3V6QTdlNWNwdk10aGY4WXJVWnhJamEtQ01xWFAybGxPUU9Fa21qSnpxVnY4bU8xX1dIZWtrNy1PYUdwenhlU1NhMVEwb3dtYWNHbFZqM2hXY2dJNWd6Sy1KX0ZrMnN2RjJxbjdMcmNscjdQMWVPeXBqT0FYeTA1NG1ra1R5em10dW1UTFBVN0xuMVJMR01kUVZkRVZkbmk3MXp1aFBkM29KQ2s1ei1KaHVSY2lJMTlTdFRrUE1NVE9tWmMxWFZKSHBnQ3VWRkZJ?oc=5</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-02-16T12:53:00</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sector inmobiliario y constructores van por más certidumbre y financiamiento - Excélsior</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Excélsior</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxONDhybVBNOTQ2LURNX2lEbFA5Vmh5dFFRejZpYWFxSmkyRkFMVWRhM3JGN0hSZjF1R3d6dV9OSmMyUDE4OWN0Nm5hdTYyd3FIbWpMV1NXU0xyM3RiYWY0TGJXRnB5bkEzcWhsSjU2STdEYWFmY3lKWEhCUHFseUtmTHBydC1tTl9TXzV5UEZ4V0xoajdG0gGUAUFVX3lxTE40OHJtUE05NDYtRE1faURsUDlWaHl0UVF6NmlhYXFKaTJGQUxVZGEzckY3SFJmMXVHd3p1X05KYzJQMTg5Y3Q2bmF1NjJ3cUhtakxXU1dTTHIzdGJhZjRMYldGcHluQTNxaGxKNTZJN0RhYWZjeUpYSEJQcWx5S2ZMcHJ0LW1OX1NfNXlQRnhXTGhqN0Y?oc=5</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-02-16T03:02:40</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Sector de la construcción en Querétaro reportó débil actividad en el 2025 - El Economista</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>El Economista</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxOMmxHYXR4TXdIRzBkVVJIbHQyZ2dhWjVMeFE4YVdmd1RHZ1RnUzRuRmhyQVNBSHVROWdrOFNtSG9VeGFSUG1YSy1BVGVHUkJ3QmJsNUQ0Qmx0S0Vhd3N6SXBmcnh4LUNtS1hwR0RTR3ZWVEYybmx1OEFJLXpMSFowQTY0M0xJbnQtdWtlNEJYRG9uN0R6czdjTFNTTUtZYjB1WEZvTXdJWDNaUHozTEZQTUNMZWzSAboBQVVfeXFMTzNFdnd0Y29yWGpEa0x1UkljMWVvOU81dXZBa0JEN0NjblhzbTJycXpKbnNUMHNvQk5CVGh5eXZFVTlLSHo2OFBkdVlOeVUtWTZ3WDN3RUlFMW5EQUE0S1hrLWRZY3BfeW1EZHNCOHdKejFtU2NWR2xjOXo0TEV5cl9vSWxURWtHdnZ3YnRwTkZtbjIxdUk3aFBZU0tHUTNmRExGZmlBR2lIazdYTmtEZnpVODhvWWtScjlR?oc=5</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-02-15T20:09:26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bancos que respaldan el acero ecológico aportan “soluciones falsas”, según un informe - bloomberglin</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>bloomberglinea.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQcXh4bUE2R0xXQkpTUG92NHptZVVaUU5DaTQyR1ZZRXBGR2swS0F6OThYZXFia3hRdHVYLVY5V3c4VVZWTVl3M1lYeW9rZ0Rid3Q4Y0pLM3dmVVNadW1IaEttMmJLelFsZ1VMWkdrZDBhWXhwWDBhNTB2T1FpN1I3c3d5Rm9JbDl0NFBrNXlZbDM4VFlvTmpOZ3hUalRUZ05IQ2V5UEZsbXZoc1o3UHNHRGVqOGMtVlJzcmhQZm5yaWRIenfSAdcBQVVfeXFMTkttNGxZUXZLOHVwcmhUWWhmN3FUOEEzcWY3WUJnS3N6aUhlQ0QtSG5tVU5nQ3dzQ2QtS0MwTnp3MkxmbWRDQjBIT1RweFFIQThLQ0g5ejFKVklLRlVGenk0a1lVLVFwZjZNVVJEWWhaOXZhZXROd0w1aXJFOVdKOUUyNzUzWlFtS0JXUWZ6c0JwZmxiOVM1SEYxaF94dlRGelVwazE2aWs3OXNFMzFQM3lQMWh4cjllVkwxZkpzbGJRa2NtczgtSGZYOFp4VTNHSTAwTUNVOHM?oc=5</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-02-15T18:30:00</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Variación en el precio de las actividades del sector construcción - El Economista</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>El Economista</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxNWTVzc3MxQjBVTXE3a3BzZ29EMFZIdDZqajdrc0tWd3Z6UkZhT3REWG9QZEhqVWF3LUNkM2ZVYS12dWhJTnBQa3UyMHZieWJUX2RRRDcyYzM4bzJtOWdBbW51WU5SWm4weHRvZzMzdG5GR2JTTFFmTkNxa0xFaTFSWTFTRTVNRk5SUlJIUW13ZVdvODZRZE1kN2RQOEdudkJIZzRXVmJRQy1XbUtSUm1wWkRGUWnSAboBQVVfeXFMTzI5VTgtTzJ2VncwdThSM1huMVlMQmZvbWRGSXNfejBnaXdIUl9ualNMMkxETmxHbTlxVjBJMl9ZTzJuRU9FQzZiZkkwQnBzMGphNHc4bFgzVE1VOWxvU2tWX0pkUWRjNmpXY0pSVVJQcXFfX0o0YmJiZXFqX3FyYnhmOHh0XzhVcE03OGJDQmNaNExCVkI4Sm9XYVVQZVdnaFBfRDd0NEJ3NV8xcHd5R0hSTy1CbnZGb3p3?oc=5</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-02-15T18:01:17</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>¡BAJARÍA TRUMP ARANCEL DE ACERO Y ALUMINIO! - SEGÚN EL ‘FINANCIAL TIMES’ - NOTIVER</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>NOTIVER</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPN1NFTFJaNDNHNWlrR0ZGcmozWmltQmtRaXdsaVdDc3BuNExHdFZ1eURmSUJYbFR2YWhXSWxjSXU4VzZTWkhtb3lUUVc3eU5KZlRzZVRYYXJkQk0yMWg3aTZ3YzZxS3R5Z2dSQ0t3eFZPMEJzSXh3b3N2RDZCS3diVlVR?oc=5</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-02-15T17:33:00</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Presidenta Claudia Sheinbaum presenta Plan de Inversión en Infraestructura para el Desarrollo con Bi</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gob MX</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNR1plamhZb2VOaHNsa2dWV3I1LS0wVkNzSnBZdV9WbG9zazRlazgxUVdrd0NzY0ozMkwtZEMxc1ptQnV2MVJjM2hPUDZ4VHJNT2syczc3dmNlS2F6QWg0YV9TWHF3bDg0a2J0RzNxQkhoaThGbzh3Yjl2cVNMN1RWYU9mWl9kLUtnTVRidXF3WUdtcnFwWGpQNG4tbjl4dWNCR2J6N3prZXlLRmNTeHVKMkdETHBaUU9UVnJBY3V4ZEFjMnotdi1WdVlncFdNM0VKOUtCMzI0cGY2S1Q3WktGcnRkNXI4d1FET2ZvUEhDbGRQX1JIT1MxSzhmbldZOS0tRTR3QkhB?oc=5</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-02-15T16:20:36</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Trump impone aranceles al acero y aluminio de México y el mundo - MSN</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0wJBVV95cUxNXzhiVnczNmhqT0t2SWpCdHJkRmc5VkF3QUR5UVJGa1N4MGU5MnRPdHVaVjZDcEkyaGpRQ0wxLTJpT3A2OTVuUDlmaDlyYkRpVXlLbjJCNjNIQUd6eVk0UGZzLWhxak5MSHNEd21kYnpQOGZtNzVreWJGSmVncU4xSFJONDVTNUhHNDFkcXlvZS0yZGlLbmNQcWNFdW1TZ0pEQk5RUTZZXzhSU1czYUNGa2h2TngzTjYzbXgwNzhnb3piRzJlSW5LbUEtcjU3S1pOc0lPOC1aWVlILU5BSVVtTExoUVJZNU43aUVyTDZnRzR2d3RFRHNDTDhIQ0pycngwSnVpT2F3dlNBNDZpaTRBTUtTdG0xZTVvc0tNV0VKWU9kNXdZNllha2hfejFRMjRKakgtUWFIWXBLTi1Sa2FCSkdZSng2MC1xYW5EZE8wdXd6Vms?oc=5</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
         <v>-0.34</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H61" t="n">
         <v>-5.100000000000001</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I61" t="n">
         <v>1.7</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J61" t="n">
         <v>-1.7</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-02-15T16:05:43</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>China podría integrarse al T-MEC luego de la renegociación del tratado, incluyendo nuevas reglas par</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>El Imparcial</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihARBVV95cUxNYU0wZmp5SF92LWpZc0hXUGthLXRLSE9oZkxFSmIyU1Q2cFJSY2tnWWdwT0Z0ZXVDaUczOTg0VVlTVEIxRFF5TE1HZnRpd2dkWURHVEFLM0lKcDV1TlJqai1wSWFXNXJFaWsyNWFObklBNDB6QWVwcU11ZHNfRnZsaXJxMkFCNGtibHB0QjQ2bTVMckNyNW9sQ2NaaW5CblI0bG5DNzllQjMwWEVodWc2TUVlX09HbTBGMDVJOGtqSnNlZlZmbFBWNVZMcVdBVmdqR1dzUzluWEh5ampIYklyWGZWVFlKS2pwZUZ1WkIzOXA5TTFRaDJZSkU4MmtjT2lyRV9TelV0bGZvd1ZFemloUVFKYUZTTnJPSi1ETTVKd2ZIZHBwV1didGJUT3ZkZzdySWdMRHNoYk0tbmo2Tl80a1pNMUl4RnBqcjBFaEgzVEJMLUJQN1V5d0hPMmdkRlplZkdUOW1WbUd2ek5hY0pBY0MxbndYUlRjQTZSMFIwSXVNWG1IbkpyVUdEcjdCc05HVGo5QWFHclY1VjB0U2RsNnNWTVhLakV6OG1od1lQN3gyanctWjRTc2xYNWxYekRtbl9DaFJYWml6STc2Z3d3Y0szQUJtQkVXTUN3N25Da3p2YXVEMnlpcFg4S3Q2YUlWbF9VLWJ5Y0x0MENKQnRCUElMc3HSAZ8EQVVfeXFMTW04VUVsNW9jYUptbjFvSW81cG1LN05Fb0Q0M2I3R0pIZlZ3ZmI2YnJCSHJkWGozX25mcVhfUGg5SHd6NUpVQ3JfOGpqWkozY2l2OFF0NGQxZTJYYUNQNHZXUnRScy1Obm41Y3hGcHZsT1BBT1lkX2xkZ09RdFFkYmkxNEloSzlmVVN1dHRySUlTVE12SGc1Y2p0elQ0NFlNbDY0OUprUkFkejBNYnVscC0tQWNzWVhLOFRYOElNeGY5TDl4VFdaSHIzTjZxNFZVclBOaFc5eUlQb3FRYWNCY1NWYk9INExkbGx3M3dCZGxkMVc4MURpSnA3MVAwaENUTjFUZDZFMEF2Vjh4QUVZX1FsV24xUEFtZ2pMNWRQRlo2b2FhWHVQUTVFR0VQQVZFS0xQcERNdUtFUVg1bUZKWWFRTjBBVVlKY1NialBwWjh2a2hiRVExcDJvTFJaOTNoRVFhMzlNMnFmT29BUHFfdXUxdXlWcGRtbjh6N3I2dmUwdXVyNmdRRWRqM3J1dlBhOF9EUHpPbklNdUhzMHVJcEZ5ak92Rlg0SUdQWmlUVUdPaUVINGlXZ3BXMTRUbmROa1FQSUdEUGotaTQtVjYwU2JMR0staGEtN0tZeWhlM1FyNmtudmJ4Zks0RUpkcHFuU3p4VjVTNGN6b2RwN1ZOOXRraEV0LUs4M2t0RS0wZmJSWDR1REViN0xDSzNvYmww?oc=5</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02-15T14:30:00</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ajuste de Nissan golpea producción; se hunde 31% en México - Industry &amp; Energy Magazine</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Industry &amp; Energy Magazine</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxORDhNMDhEdTVWNmRiV0dBbkVNSERLejRsbE1FU0owelhzcEJuclJMcDNpV2NzZmU0UTZVa0pVTi1SQXdaNW9jN2RlODNOeVFjUlRjZW9lSE1WQV91em1GSGpuaWtPWjJhQTN1YkJfX1BuZHFhektfUllYWW9EYmh0Rk52N2FTRkFXLVZISnJKUTJvM0RQMmc?oc=5</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-02-14T22:58:10</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economía emite norma oficial para productos de acero en la construcción; busca garantizar seguridad </t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>El Universal</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxQTjJ0OEVLWWw2dFdEVjNDQjBWUWhhUVVaNlllQTIwMmkxWVd0VFU1bVcxMkNxRGVVZkYwVFNqWHlKN2ttQ0hZZHo5LUlLblNtUVhrSTRBLTlYbWVOVFFWekVXcWUyUTM0MGV2MUlpT213eENVdzJYZUdlNzh2V3lEOTBza3BRYWYydmtkbE1qUl9Yay12RzRRVGI2U1NBUV9jZlF5cVpXNG9MZGFzOEZkcEFjRUlmTDJaTjZfaWpOR0l0U2ZEWDA3UFo0eXZzUG1uc2o5OGphWdIB6wFBVV95cUxPeU81dk9oSW1COFFhVTl0bFZkaE5wZ2owdzV4SDJWQmVKSTNaVkhaeTRDblNmSzhtSHVlX3kyNkhxZ0d6c3FEYWU5bktHWFI5T3l5NnZVVV9VQWltN3JmYUtOams5b1RxdldFcjVJOGpsUmtBN3pTUzV3QWsxN1E0NnFScVJSNlFpUlh5VGdSV0ZTdC1SbERNZU9YOEZ4WGdObzRRSG54VlVtUkdGVWdOWkhfQTB5dmVQWDdTOEswT0I3TS04WDd6YURyaXBRT255OFBpaWxuSHp4YkIwdDlkUGtYdFpQNDVFMFRn?oc=5</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-02-14T22:26:00</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía publica norma oficial para acero en construcción - Pulso Diario San Luis</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Pulso Diario San Luis</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNeDRHS193M2tKQWlYVy1tRWtFYVFPb0FUOUtpRHFNMmJNcTRGU0VMM19EUGkyRFprZ3hRY29yX09TQTdMMjZzOThqN3hDN2RGck9abGFOQnBZME51ZjE4a2NDem1QeXBqTjZxSVpSeDhkeExtUldmX1VpS2VFN0JNcVFfc21FeEFKNlQzcTExbVpOVmlyYWJCOWhZQVZuUXlH0gGmAUFVX3lxTE0xTnp1T3RUQm96UjhnZ25GTWw1LU1HNEUyclUtbzNJbGZDbEhmYWdOazR3UDE3RnBWVmVJbi1yZHhLSm9ZaVNrM0dYaHpwQjlQbUU1Q0lPN25leG5saXNsS3JWT1ZfbWN2T1F5RXQ5cHpBZ180UE1MdW9nc3NkUjV5X1RZaXJ3VU5fTkFDZlRZeWJHaHQwZ0lYVDFXb3JSVF9uUzhtc0E?oc=5</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H65" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-02-14T20:32:17</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía emite norma para productos de acero en la construcción - López-Dóriga Digital</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>López-Dóriga Digital</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxNbEJMMUZaVTJva1VVaW1wX05haFNVSlhUcUxsZWE1elUwaVVGNm9UYXR6VVY0d3huXzdseldpT2J5MGY5TW5UZXhsb0FiSm9LWTBZSzJEYjktZzlLaHhxd2U5Y0lOaHFfMDBQSk90V0RVT1kyWlFqR0Z2VVpOVk44eFRqRURNNm5nTFhpcTdZX1ZuY1l4TXRjTnVmNHV2ZTRScWVZZnc3UFM4TzRvT1V2bA?oc=5</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-02-14T18:14:41</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Economía emite norma para productos de acero en la construcción - El Horizonte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>El Horizonte</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNeWVrVjloUVBUNGxkQVBWa00yejVfWWVWbHMzYTdQS1AyeGZmM0tXMEMyakVyUHQ3Tlh5YTM5QWRzT1RYQkJhUjJBdkdSRG1KY3NhYzhHalR1ZUlxQUhkY3lrWjJfYWdNNEJiMlNMakhYU2wxZ1JiS1lScUhBc25YNVotOHVTUGdOY0hucGEzVzNpVXlqak1nQjdxWVppM294ejNNMjZMU2l6N254Yl9V?oc=5</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-02-14T13:58:23</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Planea EU reducir aranceles al acero y el aluminio previo a elecciones - Tiempo La Noticia Digital</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tiempo La Noticia Digital</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxOdnRQdDVUZGdqRWlYVjJad2tsaXM2V01ENTNSMTliSXd0T1VwRm5sc3FMaU9XSTlvLW9rM0RxSXE5bnZna3cyckxHbllua2ZWb2hEMVFCZlFZME10U3dJM2M5ZjFPUWx4MWw0akZfSGhqLTZkdUhQRHV4dnBoVkNRZjFPdmpweGJNQUtuU1kwbWg4T3UwTF9ZU0FLZTVjX2VhWnpiYmo0XzZ6ZVk?oc=5</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-02-14T00:30:41</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Construcción: del ajuste de 2025 a la inflexión de 2026 - Centro Urbano</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Centro Urbano</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9zcU1QNkxVSjlwb2ZfbUhBSUhrWUE4NWZ4THhObG4yUGFvMGFiTGp1aUlXQ005OXhZekswSjZIci1uWjlBR0swc2VweW9ia2Q0eUw0R3pyblFidHdwcGxveXpBUEJhb0lUVjZ3dEtmVzJuY0h6S1NXM1Rncw?oc=5</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-02-13T17:42:18</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Donald Trump evalúa reducir aranceles al acero y el aluminio; así podría beneficiar a México - EL CE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EL CEO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQQjVQVmF6Wm9FUDVRVVpRUWJpZlc0cmZXSEpsd0xabG9xbVVqSmNVVm03SmdoSTdUVkVCb09vUENhNHVQOVZRSHBpMVAwMXpHSUM4WGlUMVcyS2MzdFBoZU1VQUphSzdaYWoybUZhNzRqejRlOE9od2dhcWhzVzZnejdBOFB3U3VJOTdtR1R3NV9TR2NlRWdHUkhXaVE2WktFTXJJM21CRUtnazQyUGdLTkN2YTVMRlM5eUhz?oc=5</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02-13T17:20:56</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Donald Trump evalúa reducir aranceles al acero y aluminio ante la presión por el costo de vida - El </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>El Litoral</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxPYnR2N3ZleWpscGNYM1AzUWNyX0lGNDRqRWRMbFJrakQ1NkhLYlVMaHRXTEtoblhzNmhfbmRtZWt1TmZxNlRtLUVxTWhDa2VtU29GWExHcWZTbEROZGs5VFRfSGEwVlNKTzdxSTZXUU5lY1lsV1NDOGZUM3dyampIa2kyc01EM2VpRk5ZcDNiOHdUQmlBQ3M4Q19hcU82Ti1uWDJUQTBGMjBKMHRzYmFwYV9kVmVmbm43NktTY1FqR2hrQ1lGb1VQWkoyQjHSAdIBQVVfeXFMT1A4Q0JpSWYyMmRTN3Nva04yc3ZZcTJ5ZFVxOHRDX3NBMEoxemNIXzlmeklQakdGay1wVENTQ0RCNmlyRDVlRGFCOFR1cDlraEdKeFZWeXRQTDBsSk5qY0FVUjNMV3R1MWw2WnJkb0hVQ0VyVlgyUTRaa0lrZzFDbTRIOHB4REk1Tkt3YnNNNnpuRGhNZ0N3aTJtMGVBOUFqOC00RF9KMEpDV3RWTjNuYkNRVVloN0stZ3hlS1p5S2NxZ1BDVVZLalkzSjBvUmJLN1BR?oc=5</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-02-13T17:17:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Trump analiza reducir aranceles al acero y aluminio ante baja en popularidad - El Informador</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>El Informador</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNYUVrc3ZxN09ETXZtZGFKWk1LZG43cThfbzJOQVhlNkUxTVJ6TDNHbzJiR3lFUm5FTlNJU29sbU5GVTlEZmQ5NmNCMXl3bmFnb3NidWcyc0c1Vnh0UXdtU0VBTGE3d1ZEYlh6N3U0MFROYjZ5V3dXVzh3bHdwcktfdHRfRGxBU2E1cWNrdnd0NVdJSTZtNF9MSnEya28yR2tlUEtlTkR1LUJLRWJWZGpncXpfUE8tYmtseWVnRFl2SHYwOXhoYVh3UjFSTTd3RDZD0gHWAUFVX3lxTE45VFdQeHRibVpySVZuTWdSRUxoelVhVVdNV1pVbUgyc29HeXNkc3AxcHVoa0hta2Z3UGgtR0ZYdWFXVnhIYVRsTDlYaUZlejBqNjVDNFJJdmotdnNSNExaLVVKcTlua1l2bklqYnVSdTFkSHpRUFA0OTNPc0JHbnNHelltSTByLXBUWFhtTmIwQjJEMTZ2bHRuaXpyTWpyakhwUGpKaTE3cDZ4NmFwQVUtVXBBVldHbWJfbFVZYnF2Y0hGcE5EWHBxY21pOGU3bXRLOWh4YWc?oc=5</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-02-13T16:10:24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Trump planea reducir algunos aranceles sobre los productos de acero y aluminio: ¿Qué se sabe? - El E</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>El Economista</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxQTVFQWmJCbWt2ZExGUXJvMUpkMnJUTk42OFpiRDJnSm1sd0E2X29LQ2ZGYzlHSHJtX0F4cmd2c3FYNFMyOTV4QktEQ3JGQUZLTmh4QlcxcGhjWTBfYU1mUFJiRUViOVFMNUZtRXpXYThOZWNUeDRzbFBSRTRBa0ZEbzJQRTBEaXcxX1FGRVZzeUduUGtVNEktbTdrWURLUUxHQTR5U05COXllUXpjSDNIS2lVU1pTcHdrNmlUdGxR0gHDAUFVX3lxTE0wZ1dvakNTaTJLelB6MDN5cnFqenRpTGZWNjdyclF4STNBWnNZSmFmejQ2cU43YW5fblFRQU42QXRCQllmVGwtUUZxel9UQUFBajNTXzBfdTl5bkNwdTBEem1JZlJCWkdFelpwYnZJWnl1cUZMR3RTRlBDcmJQXzBUZVJLOEprZms3TlBZREQxRldXdFZMcW1CcjBUUmN2SDFSN0hndEdSMlNrT3JEQXRfOTBMVmdhazZmVkxtdDJ0SHNZQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02-13T15:54:00</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Los precios de los metales se desploman mientras Trump reduce los aranceles al acero y al aluminio -</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Cryptopolitan</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFAzQVBYc1QzNW85djVnMEJvdk1zODZmOTEtWFBqdWp5eU5XdkNZUDhNZ3pTajZzNlV0bENUcjZlUFN3cEJsWGh6bzVqOThyNXZFbWM1MnNfRmJqNG41REE4cU5xUmZEd19oOTgtY0Y1STZIbk1G?oc=5</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-13T15:50:27</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>México presiona en T-MEC por aranceles “costosos” al acero y autos - Industry &amp; Energy Magazine</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Industry &amp; Energy Magazine</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQUXFPQ2NuUVIxcEVtVU1ta2VZME8xcjI5UHNtMHRIMVMxS3Rtc0tBOEVhR2pEOHFYcFB5SHN1NHp1eTdHM2FwYzYtbUduMV81NkJsWWRGdjNjbm11cmg0TElOMkdYbjhOaDBlbTRPaHZzQUM0MlpCTFJqMDRkR2lkTVY1b0c4d1JxR2ZrMWJpNjIwcU5lSkFZYmNyYmhkQ25p?oc=5</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-02-13T15:46:01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Trump planea reducir algunos aranceles al acero y aluminio ante presión por el costo de vida - El Im</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>El Imparcial</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxQTUQ5QmFLVmtYRW9uWTBTMmEtM1JZV3Z4NjcwUENuaFJTRl9qb2xPbHpaeGM2MkhEdDFOQ0VmcGVFM09EcnExNlo0THVXU3R5YmIyNS13d3RSVm90bU0zRGt1SFVGc1R5cnk1dF85QzN2YUdNUFFrNnRkUkhXbnJnVEpOdlBfd0Z0cGdIcWNlWWlVcTVkSENlZnlnOS0wcVQ2bVMxeXo2UDJBSUlYUnBYZjFTak5jMGtQaGptOFpmUERmRnpxWG9CWVZtUGZVc3k3SUxFUtIB7wFBVV95cUxPZ293QXpERFBwSjRvUk9ka0p1cnpCellqZWV5U0p2c3d5WS1sLWFBa0U4cG9tc2Z6dS1vdjdaNWRKc2Z2akw3UF9rWmdXUWd6Q3lOR3NhVmUzQVBITUV0aWF6SThXUFJ3YVZxbldycWZXMy14OFNKRWhiLVkyRHd2UVRwUmhmRHdKT3lLNDB5V0JUdmRnbVQ1aEJnTFJvZUdvU0hIbDVabUFiS1BmV3ktVzFtZUxWaURDY0pvdjc4Si1SVW43MDVpMDg3cUx2cms3bHRSUzJFdEFMdVp0MHROcTBYTVpIXzFkTjVNT21CSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02-13T14:57:00</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Trump planearía reducir algunos aranceles sobre acero y aluminio - XEVA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>XEVA</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQTlJnVHZIbVNRUVpnajRvTGxnSk1YZUhRNDRaY2FmZE9GdW1hNzlLa0tWME9wYXBmODkyWkdxdThwaEdkaUNhUkZhY0ZmMzJsOWZERjUzclgzMHRDS1ZZYUs1azNXWUc5a0ozeG5Mb0dnOHU2S3g2NlZ5MVVwQ1dxRFV1MXM5NDMwVmc3czBEVW5maVZoU0JmTkFzNWd2LTNWQkJfWTZwXzA?oc=5</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-02-13T11:16:45</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Startup estadounidense desarrolla horno eléctrico de una sola etapa que reduce 30% la energía y abar</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>EcoInventos</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxPX0VOX2l6Z2U5eWdTSmVRa29ZRS14SHYzWnFyVUhDNkRhTnVuYzJCSHZxY2VlZURvSWhnM3NaS0k4Tl94NEVRdGpXWFRhb1EzeDF1TnlQSGVIUGQ1LUZLMDU5R1kzUVhKaTd3Z1ZDS0UwYmZieHpIUkI0MkZtWndBeVB4U1VNMkJNZjJnLWR3SHlDUFZiQWUxeGYzaGVNVjF5UjBMQ0E1cXd6TVVucDlNNkE3aWo0cVdzWlNqTzZtNnEyNWtDRDhqSW9xTkVQYlFvYTJkcktR?oc=5</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="J78" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-13T10:04:40</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>El aluminio cae tras conocerse planes de Estados Unidos para reducir los aranceles - bloomberglinea.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>bloomberglinea.com</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQY3lOOEVNQi1oVkpJc2o2SVFGLXpTdlV4eGRNbVRzZElsZUhIVURETHhZV1Nhb1NXcHNZRWNsWkJfalo5SVJ4bEZ4YVNWdlpLYUh2eGQ0TzU0a1d3RURkMlZPVmNPRXlFQnFNaFlWdC15aEZBMFlSRkw2ODRCcFlvNDkzQ3JXby1KRnB6Vy1BN0pLbHVLVVFEY1BwZUJ4R3RzNGswVjJnNURtVnEwWEQwZ1JWZUctYVVsZlFmZlQzazXSAdQBQVVfeXFMTjI0OVo4aUVEdHluTV9vdE4wUlppLTNpVVNGN0hKZW9SNC0yNXdEdFZzOUltaDNhdXlXWTE5UUI0d25jeXhhOXJBTmcwVTQtQ0J5emFDem9OaElsV1k2VFk3Q0RuaWlmeF9hSU9SNlpYem9zbWZobzZLcEFVMmRpbGM0T2Q2WDU0MGFyOUNuZnZyX0lBc0F3endJaWJjLWo1M09zR3dRZFpYdnY2ekdYX2tQLXN1cllJT19vUUNuU3lOOXA4LU9mVmZRZGFiYjFOd2J1Z1o?oc=5</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I79" t="n">
+        <v>5</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:10:00</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Secretaría de Economía: Nuevas reglas para el acero - El Heraldo de México</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>El Heraldo de México</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQcDh3LWZlRF9iVF9jdzBPVzFySGFMQV9UejRkRVVOVHZqTmoxdEl0NGppQmRLRExob2w2WXZLUE9QUjRlYTNMakdrZExPNXgzeE5kQ0NnQm40UnJRR3k0ZlcxcGd3b0R3dlJtd2k2SEYtX1VXQ0tmUzExTHZidUNSZjM2LUhvZFRoRGh5Y0JrVVdHd3d4OS1lbkRBZndBUWJsRlJuSmJxWkxudVJOdlRDS0QtSnkwWVBDcEJ30gHAAUFVX3lxTE5pektrdm55ZTQyT0gwcXAxbS1hdHF5XzdPaXdZYzZNQ29jckNqQ0RrclRKR3FLRG1EYWM5T094T3RYN3ZiUUNpaklycTNfWFgyaHdSbXFIQjBzXzBvTmQ1NjFkcnFpQkdJZW90bXBjb0VhS2J5akJPVzNkY0NLZkx6VG9YdGZLTjByMzZuR0RkU3JjY2J5WUtfV1VwRDhHaElLZzVoZmZpVW5uRUgxUTRwZk5VZG9SUWI5RGN4SFJSSA?oc=5</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-13T09:09:15</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Adiós, aranceles al aluminio y al acero: Equipo de Trump trabaja en reducir las tarifas del 50 por c</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>El Financiero</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPR3lLek9UN3huUDlLa2FkQmpQTEU0SDRaNFpMTXI1djdnVERnd3RVd293RHFwc2RRbW9BcUpOVXZ6dmRvSlhtVlZGWWNMLWxPdVk4eFVyRGZWRzRob2lKcVdWTjduRlM0Z1dyNjZ3bUxmYmt3R0JHYXo5Z1ZVMVgtODNqbWRIX2ZES0t6QU5pYXNhZDY5WEc0WXJub29tb1o2LTJyaDV1bjg3c3RiMnlSZXpkVER2ZkNkRW1nZVczTmcydC1JbnNybk5XSWVnZmRPY0pFRlRmUXFXU1UxYTBPMWcxbEI3YzZEVDlZTDQ0OF9MaW16?oc=5</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I81" t="n">
+        <v>5</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-13T05:54:21</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Trump planea reducir algunos aranceles sobre el acero y el aluminio, según el ‘Financial Times’ - EL</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>EL PAÍS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxNNFNSREFOSWVRbk5YaFJnYk04bk1lWl9lVjVrS0s5dldZa2dxTWZnY2ZELXMwV3h5ZXByVkZ2QXQ5Y25Ka2oxNTJGdGNJbnF2Yk45cEtyYTh4RndBWk9FNVhhMWJ2b2QxTzlheUdkOUhtNXlKUExaM3k0dng2Q3IzLTFVb01JbkYtc3ZfSUNPTXFwTEVhLTdyWWRMcTgyV2lIcWRhTVZ3N3JTYk5EREtaV3dCUURWZ0ZRQ0p2ZXQ1aUVSNEs4ZkYzNkdSVVNRUXl6bHfSAeYBQVVfeXFMT0ZIOEkwSDdtRHV6YWFjaUhsMjEtSHNfc3d4SmI5WDJpT0E0M1JySG9nTy12RmhjOGRscXlnUlpPakdIVU1CbEVEaE94OWRlNlFBMGljX19zVWE3VVRUZmVxRVdwMlFYYklSMEZweHJxTk93aFpkREZWc1pybjRtU3VvRTZkZGxWbTRWbUpENXU0QTZWa0NHNi1nbzFMU3FMbTZ4eTVIRXBHeFBZMkFQMWlXVW5CX2lwenEtM3lWSWtoSzROZXZLOERSVUdhc05lMlc2Qk1jbVN5Mmx1bjNsTVY2cXdxeEE?oc=5</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-13T03:19:36</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Kristi Noem anuncia compra de acero para reforzar el muro y Sheinbaum responde: “Nosotros construimo</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>El Imparcial</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNUmZpX0VHTFdIbGJadVJUS2Y2TThBMmRqdmRvWHVNQXkwLUZKTU9RU1Y2VVpvWlNXNklmMUZKTVJ6dV9zZXMtRVR4WTQtRW5XNTFONk8zdGU0bkVQQm1jcmNmXy0zZHlVbktCQ2RvOGJxbkJobE1uYWZ5YkNUWWJtZExrWjdkWUZrN0d0ellXdG5OQk9nNXdLd192QmhBb3VfcEVTbVRmWU8yQnlvVUk5eGR0U0xPbGxrZlRUQ0JLV2ctTVlTMFV6T3B2bnkwTFJhc0sxb1B6aHNoUjVueGY0NUpnMGhUOEplRlRETGN6UEZ4VGJ6UkHSAZACQVVfeXFMTkpzQWJGTFc3UVlBc2hxMG1MajlhT2xpbzFKRXFIRVJuMy1TaUR4QlkwWkFDbnpJU0ViQ0FfY3pxNzJKeURlcmJIRXN6TjZnSU40YXJaSXBmSDRhTkljRjFSVVFxOFB2MXlMYUstdDJ6bmZ1UDFZamFoYVBHMkkxbW5LcEktVmVoc2RxZExVS2djZEJvRXlqbXVwQ19LS2Q1R2NwVk5tMzRLbzMydFQ2SzZOTThwRGI1c0E5aW9sbjFBM3FfX2xGQ2xzVTAxRG0wRU1PSEZoZ281U05FODAybjEzUlR5XzdBcklrN1N2Rzh4THR0eFQ2cjl3VjNsY05XQURaN0s3OC01SS1JUS10NE0?oc=5</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-02-13T02:21:00</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Dice Ebrard que planteó en EU revisar aranceles 'disfuncionales' al aluminio y al acero • Economía y</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Forbes México</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNNXB6dGx4OVhpZHBYdFU4cEE2XzRHMUh6T09rN2NLb3FWWjV4TzRfTngzcTFTSDI0eThLWldRRHNNcjI5bk5kT1h4dVdmMUlkWVdyRzQyZ1ZKZEFQbVppdkp5cjlMUTh5QklVZW12WEl3SHYwUkpvcFllTmJ5RFo5bVRRMVFZTmFkLVFQSm1lajdjWFhMeGttVTRQRnVqMmlJZVh0X1kxM2dSUEsw?oc=5</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-02-12T23:57:10</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nucor, Cleveland-Cliffs y Alcoa caen mientras Trump supuestamente considera revertir los aranceles a</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Bitget</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE1pR0NBazI4TmRlLUZsTjBYbmx2WjNVa0UtTUF5bjctTXpYb1NuN2ZDYmFLYi04WXlpUnRPRS1odGFseHJyVndLS0lnendVOHFiTmNicnQ3UnFyVUpWVGd3MWx30gFnQVVfeXFMUHhiaEh3LU9SYTlBLVBiYlJkbFo3Q2JFWDJOQkRWX2ZmRVFwSXAwOWtkbVRWUHFQMENzT3hFWU5SUUY5RFFCNDBQZXBhOVFLS1pqSFJNMTJGWnZKWWprUUxLRzYwT1VDYw?oc=5</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>-0.9379999999999999</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>negativo</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>-5.627999999999999</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-8.441999999999998</v>
+      </c>
+      <c r="I85" t="n">
+        <v>2.814</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-2.814</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-02-12T23:32:45</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pichetto propuso que el peronismo debe ponerle aranceles al acero indio y a las empresas chinas Shei</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Diario Registrado</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwJBVV95cUxOS09MZ21MMjQ5S1RsMHJ1VG1lNFV1dEFHZmNZM1g2c3VINFBxMjVyN2tzaUp5eW0zTEpGb2xNeFY5b0RlMG9QU19FWWdUUkJBNkEwQTBzbHotb3gzNDNJazJCWGdReUVuYk9XakFZRXV4THk5N1pSYjBmZGFTRTZmOG5yU1hmLXVlT2lsRTJTQXI0WnVYc2ZkSF9peUNHVEtuTE9NY2RBRzQ2b1Z2WmJ3eldGR2xPX3hBak5WZm15c2sxcnVNcUFNWVlVMFAwUEpLd2pnQUFlZDZSMWxJdUx5anNoT2k5VW0xU3ZUQXg4NGVSM0N6UWtFeDFBR2N5T2Q5YjJxajJuRQ?oc=5</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J86" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-02-12T19:59:00</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Marcelo Ebrard confirma revisión del T-MEC y aranceles automotrices - Municipios Puebla</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Municipios Puebla</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxQNXZMMXJJSFQ4aUlXQUFnd3BMb2QwWFhveW5tSFFOVHpsSFFfY3NjVTNnY1p6emh1cDZPQk1nU2xhTjR4QXZYTnJvYUY2MHlmMWY1Qk4wNmljM1dKZy1vNTVqMExvMThCZTRjVXd4UXBwZUo0ajZLRzVaYlgwaDB1d1ByYVVtZ1Q3OXo5Q0VkZ0ZxS0I4TnQwa2JVOTBYM3dQRGY1Nk1zbXVVY21XZmc?oc=5</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I87" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-02-12T19:42:35</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Ebrard confirma que México ya “camina” con EEUU y Canadá hacia la revisión del T-MEC; busca mantener</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>El Imparcial</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiygJBVV95cUxPaXhOb3c3dXlhb2R6dXNlYjh3ZDVZa0VJVVdnaUYxcXU5eTVRMWZ5by1vZHVnYkI3WDFpeDRQMF9WV1F2U01udC1fSUY3VnMtYUZRNFFBd3ZDbUlIQ2tSeUt6eklYdDA4ZERLek9USXp0RHdRN2NEY1N2V0lnYll1cU9KRVRSNGZ6R2xuaDc3dElKM1ZQd1JKY2kzNHk1TEV2X3ZMM2U5R245S0Z5c3VYWHdSLXpoV2hBTFphcng5VE5TeHdHQjlwTTZLNFlsWThScUxEeEZqVmVsTDJadkZyNzZEV1d1MmRYSkdiRklhSEcxUU1JdEtiRnM5RWt5TnVXdEp1MHZHdDNMNnJTamk4aDJCLTQ1ekk3eVRSNGpjM0JManpYZ2N3OGxTNVVCYnV6X3VrX1JDb2VqbnZMRWt4R1I0T3Q5NUktVWfSAeQCQVVfeXFMTldzY0hORGZ6d18xaEkta05YWmg2UG5NcTdjNUduMFNCbVlkV2VlQU1CTTlJQ2dyWURHdWZQdVoyelhKeFpZcjN1NkY0N1lrdFljZGIxVGU1YmxHOWpTVW90QkFULURwSXVaRmtaSnVtSmF0WUJPbWIxa1hsOTBOb1BRbVdNMEZZcC04ejFqREZNVHlJTXFGQktvZUtVQmpSQkV0ZjVjWWp6SUJYOHVZVmRRd3JxZmtuV29aZjdqZlZ3OENULUNPQTdaXzVXTHpCTjJ0b2lkMWtEdGdETDR0YmZjdHpHMGVqLUl5ZlJiNkl4STgwRnA5RXkyNkx2aWNoWGJzUlRLWVVDTFlYUlJGLUNfVWZzYldCS2tLSFdsUFVXUGVXb3VYY3FOZVY0UGpDeVBESEg1NVBHT3pkRmp6WGluT28tOFhzZkFfc25MRFI1OGEwWkhaYkMwcG45OU9XVDFuNnA?oc=5</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-5.100000000000001</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-02-12T18:44:30</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Consulta concluye con apoyo unánime para renovar y perfeccionar T-MEC rumbo a revisión 2026: Ebrard </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>debate.com.mx</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi_wFBVV95cUxOLUp5NkxrQ19YYy1KLU9zMHg2SnVTTmR2dUY2azd1Vk54VHYtcnBBZkpvcG8zeFlGRDl5SFNXbWxfZVpQdG41QUZMTnFnRDl0TWdaMWdlVGFZUHBWUUUxbTRlVFJ2Z1hRbFNCUUN2Rnp4UlhCUTlHNmhUcnZvNXh1TjNLcmt3N3RwV1AtNTZFTkszdDlaNG1SRDlnM0U3dkoxclQwRnNXQUh5MVo5ODd0ZjRPSzVwZ2hveVBRT1R6UVlNVW82ZnNDSWxBaFRqdTVwSUp0czJzLUVzR2NGNzN2eU0xR3BoZTVoQVpfd3J4aGphMHh2MGxKeXJjN2s1YzTSAYQCQVVfeXFMTW10VGlFYWVqdlNNTXZIWlRaUTVhcEdYX2duanZMRnMzWjhGcnc4Vld1R3c5aXFMVnozZENMTEF3aDA3N3M2aFpzOUFJT0xYVFNCWGxwN080ZkJiMDFpdzJuTldsSENHRFR4UEJLQ2lWTFRwaDZvVEJkU0tDYS1BRnh3emtUZFMtbTdwY3RiY3VoMEQ1ejI4NEl5cTVWNHluU3B4OWR4ZFQ4bndtcDk2ZFFFYmdFNGt5MGN4M1J6cG5mbUpKX040VnV2R1hBS0VmbnpFYmFsb0tGYUNRTDBBMERGaUFyUGVYMTl3aGFxaVRhWndJVF80MmpXWjlMWW03UWIyYS0?oc=5</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
